--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.66</v>
+        <v>1.81</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>2.68</v>
+        <v>4.59</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.95</v>
+        <v>2.66</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="R19" t="n">
-        <v>4.11</v>
+        <v>2.68</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="R20" t="n">
-        <v>4.59</v>
+        <v>4.11</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.54</v>
+        <v>2.09</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R21" t="n">
-        <v>2.91</v>
+        <v>3.84</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.09</v>
+        <v>2.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R22" t="n">
-        <v>3.84</v>
+        <v>2.91</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R28" t="n">
-        <v>4.4</v>
+        <v>4.98</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>4.98</v>
+        <v>4.4</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,112 +2377,112 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,112 +2771,112 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="R18" t="n">
-        <v>4.59</v>
+        <v>4.11</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.66</v>
+        <v>1.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>2.68</v>
+        <v>4.59</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>2.66</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="R20" t="n">
-        <v>4.11</v>
+        <v>2.68</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>3.94</v>
+        <v>5.4</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="R28" t="n">
-        <v>4.98</v>
+        <v>4.36</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="R30" t="n">
-        <v>4.36</v>
+        <v>4.98</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,112 +2377,112 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,112 +2771,112 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>2.66</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="R18" t="n">
-        <v>4.11</v>
+        <v>2.68</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.66</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="R20" t="n">
-        <v>2.68</v>
+        <v>4.11</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="R28" t="n">
-        <v>4.36</v>
+        <v>4.98</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="R29" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
-        <v>4.98</v>
+        <v>4.4</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.09</v>
+        <v>2.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R21" t="n">
-        <v>3.84</v>
+        <v>2.91</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.54</v>
+        <v>2.09</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R22" t="n">
-        <v>2.91</v>
+        <v>3.84</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>3.94</v>
+        <v>5.4</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="R28" t="n">
-        <v>4.98</v>
+        <v>4.36</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="R29" t="n">
-        <v>4.36</v>
+        <v>4.98</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.66</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="R18" t="n">
-        <v>2.68</v>
+        <v>4.11</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>2.66</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="R20" t="n">
-        <v>4.11</v>
+        <v>2.68</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.54</v>
+        <v>2.09</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R21" t="n">
-        <v>2.91</v>
+        <v>3.84</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.09</v>
+        <v>2.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R22" t="n">
-        <v>3.84</v>
+        <v>2.91</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,112 +2377,112 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,112 +2771,112 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>2.66</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="R18" t="n">
-        <v>4.11</v>
+        <v>2.68</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.66</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="R20" t="n">
-        <v>2.68</v>
+        <v>4.11</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.09</v>
+        <v>2.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R21" t="n">
-        <v>3.84</v>
+        <v>2.91</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.54</v>
+        <v>2.09</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R22" t="n">
-        <v>2.91</v>
+        <v>3.84</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="R25" t="n">
-        <v>5.4</v>
+        <v>3.94</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,112 +2377,112 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,112 +2771,112 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.66</v>
+        <v>1.81</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>2.68</v>
+        <v>4.59</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>2.66</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="R19" t="n">
-        <v>4.59</v>
+        <v>2.68</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,112 +2574,112 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,112 +2771,112 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="R12" t="n">
-        <v>2.35</v>
+        <v>3.19</v>
       </c>
       <c r="S12" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="R18" t="n">
-        <v>4.59</v>
+        <v>4.11</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.66</v>
+        <v>1.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>2.68</v>
+        <v>4.59</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>2.66</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="R20" t="n">
-        <v>4.11</v>
+        <v>2.68</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="R24" t="n">
-        <v>5.4</v>
+        <v>3.94</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>3.94</v>
+        <v>5.4</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="R30" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI30"/>
+  <dimension ref="A1:BI29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.01</v>
+        <v>2.32</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="R10" t="n">
-        <v>3.95</v>
+        <v>3.19</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2570,116 +2570,116 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R11" t="n">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="S11" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.32</v>
+        <v>2.01</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="R12" t="n">
-        <v>3.19</v>
+        <v>3.95</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2915,27 +2915,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,112 +2968,112 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.81</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="R13" t="n">
-        <v>4.17</v>
+        <v>2.35</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>46113.6875</v>
+        <v>46113.625</v>
       </c>
     </row>
     <row r="14">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>46113.72916666666</v>
+        <v>46113.6875</v>
       </c>
     </row>
     <row r="15">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46113.75</v>
+        <v>46113.72916666666</v>
       </c>
     </row>
     <row r="17">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>4.11</v>
+        <v>4.59</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>2.66</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="R19" t="n">
-        <v>4.59</v>
+        <v>2.68</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.66</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="R20" t="n">
-        <v>2.68</v>
+        <v>4.11</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.67</v>
+        <v>2.36</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>3.24</v>
       </c>
       <c r="R25" t="n">
-        <v>5.4</v>
+        <v>3.25</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46113.83333333334</v>
+        <v>46113.85416666666</v>
       </c>
     </row>
     <row r="26">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.24</v>
+        <v>2.92</v>
       </c>
       <c r="R26" t="n">
-        <v>3.25</v>
+        <v>2.45</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46113.85416666666</v>
+        <v>46113.875</v>
       </c>
     </row>
     <row r="27">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.1</v>
+        <v>1.76</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="R27" t="n">
-        <v>2.45</v>
+        <v>4.98</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46113.875</v>
+        <v>46113.89583333334</v>
       </c>
     </row>
     <row r="28">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="R28" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>4.98</v>
+        <v>4.4</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6255,203 +6255,6 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>46113.89583333334</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Brazil Serie A</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Fluminense</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Corinthians</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P30" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="R30" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI30" s="3" t="n">
         <v>46113.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2570,17 +2570,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="R11" t="n">
-        <v>2.87</v>
+        <v>3.95</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,112 +2771,112 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.01</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
-        <v>3.95</v>
+        <v>2.35</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,112 +2968,112 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="S13" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="R18" t="n">
-        <v>4.59</v>
+        <v>4.11</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>4.11</v>
+        <v>4.59</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="R27" t="n">
-        <v>4.98</v>
+        <v>4.36</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="R28" t="n">
-        <v>4.36</v>
+        <v>4.98</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,112 +2377,112 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>3.19</v>
+        <v>2.35</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,112 +2771,112 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="R12" t="n">
-        <v>2.35</v>
+        <v>3.19</v>
       </c>
       <c r="S12" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>2.66</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="R18" t="n">
-        <v>4.11</v>
+        <v>2.68</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.66</v>
+        <v>1.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>2.68</v>
+        <v>4.59</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="R20" t="n">
-        <v>4.59</v>
+        <v>4.11</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="R23" t="n">
-        <v>5.4</v>
+        <v>3.94</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>3.94</v>
+        <v>5.4</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>4.98</v>
+        <v>4.4</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R29" t="n">
-        <v>4.4</v>
+        <v>4.98</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,112 +2377,112 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="S10" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.01</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="R11" t="n">
-        <v>3.95</v>
+        <v>3.19</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.32</v>
+        <v>2.01</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="R12" t="n">
-        <v>3.19</v>
+        <v>3.95</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,112 +2968,112 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R13" t="n">
-        <v>2.87</v>
+        <v>2.35</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.66</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="R18" t="n">
-        <v>2.68</v>
+        <v>4.11</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>2.66</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="R19" t="n">
-        <v>4.59</v>
+        <v>2.68</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>4.11</v>
+        <v>4.59</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.54</v>
+        <v>2.09</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R21" t="n">
-        <v>2.91</v>
+        <v>3.84</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.09</v>
+        <v>2.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R22" t="n">
-        <v>3.84</v>
+        <v>2.91</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R28" t="n">
-        <v>4.4</v>
+        <v>4.98</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="R29" t="n">
-        <v>4.98</v>
+        <v>4.36</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="R10" t="n">
-        <v>2.87</v>
+        <v>3.95</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>3.95</v>
+        <v>2.87</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.66</v>
+        <v>1.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>2.68</v>
+        <v>4.59</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.81</v>
+        <v>2.66</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="R20" t="n">
-        <v>4.59</v>
+        <v>2.68</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>3.94</v>
+        <v>5.4</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="R24" t="n">
-        <v>5.4</v>
+        <v>3.94</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R27" t="n">
-        <v>4.4</v>
+        <v>4.98</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="R28" t="n">
-        <v>4.98</v>
+        <v>4.36</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>3.95</v>
+        <v>2.87</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="R12" t="n">
-        <v>2.87</v>
+        <v>3.95</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>4.11</v>
+        <v>4.59</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="R19" t="n">
-        <v>4.59</v>
+        <v>4.11</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.09</v>
+        <v>2.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R21" t="n">
-        <v>3.84</v>
+        <v>2.91</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.54</v>
+        <v>2.09</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R22" t="n">
-        <v>2.91</v>
+        <v>3.84</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="R23" t="n">
-        <v>5.4</v>
+        <v>3.94</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>3.94</v>
+        <v>5.4</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="R27" t="n">
-        <v>4.98</v>
+        <v>4.36</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="R28" t="n">
-        <v>4.36</v>
+        <v>4.98</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,112 +2377,112 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R10" t="n">
-        <v>2.87</v>
+        <v>2.35</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>2.01</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="R11" t="n">
-        <v>3.19</v>
+        <v>3.95</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.01</v>
+        <v>2.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="R12" t="n">
-        <v>3.95</v>
+        <v>3.19</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,112 +2968,112 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="S13" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="R18" t="n">
-        <v>4.59</v>
+        <v>4.11</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>4.11</v>
+        <v>4.59</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="R27" t="n">
-        <v>4.36</v>
+        <v>4.98</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>4.98</v>
+        <v>4.4</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="R29" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="R27" t="n">
-        <v>4.98</v>
+        <v>4.36</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="R29" t="n">
-        <v>4.36</v>
+        <v>4.98</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.01</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="R11" t="n">
-        <v>3.95</v>
+        <v>3.19</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>3.19</v>
+        <v>2.87</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="R13" t="n">
-        <v>2.87</v>
+        <v>3.95</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>2.66</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="R18" t="n">
-        <v>4.11</v>
+        <v>2.68</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.66</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="R20" t="n">
-        <v>2.68</v>
+        <v>4.11</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.54</v>
+        <v>2.09</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R21" t="n">
-        <v>2.91</v>
+        <v>3.84</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.09</v>
+        <v>2.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R22" t="n">
-        <v>3.84</v>
+        <v>2.91</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R28" t="n">
-        <v>4.4</v>
+        <v>4.98</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>4.98</v>
+        <v>4.4</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,112 +2377,112 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="R10" t="n">
-        <v>2.35</v>
+        <v>3.95</v>
       </c>
       <c r="S10" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,112 +2771,112 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
-        <v>2.87</v>
+        <v>2.35</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>3.95</v>
+        <v>2.87</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.66</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="R18" t="n">
-        <v>2.68</v>
+        <v>4.11</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>2.66</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="R19" t="n">
-        <v>4.59</v>
+        <v>2.68</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>4.11</v>
+        <v>4.59</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.09</v>
+        <v>2.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R21" t="n">
-        <v>3.84</v>
+        <v>2.91</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.54</v>
+        <v>2.09</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R22" t="n">
-        <v>2.91</v>
+        <v>3.84</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>3.94</v>
+        <v>5.4</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="R24" t="n">
-        <v>5.4</v>
+        <v>3.94</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.01</v>
+        <v>2.32</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="R10" t="n">
-        <v>3.95</v>
+        <v>3.19</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>2.01</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="R11" t="n">
-        <v>3.19</v>
+        <v>3.95</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>2.66</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="R18" t="n">
-        <v>4.11</v>
+        <v>2.68</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.66</v>
+        <v>1.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>2.68</v>
+        <v>4.59</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="R20" t="n">
-        <v>4.59</v>
+        <v>4.11</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.54</v>
+        <v>2.09</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R21" t="n">
-        <v>2.91</v>
+        <v>3.84</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.09</v>
+        <v>2.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R22" t="n">
-        <v>3.84</v>
+        <v>2.91</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="R29" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>2.01</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="R10" t="n">
-        <v>3.19</v>
+        <v>3.95</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.01</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="R11" t="n">
-        <v>3.95</v>
+        <v>3.19</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.66</v>
+        <v>1.81</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>2.68</v>
+        <v>4.59</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="R19" t="n">
-        <v>4.59</v>
+        <v>4.11</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>2.66</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="R20" t="n">
-        <v>4.11</v>
+        <v>2.68</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R27" t="n">
-        <v>4.4</v>
+        <v>4.98</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>4.98</v>
+        <v>4.4</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.01</v>
+        <v>2.32</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="R10" t="n">
-        <v>3.95</v>
+        <v>3.19</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,112 +2574,112 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="R11" t="n">
-        <v>3.19</v>
+        <v>2.35</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,112 +2771,112 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="R12" t="n">
-        <v>2.35</v>
+        <v>3.95</v>
       </c>
       <c r="S12" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.95</v>
+        <v>2.66</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="R19" t="n">
-        <v>4.11</v>
+        <v>2.68</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.66</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="R20" t="n">
-        <v>2.68</v>
+        <v>4.11</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,112 +2574,112 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R11" t="n">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="S11" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,112 +2968,112 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R13" t="n">
-        <v>2.87</v>
+        <v>2.35</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="R18" t="n">
-        <v>4.59</v>
+        <v>4.11</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>4.11</v>
+        <v>4.59</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.09</v>
+        <v>2.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R21" t="n">
-        <v>3.84</v>
+        <v>2.91</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.54</v>
+        <v>2.09</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R22" t="n">
-        <v>2.91</v>
+        <v>3.84</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="R23" t="n">
-        <v>5.4</v>
+        <v>3.94</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>3.94</v>
+        <v>5.4</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>3.19</v>
+        <v>2.87</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="R11" t="n">
-        <v>2.87</v>
+        <v>3.19</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.66</v>
+        <v>1.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>2.68</v>
+        <v>4.59</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.81</v>
+        <v>2.66</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="R20" t="n">
-        <v>4.59</v>
+        <v>2.68</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.54</v>
+        <v>2.09</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R21" t="n">
-        <v>2.91</v>
+        <v>3.84</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.09</v>
+        <v>2.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R22" t="n">
-        <v>3.84</v>
+        <v>2.91</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>4.98</v>
+        <v>4.4</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="R28" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="R29" t="n">
-        <v>4.36</v>
+        <v>4.98</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,112 +2574,112 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="R11" t="n">
-        <v>3.19</v>
+        <v>2.35</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,112 +2968,112 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="R13" t="n">
-        <v>2.35</v>
+        <v>3.19</v>
       </c>
       <c r="S13" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>2.66</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="R18" t="n">
-        <v>4.11</v>
+        <v>2.68</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.66</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="R20" t="n">
-        <v>2.68</v>
+        <v>4.11</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.09</v>
+        <v>2.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R21" t="n">
-        <v>3.84</v>
+        <v>2.91</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.54</v>
+        <v>2.09</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R22" t="n">
-        <v>2.91</v>
+        <v>3.84</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>3.94</v>
+        <v>5.4</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="R24" t="n">
-        <v>5.4</v>
+        <v>3.94</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="R27" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.05</v>
+        <v>2.32</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="R10" t="n">
-        <v>2.87</v>
+        <v>3.19</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,112 +2574,112 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R11" t="n">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="S11" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,112 +2968,112 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="R13" t="n">
-        <v>3.19</v>
+        <v>2.35</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.54</v>
+        <v>2.09</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R21" t="n">
-        <v>2.91</v>
+        <v>3.84</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.09</v>
+        <v>2.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R22" t="n">
-        <v>3.84</v>
+        <v>2.91</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="R23" t="n">
-        <v>5.4</v>
+        <v>3.94</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>3.94</v>
+        <v>5.4</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.32</v>
+        <v>2.01</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="R10" t="n">
-        <v>3.19</v>
+        <v>3.95</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,112 +2574,112 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R11" t="n">
-        <v>2.87</v>
+        <v>2.35</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>3.95</v>
+        <v>2.87</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,112 +2968,112 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="R13" t="n">
-        <v>2.35</v>
+        <v>3.19</v>
       </c>
       <c r="S13" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.66</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="R18" t="n">
-        <v>2.68</v>
+        <v>4.11</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>2.66</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="R19" t="n">
-        <v>4.59</v>
+        <v>2.68</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
-        <v>4.11</v>
+        <v>4.59</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1983,76 +1983,76 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="R8" t="n">
         <v>2.06</v>
       </c>
       <c r="S8" t="n">
-        <v>4.65</v>
+        <v>4.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="U8" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="V8" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="W8" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="X8" t="n">
-        <v>3.68</v>
+        <v>3.79</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="Z8" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.62</v>
+        <v>3.06</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AG8" t="n">
-        <v>6.12</v>
+        <v>6.48</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AI8" t="n">
-        <v>12</v>
+        <v>14.7</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AN8" t="n">
         <v>1.27</v>
@@ -2061,52 +2061,52 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AR8" t="n">
         <v>2.36</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.27</v>
+        <v>3.38</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.84</v>
+        <v>4.77</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AZ8" t="n">
         <v>3.06</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.77</v>
+        <v>2.98</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BF8" t="n">
         <v>1.05</v>
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.51</v>
+        <v>2.37</v>
       </c>
       <c r="Q9" t="n">
         <v>3.58</v>
       </c>
       <c r="R9" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.01</v>
+        <v>2.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>3.95</v>
+        <v>2.54</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>2.35</v>
+        <v>4.72</v>
       </c>
       <c r="S11" t="n">
-        <v>3.12</v>
+        <v>2.57</v>
       </c>
       <c r="T11" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="U11" t="n">
-        <v>2.91</v>
+        <v>4.45</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W11" t="n">
-        <v>2.91</v>
+        <v>2.59</v>
       </c>
       <c r="X11" t="n">
-        <v>2.66</v>
+        <v>3.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.3</v>
+        <v>7.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.28</v>
+        <v>2.89</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AI11" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.04</v>
+        <v>1.82</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.42</v>
+        <v>1.8</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.13</v>
+        <v>1.46</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.31</v>
+        <v>1.79</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.74</v>
+        <v>2.28</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.48</v>
+        <v>4</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.39</v>
+        <v>2.45</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.95</v>
+        <v>1.87</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.76</v>
+        <v>1.32</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.68</v>
+        <v>3.34</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,112 +2771,112 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R12" t="n">
-        <v>2.87</v>
+        <v>2.35</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>4.39</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R28" t="n">
-        <v>4.4</v>
+        <v>4.98</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="R29" t="n">
-        <v>4.98</v>
+        <v>4.36</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>2.54</v>
+        <v>3.18</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AF10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC10" t="n">
         <v>2.2</v>
       </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0</v>
-      </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF13" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AG13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.16</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>4.11</v>
+        <v>4.59</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="R20" t="n">
-        <v>4.59</v>
+        <v>4.11</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.09</v>
+        <v>2.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R21" t="n">
-        <v>3.84</v>
+        <v>2.91</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.54</v>
+        <v>2.09</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R22" t="n">
-        <v>2.91</v>
+        <v>3.84</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R27" t="n">
-        <v>4.4</v>
+        <v>4.98</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>4.98</v>
+        <v>4.4</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2183,10 +2183,10 @@
         <v>2.37</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.58</v>
+        <v>3.54</v>
       </c>
       <c r="R9" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2383,7 +2383,7 @@
         <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="S10" t="n">
         <v>2.86</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.75</v>
+        <v>2.28</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>4.72</v>
+        <v>2.54</v>
       </c>
       <c r="S11" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.14</v>
+        <v>1.65</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2771,40 +2771,40 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="S12" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="U12" t="n">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W12" t="n">
-        <v>2.91</v>
+        <v>2.63</v>
       </c>
       <c r="X12" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="Z12" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AB12" t="n">
         <v>1.01</v>
@@ -2813,7 +2813,7 @@
         <v>1.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AE12" t="n">
         <v>1.85</v>
@@ -2822,28 +2822,28 @@
         <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AJ12" t="n">
         <v>1.07</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BC12" t="n">
         <v>2.18</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.68</v>
+        <v>3.8</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AR13" t="n">
         <v>2.28</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R14" t="n">
-        <v>4.17</v>
+        <v>3.7</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.88</v>
       </c>
-      <c r="Q17" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="R17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="Q18" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X18" t="n">
         <v>3.3</v>
       </c>
-      <c r="R18" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="R19" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD19" t="n">
         <v>2.66</v>
       </c>
-      <c r="Q19" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4356,124 +4356,124 @@
         <v>4.11</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.54</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.24</v>
+        <v>2.91</v>
       </c>
       <c r="R21" t="n">
-        <v>2.91</v>
+        <v>3.2</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.38</v>
+        <v>3.9</v>
       </c>
       <c r="R23" t="n">
-        <v>3.94</v>
+        <v>5.5</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>5.4</v>
+        <v>4.16</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5341,40 +5341,40 @@
         <v>3.25</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AE25" t="n">
         <v>2.1</v>
@@ -5383,82 +5383,82 @@
         <v>1.7</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5538,124 +5538,124 @@
         <v>2.45</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="R27" t="n">
-        <v>4.98</v>
+        <v>4.36</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5932,124 +5932,124 @@
         <v>4.4</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.44</v>
+        <v>3.28</v>
       </c>
       <c r="R29" t="n">
-        <v>4.36</v>
+        <v>4.98</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.75</v>
+        <v>1.61</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,40 +2377,40 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="S10" t="n">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="T10" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U10" t="n">
-        <v>3.78</v>
+        <v>3.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="X10" t="n">
-        <v>2.89</v>
+        <v>2.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AB10" t="n">
         <v>1.01</v>
@@ -2419,91 +2419,91 @@
         <v>1.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AI10" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.58</v>
+        <v>1.31</v>
       </c>
       <c r="AR10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS10" t="n">
         <v>1.95</v>
       </c>
-      <c r="AS10" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AT10" t="n">
-        <v>3.3</v>
+        <v>2.48</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.88</v>
+        <v>4.39</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.16</v>
+        <v>2.95</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.26</v>
+        <v>1.45</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
         <v>1.22</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.55</v>
+        <v>1.81</v>
       </c>
       <c r="Q12" t="n">
         <v>3.3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>2.57</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="U12" t="n">
-        <v>3.2</v>
+        <v>4.45</v>
       </c>
       <c r="V12" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W12" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="X12" t="n">
-        <v>2.6</v>
+        <v>3.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AG12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AS12" t="n">
         <v>3</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AT12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AX12" t="n">
         <v>1.32</v>
       </c>
-      <c r="AI12" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AY12" t="n">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="S13" t="n">
-        <v>2.57</v>
+        <v>2.86</v>
       </c>
       <c r="T13" t="n">
         <v>2.04</v>
       </c>
       <c r="U13" t="n">
-        <v>4.45</v>
+        <v>3.78</v>
       </c>
       <c r="V13" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W13" t="n">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="X13" t="n">
-        <v>3.02</v>
+        <v>2.89</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="AA13" t="n">
         <v>1.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="AG13" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AH13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB13" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.26</v>
-      </c>
       <c r="BC13" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.34</v>
+        <v>3.64</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="R18" t="n">
-        <v>4.33</v>
+        <v>4.11</v>
       </c>
       <c r="S18" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="T18" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="U18" t="n">
-        <v>5.68</v>
+        <v>5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W18" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="X18" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY18" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z18" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC18" t="n">
+      <c r="AZ18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BB18" t="n">
         <v>1.36</v>
       </c>
-      <c r="AD18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT18" t="n">
+      <c r="BC18" t="n">
         <v>2.56</v>
       </c>
-      <c r="AU18" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.41</v>
-      </c>
       <c r="BD18" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T20" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q20" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="R20" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="U20" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD20" t="n">
         <v>2.7</v>
       </c>
-      <c r="T20" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U20" t="n">
-        <v>5</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC20" t="n">
+      <c r="AE20" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY20" t="n">
         <v>1.42</v>
       </c>
-      <c r="AD20" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AZ20" t="n">
-        <v>1.72</v>
+        <v>1.12</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.79</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,28 +4938,28 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>5.5</v>
+        <v>4.16</v>
       </c>
       <c r="S23" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="T23" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="U23" t="n">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="V23" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W23" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="X23" t="n">
         <v>2.99</v>
@@ -4968,100 +4968,100 @@
         <v>1.34</v>
       </c>
       <c r="Z23" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB23" t="n">
         <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AI23" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AM23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN23" t="n">
+      <c r="AQ23" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BC23" t="n">
         <v>2.27</v>
       </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU23" t="n">
+      <c r="BD23" t="n">
         <v>3.5</v>
       </c>
-      <c r="AV23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>3.42</v>
-      </c>
       <c r="BE23" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BF23" t="n">
         <v>1.11</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,28 +5135,28 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="R24" t="n">
-        <v>4.16</v>
+        <v>5.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="T24" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="U24" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="V24" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W24" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="X24" t="n">
         <v>2.99</v>
@@ -5165,100 +5165,100 @@
         <v>1.34</v>
       </c>
       <c r="Z24" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB24" t="n">
         <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AF24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AL24" t="n">
         <v>1.7</v>
       </c>
-      <c r="AG24" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AM24" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.88</v>
+        <v>2.27</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.75</v>
+        <v>3.9</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BF24" t="n">
         <v>1.11</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,112 +5923,112 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R28" t="n">
-        <v>4.4</v>
+        <v>4.98</v>
       </c>
       <c r="S28" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="T28" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U28" t="n">
-        <v>4.99</v>
+        <v>5.6</v>
       </c>
       <c r="V28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY28" t="n">
         <v>1.41</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.42</v>
       </c>
       <c r="AZ28" t="n">
         <v>1.36</v>
@@ -6037,19 +6037,19 @@
         <v>3.86</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,112 +6120,112 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="Q29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U29" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG29" t="n">
         <v>3.28</v>
       </c>
-      <c r="R29" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U29" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>4</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AI29" t="n">
-        <v>7.9</v>
+        <v>6.25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.11</v>
+        <v>1.88</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AQ29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY29" t="n">
         <v>1.42</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.41</v>
       </c>
       <c r="AZ29" t="n">
         <v>1.36</v>
@@ -6234,19 +6234,19 @@
         <v>3.86</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,112 +2377,112 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="S10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,112 +2574,112 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R11" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW11" t="n">
         <v>2.2</v>
       </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T18" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q18" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="R18" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD18" t="n">
         <v>2.7</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U18" t="n">
-        <v>5</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC18" t="n">
+      <c r="AE18" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY18" t="n">
         <v>1.42</v>
       </c>
-      <c r="AD18" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>1.72</v>
+        <v>1.12</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.79</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.44</v>
+        <v>1.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.82</v>
+        <v>3.16</v>
       </c>
       <c r="R19" t="n">
-        <v>3.24</v>
+        <v>4.11</v>
       </c>
       <c r="S19" t="n">
-        <v>3.17</v>
+        <v>2.7</v>
       </c>
       <c r="T19" t="n">
-        <v>1.82</v>
+        <v>2.03</v>
       </c>
       <c r="U19" t="n">
-        <v>4.26</v>
+        <v>5</v>
       </c>
       <c r="V19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>1.54</v>
       </c>
-      <c r="W19" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AR19" t="n">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.82</v>
+        <v>2.26</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.57</v>
+        <v>3</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.19</v>
+        <v>3.05</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.84</v>
+        <v>2.28</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.32</v>
+        <v>1.91</v>
       </c>
       <c r="AX19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ19" t="n">
         <v>1.72</v>
       </c>
-      <c r="AY19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.61</v>
-      </c>
       <c r="BA19" t="n">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.73</v>
+        <v>2.44</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.34</v>
+        <v>2.82</v>
       </c>
       <c r="R20" t="n">
-        <v>4.33</v>
+        <v>3.24</v>
       </c>
       <c r="S20" t="n">
-        <v>2.43</v>
+        <v>3.17</v>
       </c>
       <c r="T20" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="U20" t="n">
-        <v>5.68</v>
+        <v>4.26</v>
       </c>
       <c r="V20" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="W20" t="n">
-        <v>2.47</v>
+        <v>2.29</v>
       </c>
       <c r="X20" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.9</v>
+        <v>8</v>
       </c>
       <c r="AA20" t="n">
         <v>1.01</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG20" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AI20" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4434,19 +4434,19 @@
         <v>1.62</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.22</v>
+        <v>4.19</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="AX20" t="n">
         <v>1.72</v>
@@ -4455,25 +4455,25 @@
         <v>1.42</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.12</v>
+        <v>1.61</v>
       </c>
       <c r="BA20" t="n">
-        <v>9.050000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,28 +4544,28 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.91</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="S21" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="T21" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="U21" t="n">
-        <v>3.83</v>
+        <v>4.2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W21" t="n">
-        <v>2.39</v>
+        <v>2.59</v>
       </c>
       <c r="X21" t="n">
         <v>3.04</v>
@@ -4574,19 +4574,19 @@
         <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="n">
         <v>1.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="AE21" t="n">
         <v>2.15</v>
@@ -4595,82 +4595,82 @@
         <v>1.66</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.84</v>
+        <v>3.74</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AJ21" t="n">
         <v>1.03</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AN21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX21" t="n">
         <v>1.62</v>
       </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AY21" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="BB21" t="n">
         <v>1.27</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,28 +4741,28 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="R22" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="S22" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="U22" t="n">
-        <v>4.2</v>
+        <v>3.83</v>
       </c>
       <c r="V22" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W22" t="n">
-        <v>2.59</v>
+        <v>2.39</v>
       </c>
       <c r="X22" t="n">
         <v>3.04</v>
@@ -4771,19 +4771,19 @@
         <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA22" t="n">
         <v>1.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="AE22" t="n">
         <v>2.15</v>
@@ -4792,82 +4792,82 @@
         <v>1.66</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI22" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AJ22" t="n">
         <v>1.03</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="BB22" t="n">
         <v>1.27</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,28 +4938,28 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="R23" t="n">
-        <v>4.16</v>
+        <v>5.5</v>
       </c>
       <c r="S23" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="T23" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="U23" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="V23" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W23" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="X23" t="n">
         <v>2.99</v>
@@ -4968,100 +4968,100 @@
         <v>1.34</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB23" t="n">
         <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AF23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AL23" t="n">
         <v>1.7</v>
       </c>
-      <c r="AG23" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AM23" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.88</v>
+        <v>2.27</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.75</v>
+        <v>3.9</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BF23" t="n">
         <v>1.11</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,28 +5135,28 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>5.5</v>
+        <v>4.16</v>
       </c>
       <c r="S24" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="T24" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="U24" t="n">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="V24" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W24" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="X24" t="n">
         <v>2.99</v>
@@ -5165,100 +5165,100 @@
         <v>1.34</v>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB24" t="n">
         <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AI24" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AM24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN24" t="n">
+      <c r="AQ24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BC24" t="n">
         <v>2.27</v>
       </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU24" t="n">
+      <c r="BD24" t="n">
         <v>3.5</v>
       </c>
-      <c r="AV24" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>3.42</v>
-      </c>
       <c r="BE24" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BF24" t="n">
         <v>1.11</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,49 +5726,49 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="T27" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="U27" t="n">
-        <v>4.85</v>
+        <v>4.99</v>
       </c>
       <c r="V27" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W27" t="n">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="X27" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="AE27" t="n">
         <v>2.05</v>
@@ -5777,82 +5777,82 @@
         <v>1.75</v>
       </c>
       <c r="AG27" t="n">
-        <v>4.1</v>
+        <v>3.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AI27" t="n">
-        <v>9</v>
+        <v>6.25</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="AL27" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AX27" t="n">
         <v>1.72</v>
       </c>
-      <c r="AM27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AY27" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.8</v>
+        <v>3.86</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.22</v>
+        <v>3.44</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.28</v>
+        <v>3.44</v>
       </c>
       <c r="R28" t="n">
-        <v>4.98</v>
+        <v>4.36</v>
       </c>
       <c r="S28" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="T28" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="U28" t="n">
-        <v>5.6</v>
+        <v>4.85</v>
       </c>
       <c r="V28" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W28" t="n">
         <v>2.47</v>
       </c>
       <c r="X28" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="Y28" t="n">
         <v>1.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB28" t="n">
         <v>1.03</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.89</v>
+        <v>2.68</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AG28" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AI28" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="AJ28" t="n">
         <v>1.02</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AN28" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="BA28" t="n">
-        <v>3.86</v>
+        <v>2.8</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,112 +6120,112 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R29" t="n">
-        <v>4.4</v>
+        <v>4.98</v>
       </c>
       <c r="S29" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="T29" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U29" t="n">
-        <v>4.99</v>
+        <v>5.6</v>
       </c>
       <c r="V29" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY29" t="n">
         <v>1.41</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.42</v>
       </c>
       <c r="AZ29" t="n">
         <v>1.36</v>
@@ -6234,19 +6234,19 @@
         <v>3.86</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,112 +2377,112 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AF10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW10" t="n">
         <v>2.2</v>
       </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.55</v>
+        <v>1.81</v>
       </c>
       <c r="Q11" t="n">
         <v>3.3</v>
       </c>
       <c r="R11" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="S11" t="n">
-        <v>3.2</v>
+        <v>2.57</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="U11" t="n">
-        <v>3.2</v>
+        <v>4.45</v>
       </c>
       <c r="V11" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W11" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="X11" t="n">
-        <v>2.6</v>
+        <v>3.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>6</v>
+        <v>7.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.3</v>
+        <v>2.89</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="AG11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AS11" t="n">
         <v>3</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AT11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AX11" t="n">
         <v>1.32</v>
       </c>
-      <c r="AI11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AY11" t="n">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
-        <v>2.57</v>
+        <v>2.86</v>
       </c>
       <c r="T12" t="n">
         <v>2.04</v>
       </c>
       <c r="U12" t="n">
-        <v>4.45</v>
+        <v>3.78</v>
       </c>
       <c r="V12" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W12" t="n">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="X12" t="n">
-        <v>3.02</v>
+        <v>2.89</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="AA12" t="n">
         <v>1.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="AG12" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="AH12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB12" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.26</v>
-      </c>
       <c r="BC12" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.34</v>
+        <v>3.64</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF13" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>3</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AG13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="R18" t="n">
-        <v>4.33</v>
+        <v>4.11</v>
       </c>
       <c r="S18" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="T18" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="U18" t="n">
-        <v>5.68</v>
+        <v>5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W18" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="X18" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY18" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z18" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC18" t="n">
+      <c r="AZ18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BB18" t="n">
         <v>1.36</v>
       </c>
-      <c r="AD18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT18" t="n">
+      <c r="BC18" t="n">
         <v>2.56</v>
       </c>
-      <c r="AU18" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.41</v>
-      </c>
       <c r="BD18" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.95</v>
+        <v>2.44</v>
       </c>
       <c r="Q19" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="R19" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BD19" t="n">
         <v>3.16</v>
       </c>
-      <c r="R19" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U19" t="n">
-        <v>5</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="X19" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>2.9</v>
-      </c>
       <c r="BE19" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.44</v>
+        <v>1.73</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.82</v>
+        <v>3.34</v>
       </c>
       <c r="R20" t="n">
-        <v>3.24</v>
+        <v>4.33</v>
       </c>
       <c r="S20" t="n">
-        <v>3.17</v>
+        <v>2.43</v>
       </c>
       <c r="T20" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="U20" t="n">
-        <v>4.26</v>
+        <v>5.68</v>
       </c>
       <c r="V20" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="W20" t="n">
-        <v>2.29</v>
+        <v>2.47</v>
       </c>
       <c r="X20" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="AA20" t="n">
         <v>1.01</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG20" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AI20" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.51</v>
+        <v>1.96</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4434,19 +4434,19 @@
         <v>1.62</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.19</v>
+        <v>4.22</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="AX20" t="n">
         <v>1.72</v>
@@ -4455,25 +4455,25 @@
         <v>1.42</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.61</v>
+        <v>1.12</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.6</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,28 +4544,28 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>2.91</v>
       </c>
       <c r="R21" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="S21" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="T21" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="U21" t="n">
-        <v>4.2</v>
+        <v>3.83</v>
       </c>
       <c r="V21" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W21" t="n">
-        <v>2.59</v>
+        <v>2.39</v>
       </c>
       <c r="X21" t="n">
         <v>3.04</v>
@@ -4574,19 +4574,19 @@
         <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA21" t="n">
         <v>1.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="AE21" t="n">
         <v>2.15</v>
@@ -4595,82 +4595,82 @@
         <v>1.66</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI21" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AJ21" t="n">
         <v>1.03</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="BB21" t="n">
         <v>1.27</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,28 +4741,28 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.91</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="T22" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="U22" t="n">
-        <v>3.83</v>
+        <v>4.2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W22" t="n">
-        <v>2.39</v>
+        <v>2.59</v>
       </c>
       <c r="X22" t="n">
         <v>3.04</v>
@@ -4771,19 +4771,19 @@
         <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AA22" t="n">
         <v>1.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="AE22" t="n">
         <v>2.15</v>
@@ -4792,82 +4792,82 @@
         <v>1.66</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.84</v>
+        <v>3.74</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI22" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AJ22" t="n">
         <v>1.03</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AN22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX22" t="n">
         <v>1.62</v>
       </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AY22" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="BB22" t="n">
         <v>1.27</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,28 +4938,28 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>5.5</v>
+        <v>4.16</v>
       </c>
       <c r="S23" t="n">
-        <v>2.15</v>
+        <v>2.55</v>
       </c>
       <c r="T23" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="U23" t="n">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="V23" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W23" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="X23" t="n">
         <v>2.99</v>
@@ -4968,100 +4968,100 @@
         <v>1.34</v>
       </c>
       <c r="Z23" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB23" t="n">
         <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AI23" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.03</v>
+        <v>1.86</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="AM23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN23" t="n">
+      <c r="AQ23" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BC23" t="n">
         <v>2.27</v>
       </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU23" t="n">
+      <c r="BD23" t="n">
         <v>3.5</v>
       </c>
-      <c r="AV23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>3.42</v>
-      </c>
       <c r="BE23" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BF23" t="n">
         <v>1.11</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,28 +5135,28 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="R24" t="n">
-        <v>4.16</v>
+        <v>5.5</v>
       </c>
       <c r="S24" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="T24" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="U24" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="V24" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W24" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="X24" t="n">
         <v>2.99</v>
@@ -5165,100 +5165,100 @@
         <v>1.34</v>
       </c>
       <c r="Z24" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB24" t="n">
         <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AF24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AL24" t="n">
         <v>1.7</v>
       </c>
-      <c r="AG24" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AM24" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.88</v>
+        <v>2.27</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.75</v>
+        <v>3.9</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BF24" t="n">
         <v>1.11</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2183,10 +2183,10 @@
         <v>2.37</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.54</v>
+        <v>3.25</v>
       </c>
       <c r="R9" t="n">
-        <v>2.74</v>
+        <v>3.13</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,40 +2377,40 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>2.6</v>
+        <v>3.92</v>
       </c>
       <c r="S10" t="n">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="T10" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="U10" t="n">
-        <v>3.2</v>
+        <v>3.78</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W10" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="X10" t="n">
-        <v>2.6</v>
+        <v>2.89</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AB10" t="n">
         <v>1.01</v>
@@ -2419,91 +2419,91 @@
         <v>1.28</v>
       </c>
       <c r="AD10" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG10" t="n">
         <v>3.3</v>
       </c>
-      <c r="AE10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF10" t="n">
+      <c r="AH10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR10" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK10" t="n">
+      <c r="AS10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AW10" t="n">
         <v>1.72</v>
       </c>
-      <c r="AL10" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AX10" t="n">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BB10" t="n">
         <v>1.22</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.81</v>
+        <v>2.55</v>
       </c>
       <c r="Q11" t="n">
         <v>3.3</v>
       </c>
       <c r="R11" t="n">
-        <v>4.2</v>
+        <v>2.6</v>
       </c>
       <c r="S11" t="n">
-        <v>2.57</v>
+        <v>3.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>4.45</v>
+        <v>3.2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W11" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="X11" t="n">
-        <v>3.02</v>
+        <v>2.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="Z11" t="n">
-        <v>7.3</v>
+        <v>6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR11" t="n">
         <v>1.74</v>
       </c>
-      <c r="AG11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH11" t="n">
+      <c r="AS11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.26</v>
-      </c>
       <c r="BC11" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF12" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AG12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AR13" t="n">
         <v>2.28</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q14" t="n">
         <v>3.5</v>
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R17" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="S17" t="n">
         <v>2.56</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BD18" t="n">
         <v>3.16</v>
       </c>
-      <c r="R18" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U18" t="n">
-        <v>5</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>2.9</v>
-      </c>
       <c r="BE18" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.44</v>
+        <v>1.76</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.82</v>
+        <v>3.34</v>
       </c>
       <c r="R19" t="n">
-        <v>3.24</v>
+        <v>4.87</v>
       </c>
       <c r="S19" t="n">
-        <v>3.17</v>
+        <v>2.43</v>
       </c>
       <c r="T19" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="U19" t="n">
-        <v>4.26</v>
+        <v>5.68</v>
       </c>
       <c r="V19" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="W19" t="n">
-        <v>2.29</v>
+        <v>2.47</v>
       </c>
       <c r="X19" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="AA19" t="n">
         <v>1.01</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AI19" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.51</v>
+        <v>1.96</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4237,19 +4237,19 @@
         <v>1.62</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.19</v>
+        <v>4.22</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="AX19" t="n">
         <v>1.72</v>
@@ -4258,25 +4258,25 @@
         <v>1.42</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.61</v>
+        <v>1.12</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.6</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.34</v>
+        <v>3.16</v>
       </c>
       <c r="R20" t="n">
-        <v>4.33</v>
+        <v>4.11</v>
       </c>
       <c r="S20" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="T20" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="U20" t="n">
-        <v>5.68</v>
+        <v>5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W20" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="X20" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY20" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z20" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC20" t="n">
+      <c r="AZ20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BB20" t="n">
         <v>1.36</v>
       </c>
-      <c r="AD20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT20" t="n">
+      <c r="BC20" t="n">
         <v>2.56</v>
       </c>
-      <c r="AU20" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.41</v>
-      </c>
       <c r="BD20" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="R21" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="S21" t="n">
         <v>2.75</v>
@@ -4592,7 +4592,7 @@
         <v>2.15</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AG21" t="n">
         <v>3.84</v>
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
-        <v>3.5</v>
+        <v>3.46</v>
       </c>
       <c r="S22" t="n">
         <v>2.73</v>
@@ -4786,10 +4786,10 @@
         <v>2.85</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AG22" t="n">
         <v>3.74</v>
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>4.16</v>
+        <v>4</v>
       </c>
       <c r="S23" t="n">
         <v>2.55</v>
@@ -4983,10 +4983,10 @@
         <v>2.99</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
         <v>3.54</v>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="R24" t="n">
-        <v>5.5</v>
+        <v>6.39</v>
       </c>
       <c r="S24" t="n">
         <v>2.15</v>
@@ -5180,10 +5180,10 @@
         <v>2.94</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
         <v>3.62</v>
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="R25" t="n">
-        <v>3.25</v>
+        <v>2.91</v>
       </c>
       <c r="S25" t="n">
         <v>3.26</v>
@@ -5377,10 +5377,10 @@
         <v>2.85</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG25" t="n">
         <v>3.9</v>
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.1</v>
+        <v>3.81</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="R26" t="n">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="S26" t="n">
         <v>4.78</v>
@@ -5574,7 +5574,7 @@
         <v>2.46</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="AF26" t="n">
         <v>1.53</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,112 +5726,112 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="R27" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="S27" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="T27" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U27" t="n">
-        <v>4.99</v>
+        <v>5.6</v>
       </c>
       <c r="V27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X27" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY27" t="n">
         <v>1.41</v>
-      </c>
-      <c r="W27" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.42</v>
       </c>
       <c r="AZ27" t="n">
         <v>1.36</v>
@@ -5840,19 +5840,19 @@
         <v>3.86</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R28" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X28" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN28" t="n">
         <v>1.88</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD28" t="n">
         <v>3.44</v>
       </c>
-      <c r="R28" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U28" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>3.22</v>
-      </c>
       <c r="BE28" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>4.98</v>
+        <v>4.2</v>
       </c>
       <c r="S29" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="T29" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="U29" t="n">
-        <v>5.6</v>
+        <v>4.85</v>
       </c>
       <c r="V29" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W29" t="n">
         <v>2.47</v>
       </c>
       <c r="X29" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="Y29" t="n">
         <v>1.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB29" t="n">
         <v>1.03</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.89</v>
+        <v>2.68</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG29" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AI29" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="AJ29" t="n">
         <v>1.02</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="BA29" t="n">
-        <v>3.86</v>
+        <v>2.8</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
         <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>3.92</v>
+        <v>4.54</v>
       </c>
       <c r="S10" t="n">
-        <v>2.86</v>
+        <v>2.57</v>
       </c>
       <c r="T10" t="n">
         <v>2.04</v>
       </c>
       <c r="U10" t="n">
-        <v>3.78</v>
+        <v>4.45</v>
       </c>
       <c r="V10" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W10" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="X10" t="n">
-        <v>2.89</v>
+        <v>3.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="AA10" t="n">
         <v>1.03</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="AG10" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AI10" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.97</v>
+        <v>1.82</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AN10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>1.62</v>
       </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ10" t="n">
+      <c r="BA10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE10" t="n">
         <v>1.58</v>
       </c>
-      <c r="AR10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.63</v>
-      </c>
       <c r="BF10" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,112 +2574,112 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="S11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>2.54</v>
+        <v>3.92</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="AF12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC12" t="n">
         <v>2.2</v>
       </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.8</v>
+        <v>2.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R13" t="n">
-        <v>4.54</v>
+        <v>2.6</v>
       </c>
       <c r="S13" t="n">
-        <v>2.57</v>
+        <v>3.2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U13" t="n">
-        <v>4.45</v>
+        <v>3.2</v>
       </c>
       <c r="V13" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="X13" t="n">
-        <v>3.02</v>
+        <v>2.6</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="Z13" t="n">
-        <v>7.3</v>
+        <v>6</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AF13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR13" t="n">
         <v>1.74</v>
       </c>
-      <c r="AG13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH13" t="n">
+      <c r="AS13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.26</v>
-      </c>
       <c r="BC13" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.82</v>
+        <v>3.16</v>
       </c>
       <c r="R18" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BD18" t="n">
         <v>2.9</v>
       </c>
-      <c r="S18" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U18" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>3.16</v>
-      </c>
       <c r="BE18" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BD20" t="n">
         <v>3.16</v>
       </c>
-      <c r="R20" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U20" t="n">
-        <v>5</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>2.9</v>
-      </c>
       <c r="BE20" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,28 +4544,28 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="R21" t="n">
-        <v>3.7</v>
+        <v>3.46</v>
       </c>
       <c r="S21" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="T21" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="U21" t="n">
-        <v>3.83</v>
+        <v>4.2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W21" t="n">
-        <v>2.39</v>
+        <v>2.59</v>
       </c>
       <c r="X21" t="n">
         <v>3.04</v>
@@ -4574,103 +4574,103 @@
         <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="n">
         <v>1.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.84</v>
+        <v>3.74</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI21" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AJ21" t="n">
         <v>1.03</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AN21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX21" t="n">
         <v>1.62</v>
       </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AY21" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="BB21" t="n">
         <v>1.27</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,28 +4741,28 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="R22" t="n">
-        <v>3.46</v>
+        <v>3.7</v>
       </c>
       <c r="S22" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="T22" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="U22" t="n">
-        <v>4.2</v>
+        <v>3.83</v>
       </c>
       <c r="V22" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W22" t="n">
-        <v>2.59</v>
+        <v>2.39</v>
       </c>
       <c r="X22" t="n">
         <v>3.04</v>
@@ -4771,103 +4771,103 @@
         <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA22" t="n">
         <v>1.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI22" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AJ22" t="n">
         <v>1.03</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="BB22" t="n">
         <v>1.27</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="S27" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="T27" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="U27" t="n">
-        <v>5.6</v>
+        <v>4.85</v>
       </c>
       <c r="V27" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W27" t="n">
         <v>2.47</v>
       </c>
       <c r="X27" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="Y27" t="n">
         <v>1.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB27" t="n">
         <v>1.03</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.89</v>
+        <v>2.68</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AI27" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="AJ27" t="n">
         <v>1.02</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AW27" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="BA27" t="n">
-        <v>3.86</v>
+        <v>2.8</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,112 +5923,112 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="R28" t="n">
-        <v>4.24</v>
+        <v>5</v>
       </c>
       <c r="S28" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="T28" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U28" t="n">
-        <v>4.99</v>
+        <v>5.6</v>
       </c>
       <c r="V28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY28" t="n">
         <v>1.41</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X28" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.42</v>
       </c>
       <c r="AZ28" t="n">
         <v>1.36</v>
@@ -6037,19 +6037,19 @@
         <v>3.86</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="R29" t="n">
-        <v>4.2</v>
+        <v>4.24</v>
       </c>
       <c r="S29" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="T29" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="U29" t="n">
-        <v>4.85</v>
+        <v>4.99</v>
       </c>
       <c r="V29" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W29" t="n">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="X29" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AG29" t="n">
-        <v>4.1</v>
+        <v>3.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AI29" t="n">
-        <v>9</v>
+        <v>6.25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="AL29" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AX29" t="n">
         <v>1.72</v>
       </c>
-      <c r="AM29" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AY29" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.8</v>
+        <v>3.86</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.22</v>
+        <v>3.44</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1986,76 +1986,76 @@
         <v>3.35</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
         <v>2.06</v>
       </c>
       <c r="S8" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="T8" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="U8" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="V8" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="W8" t="n">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="X8" t="n">
-        <v>3.79</v>
+        <v>3.44</v>
       </c>
       <c r="Y8" t="n">
         <v>1.24</v>
       </c>
       <c r="Z8" t="n">
-        <v>14.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.06</v>
+        <v>2.35</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AG8" t="n">
-        <v>6.48</v>
+        <v>4.83</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AI8" t="n">
-        <v>14.7</v>
+        <v>10</v>
       </c>
       <c r="AJ8" t="n">
         <v>1</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="AM8" t="n">
         <v>1.44</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>1.58</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.98</v>
+        <v>2.56</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.69</v>
+        <v>2.99</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.25</v>
+        <v>3.49</v>
       </c>
       <c r="R9" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q10" t="n">
         <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>4.54</v>
+        <v>5.25</v>
       </c>
       <c r="S10" t="n">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="T10" t="n">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="U10" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="V10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
         <v>1.44</v>
       </c>
-      <c r="W10" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="Y10" t="n">
+      <c r="AQ10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AX10" t="n">
         <v>1.33</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.32</v>
       </c>
       <c r="AY10" t="n">
         <v>1.19</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,112 +2574,112 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R11" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW11" t="n">
         <v>2.2</v>
       </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF12" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W12" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="X12" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AG12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BA13" t="n">
         <v>2.55</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
       <c r="BB13" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="Q14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R14" t="n">
         <v>3.5</v>
       </c>
-      <c r="R14" t="n">
-        <v>3.7</v>
-      </c>
       <c r="S14" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="T14" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="U14" t="n">
-        <v>4.45</v>
+        <v>4.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W14" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="X14" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AD14" t="n">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="AG14" t="n">
         <v>2.8</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>1.16</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="R18" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="T18" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q18" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="R18" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD18" t="n">
         <v>2.7</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U18" t="n">
-        <v>5</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC18" t="n">
+      <c r="AE18" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY18" t="n">
         <v>1.42</v>
       </c>
-      <c r="AD18" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>1.72</v>
+        <v>1.12</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.79</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.34</v>
+        <v>2.82</v>
       </c>
       <c r="R19" t="n">
-        <v>4.87</v>
+        <v>2.9</v>
       </c>
       <c r="S19" t="n">
-        <v>2.43</v>
+        <v>3.17</v>
       </c>
       <c r="T19" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="U19" t="n">
-        <v>5.68</v>
+        <v>4.26</v>
       </c>
       <c r="V19" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="W19" t="n">
-        <v>2.47</v>
+        <v>2.29</v>
       </c>
       <c r="X19" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.9</v>
+        <v>8</v>
       </c>
       <c r="AA19" t="n">
         <v>1.01</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AI19" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4237,19 +4237,19 @@
         <v>1.62</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.22</v>
+        <v>4.19</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="AX19" t="n">
         <v>1.72</v>
@@ -4258,25 +4258,25 @@
         <v>1.42</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.12</v>
+        <v>1.61</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.050000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.82</v>
+        <v>3.16</v>
       </c>
       <c r="R20" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BD20" t="n">
         <v>2.9</v>
       </c>
-      <c r="S20" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U20" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>3.16</v>
-      </c>
       <c r="BE20" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="R27" t="n">
-        <v>4.2</v>
+        <v>4.24</v>
       </c>
       <c r="S27" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="T27" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="U27" t="n">
-        <v>4.85</v>
+        <v>4.99</v>
       </c>
       <c r="V27" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W27" t="n">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="X27" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AG27" t="n">
-        <v>4.1</v>
+        <v>3.28</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AI27" t="n">
-        <v>9</v>
+        <v>6.25</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="AL27" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AX27" t="n">
         <v>1.72</v>
       </c>
-      <c r="AM27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AY27" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.56</v>
+        <v>1.36</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.8</v>
+        <v>3.86</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.22</v>
+        <v>3.44</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="S28" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="T28" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="U28" t="n">
-        <v>5.6</v>
+        <v>4.85</v>
       </c>
       <c r="V28" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W28" t="n">
         <v>2.47</v>
       </c>
       <c r="X28" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="Y28" t="n">
         <v>1.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB28" t="n">
         <v>1.03</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.89</v>
+        <v>2.68</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG28" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AI28" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="AJ28" t="n">
         <v>1.02</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AN28" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="BA28" t="n">
-        <v>3.86</v>
+        <v>2.8</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,112 +6120,112 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="R29" t="n">
-        <v>4.24</v>
+        <v>5</v>
       </c>
       <c r="S29" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="T29" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U29" t="n">
-        <v>4.99</v>
+        <v>5.6</v>
       </c>
       <c r="V29" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY29" t="n">
         <v>1.41</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X29" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.42</v>
       </c>
       <c r="AZ29" t="n">
         <v>1.36</v>
@@ -6234,19 +6234,19 @@
         <v>3.86</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1983,10 +1983,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="R8" t="n">
         <v>2.06</v>
@@ -2019,19 +2019,19 @@
         <v>1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AC8" t="n">
         <v>1.48</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.35</v>
+        <v>2.51</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AG8" t="n">
         <v>4.83</v>
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.83</v>
+        <v>2.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
-        <v>5.25</v>
+        <v>2.6</v>
       </c>
       <c r="S10" t="n">
-        <v>2.61</v>
+        <v>3.2</v>
       </c>
       <c r="T10" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="U10" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="V10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y10" t="n">
         <v>1.43</v>
       </c>
-      <c r="W10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X10" t="n">
+      <c r="Z10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG10" t="n">
         <v>3</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AH10" t="n">
         <v>1.32</v>
       </c>
-      <c r="Z10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AI10" t="n">
-        <v>9</v>
+        <v>5.7</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.03</v>
+        <v>1.72</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.77</v>
+        <v>1.31</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.75</v>
+        <v>1.74</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.05</v>
+        <v>1.95</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.95</v>
+        <v>2.48</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.48</v>
+        <v>4.39</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.93</v>
+        <v>2.95</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.33</v>
+        <v>1.76</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.19</v>
+        <v>1.45</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.41</v>
+        <v>2.18</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,112 +2574,112 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="S11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R12" t="n">
-        <v>2.54</v>
+        <v>4.02</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.65</v>
+        <v>2.22</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
         <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>4.02</v>
+        <v>5.25</v>
       </c>
       <c r="S13" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W13" t="n">
         <v>2.6</v>
       </c>
-      <c r="T13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.44</v>
-      </c>
       <c r="X13" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA13" t="n">
         <v>1.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.22</v>
+        <v>2.35</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AI13" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.94</v>
+        <v>2.75</v>
       </c>
       <c r="AS13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU13" t="n">
         <v>2.48</v>
       </c>
-      <c r="AT13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AV13" t="n">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.55</v>
+        <v>3.05</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.34</v>
+        <v>2.82</v>
       </c>
       <c r="R18" t="n">
-        <v>4.87</v>
+        <v>2.9</v>
       </c>
       <c r="S18" t="n">
-        <v>2.43</v>
+        <v>3.17</v>
       </c>
       <c r="T18" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="U18" t="n">
-        <v>5.68</v>
+        <v>4.26</v>
       </c>
       <c r="V18" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="W18" t="n">
-        <v>2.47</v>
+        <v>2.29</v>
       </c>
       <c r="X18" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z18" t="n">
-        <v>8.9</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
         <v>1.01</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG18" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AI18" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4040,19 +4040,19 @@
         <v>1.62</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="AU18" t="n">
-        <v>4.22</v>
+        <v>4.19</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="AX18" t="n">
         <v>1.72</v>
@@ -4061,25 +4061,25 @@
         <v>1.42</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.12</v>
+        <v>1.61</v>
       </c>
       <c r="BA18" t="n">
-        <v>9.050000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.82</v>
+        <v>3.34</v>
       </c>
       <c r="R19" t="n">
-        <v>2.9</v>
+        <v>4.87</v>
       </c>
       <c r="S19" t="n">
-        <v>3.17</v>
+        <v>2.43</v>
       </c>
       <c r="T19" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="U19" t="n">
-        <v>4.26</v>
+        <v>5.68</v>
       </c>
       <c r="V19" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="W19" t="n">
-        <v>2.29</v>
+        <v>2.47</v>
       </c>
       <c r="X19" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="AA19" t="n">
         <v>1.01</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG19" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AI19" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.51</v>
+        <v>1.96</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4237,19 +4237,19 @@
         <v>1.62</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.19</v>
+        <v>4.22</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="AX19" t="n">
         <v>1.72</v>
@@ -4258,25 +4258,25 @@
         <v>1.42</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.61</v>
+        <v>1.12</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.6</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,28 +4544,28 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R21" t="n">
-        <v>3.46</v>
+        <v>3.25</v>
       </c>
       <c r="S21" t="n">
-        <v>2.73</v>
+        <v>3.02</v>
       </c>
       <c r="T21" t="n">
-        <v>1.98</v>
+        <v>1.84</v>
       </c>
       <c r="U21" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="V21" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W21" t="n">
-        <v>2.59</v>
+        <v>2.39</v>
       </c>
       <c r="X21" t="n">
         <v>3.04</v>
@@ -4580,97 +4580,97 @@
         <v>1.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AD21" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BA21" t="n">
         <v>2.85</v>
       </c>
-      <c r="AE21" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>2.47</v>
-      </c>
       <c r="BB21" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,28 +4741,28 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="S22" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="T22" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="V22" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W22" t="n">
-        <v>2.39</v>
+        <v>2.59</v>
       </c>
       <c r="X22" t="n">
         <v>3.04</v>
@@ -4771,103 +4771,103 @@
         <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AA22" t="n">
         <v>1.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="AH22" t="n">
         <v>1.22</v>
       </c>
       <c r="AI22" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AJ22" t="n">
         <v>1.03</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.4</v>
+        <v>3.72</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.7</v>
+        <v>2.43</v>
       </c>
       <c r="BB22" t="n">
         <v>1.27</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,55 +4938,55 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.9</v>
+        <v>1.56</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="R23" t="n">
-        <v>4</v>
+        <v>6.39</v>
       </c>
       <c r="S23" t="n">
-        <v>2.55</v>
+        <v>2.15</v>
       </c>
       <c r="T23" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="U23" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="V23" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W23" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="X23" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB23" t="n">
         <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AD23" t="n">
         <v>2.99</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG23" t="n">
         <v>3.54</v>
@@ -4995,76 +4995,76 @@
         <v>1.22</v>
       </c>
       <c r="AI23" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.75</v>
+        <v>3.46</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="BC23" t="n">
         <v>2.27</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="BE23" t="n">
         <v>1.59</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,28 +5135,28 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="R24" t="n">
-        <v>6.39</v>
+        <v>4.2</v>
       </c>
       <c r="S24" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="U24" t="n">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
       <c r="V24" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W24" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="X24" t="n">
         <v>2.99</v>
@@ -5165,100 +5165,100 @@
         <v>1.34</v>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AK24" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AM24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN24" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AQ24" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="AT24" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BA24" t="n">
         <v>2.75</v>
       </c>
-      <c r="AU24" t="n">
+      <c r="BB24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD24" t="n">
         <v>3.5</v>
       </c>
-      <c r="AV24" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>3.42</v>
-      </c>
       <c r="BE24" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BF24" t="n">
         <v>1.11</v>
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.54</v>
+        <v>2.37</v>
       </c>
       <c r="Q25" t="n">
         <v>3.15</v>
@@ -5341,13 +5341,13 @@
         <v>2.91</v>
       </c>
       <c r="S25" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="T25" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="U25" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="V25" t="n">
         <v>1.46</v>
@@ -5356,13 +5356,13 @@
         <v>2.53</v>
       </c>
       <c r="X25" t="n">
-        <v>3.15</v>
+        <v>3.33</v>
       </c>
       <c r="Y25" t="n">
         <v>1.31</v>
       </c>
       <c r="Z25" t="n">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="AA25" t="n">
         <v>1.01</v>
@@ -5371,13 +5371,13 @@
         <v>1.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AD25" t="n">
         <v>2.85</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="AF25" t="n">
         <v>1.68</v>
@@ -5389,22 +5389,22 @@
         <v>1.18</v>
       </c>
       <c r="AI25" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
         <v>1.02</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AM25" t="n">
         <v>1.36</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5443,13 +5443,13 @@
         <v>1.88</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="BB25" t="n">
         <v>1.27</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="BD25" t="n">
         <v>3.4</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="R27" t="n">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="S27" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="T27" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="U27" t="n">
-        <v>4.99</v>
+        <v>4.5</v>
       </c>
       <c r="V27" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="W27" t="n">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="X27" t="n">
-        <v>2.85</v>
+        <v>3.22</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z27" t="n">
         <v>7</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AB27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>1.02</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AK27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
         <v>1.28</v>
       </c>
-      <c r="AD27" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AQ27" t="n">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AS27" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.57</v>
+        <v>3.07</v>
       </c>
       <c r="AU27" t="n">
-        <v>4.19</v>
+        <v>3.18</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.84</v>
+        <v>2.37</v>
       </c>
       <c r="AW27" t="n">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="BA27" t="n">
-        <v>3.86</v>
+        <v>2.97</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.44</v>
+        <v>3.22</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.9</v>
+        <v>1.67</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="R28" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="S28" t="n">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="T28" t="n">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="U28" t="n">
-        <v>4.85</v>
+        <v>5.6</v>
       </c>
       <c r="V28" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W28" t="n">
         <v>2.47</v>
       </c>
       <c r="X28" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="Y28" t="n">
         <v>1.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB28" t="n">
         <v>1.03</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.68</v>
+        <v>2.89</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG28" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AI28" t="n">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="AJ28" t="n">
         <v>1.02</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.85</v>
+        <v>2.11</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="BB28" t="n">
         <v>1.28</v>
       </c>
-      <c r="AQ28" t="n">
+      <c r="BC28" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BE28" t="n">
         <v>1.5</v>
       </c>
-      <c r="AR28" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>1.49</v>
-      </c>
       <c r="BF28" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,112 +6120,112 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="R29" t="n">
-        <v>5</v>
+        <v>4.24</v>
       </c>
       <c r="S29" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="T29" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="U29" t="n">
-        <v>5.6</v>
+        <v>4.99</v>
       </c>
       <c r="V29" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="W29" t="n">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="X29" t="n">
-        <v>3.16</v>
+        <v>2.85</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z29" t="n">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="AA29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB29" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB29" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AC29" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.89</v>
+        <v>3.05</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AG29" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AI29" t="n">
-        <v>7.9</v>
+        <v>6.25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.11</v>
+        <v>1.88</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AQ29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY29" t="n">
         <v>1.42</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.41</v>
       </c>
       <c r="AZ29" t="n">
         <v>1.36</v>
@@ -6234,19 +6234,19 @@
         <v>3.86</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2377,40 +2377,40 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
         <v>3.3</v>
       </c>
       <c r="R10" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="S10" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="U10" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="V10" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="X10" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AB10" t="n">
         <v>1.01</v>
@@ -2419,37 +2419,37 @@
         <v>1.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AE10" t="n">
         <v>1.85</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AG10" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AI10" t="n">
-        <v>5.7</v>
+        <v>6.45</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BC10" t="n">
         <v>2.18</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.28</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>2.54</v>
+        <v>5.25</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.65</v>
+        <v>2.35</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>2.28</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>5.25</v>
+        <v>2.54</v>
       </c>
       <c r="S13" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3756,43 +3756,43 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="R17" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T17" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="U17" t="n">
-        <v>4.78</v>
+        <v>4.66</v>
       </c>
       <c r="V17" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="X17" t="n">
         <v>2.99</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC17" t="n">
         <v>1.33</v>
@@ -3807,28 +3807,28 @@
         <v>1.66</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="AH17" t="n">
         <v>1.21</v>
       </c>
       <c r="AI17" t="n">
-        <v>6.9</v>
+        <v>7.5</v>
       </c>
       <c r="AJ17" t="n">
         <v>1.04</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AM17" t="n">
         <v>1.3</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3837,13 +3837,13 @@
         <v>1.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.64</v>
+        <v>1.96</v>
       </c>
       <c r="AS17" t="n">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AT17" t="n">
         <v>2.88</v>
@@ -3852,37 +3852,37 @@
         <v>3.65</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AW17" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="AY17" t="n">
         <v>1.33</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BA17" t="n">
         <v>2.9</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.82</v>
+        <v>3.16</v>
       </c>
       <c r="R18" t="n">
-        <v>2.9</v>
+        <v>4.11</v>
       </c>
       <c r="S18" t="n">
-        <v>3.17</v>
+        <v>2.49</v>
       </c>
       <c r="T18" t="n">
-        <v>1.82</v>
+        <v>2.04</v>
       </c>
       <c r="U18" t="n">
-        <v>4.26</v>
+        <v>5.1</v>
       </c>
       <c r="V18" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W18" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="X18" t="n">
-        <v>3.29</v>
+        <v>3.42</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AB18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BF18" t="n">
         <v>1.06</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.09</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.76</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.34</v>
+        <v>2.95</v>
       </c>
       <c r="R19" t="n">
-        <v>4.87</v>
+        <v>2.94</v>
       </c>
       <c r="S19" t="n">
-        <v>2.43</v>
+        <v>2.87</v>
       </c>
       <c r="T19" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="U19" t="n">
-        <v>5.68</v>
+        <v>4.13</v>
       </c>
       <c r="V19" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W19" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="X19" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="Y19" t="n">
         <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="AA19" t="n">
         <v>1.01</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.15</v>
+        <v>3.92</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AI19" t="n">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.96</v>
+        <v>1.52</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4234,49 +4234,49 @@
         <v>1.34</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.22</v>
+        <v>4.16</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AY19" t="n">
         <v>1.42</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.12</v>
+        <v>1.62</v>
       </c>
       <c r="BA19" t="n">
-        <v>9.050000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
-        <v>4.11</v>
+        <v>4.49</v>
       </c>
       <c r="S20" t="n">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="T20" t="n">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="U20" t="n">
-        <v>5</v>
+        <v>5.41</v>
       </c>
       <c r="V20" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="W20" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="X20" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA20" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="AG20" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AI20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AN20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR20" t="n">
         <v>1.76</v>
       </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AS20" t="n">
-        <v>2.26</v>
+        <v>1.97</v>
       </c>
       <c r="AT20" t="n">
-        <v>3</v>
+        <v>2.51</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.05</v>
+        <v>4.31</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.28</v>
+        <v>2.91</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.72</v>
+        <v>1.37</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.79</v>
+        <v>3.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.9</v>
+        <v>3.22</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,28 +4544,28 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R21" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="S21" t="n">
-        <v>3.02</v>
+        <v>2.73</v>
       </c>
       <c r="T21" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="V21" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W21" t="n">
-        <v>2.39</v>
+        <v>2.59</v>
       </c>
       <c r="X21" t="n">
         <v>3.04</v>
@@ -4574,103 +4574,103 @@
         <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA21" t="n">
         <v>1.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.94</v>
+        <v>2.85</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.54</v>
+        <v>4.2</v>
       </c>
       <c r="AH21" t="n">
         <v>1.22</v>
       </c>
       <c r="AI21" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AS21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC21" t="n">
         <v>2.35</v>
       </c>
-      <c r="AT21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX21" t="n">
+      <c r="BD21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE21" t="n">
         <v>1.53</v>
       </c>
-      <c r="AY21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BF21" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,28 +4741,28 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R22" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="S22" t="n">
-        <v>2.73</v>
+        <v>3.02</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="U22" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="V22" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W22" t="n">
-        <v>2.59</v>
+        <v>2.39</v>
       </c>
       <c r="X22" t="n">
         <v>3.04</v>
@@ -4771,103 +4771,103 @@
         <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA22" t="n">
         <v>1.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AG22" t="n">
-        <v>4.2</v>
+        <v>3.54</v>
       </c>
       <c r="AH22" t="n">
         <v>1.22</v>
       </c>
       <c r="AI22" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.43</v>
+        <v>2.85</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5529,19 +5529,19 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>4.78</v>
+        <v>4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
         <v>2.77</v>
@@ -5553,7 +5553,7 @@
         <v>2.32</v>
       </c>
       <c r="X26" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Y26" t="n">
         <v>1.27</v>
@@ -5565,28 +5565,28 @@
         <v>1.01</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AD26" t="n">
         <v>2.46</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG26" t="n">
-        <v>4.35</v>
+        <v>4.75</v>
       </c>
       <c r="AH26" t="n">
         <v>1.14</v>
       </c>
       <c r="AI26" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AJ26" t="n">
         <v>1.01</v>
@@ -5595,7 +5595,7 @@
         <v>2.06</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AM26" t="n">
         <v>1.33</v>
@@ -5607,55 +5607,55 @@
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AQ26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="BE26" t="n">
         <v>1.44</v>
       </c>
-      <c r="AR26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>1.5</v>
-      </c>
       <c r="BF26" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="S27" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="T27" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="U27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="V27" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W27" t="n">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="X27" t="n">
-        <v>3.22</v>
+        <v>2.85</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AC27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AY27" t="n">
         <v>1.37</v>
       </c>
-      <c r="AD27" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AZ27" t="n">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.22</v>
+        <v>3.44</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="R28" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="S28" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="U28" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="V28" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W28" t="n">
         <v>2.47</v>
       </c>
       <c r="X28" t="n">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="Y28" t="n">
         <v>1.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.89</v>
+        <v>2.68</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG28" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AI28" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ28" t="n">
         <v>1.02</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AN28" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.65</v>
+        <v>3.07</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.55</v>
+        <v>3.18</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="BA28" t="n">
-        <v>3.86</v>
+        <v>2.97</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,79 +6120,79 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>4.24</v>
+        <v>5</v>
       </c>
       <c r="S29" t="n">
-        <v>2.41</v>
+        <v>2.29</v>
       </c>
       <c r="T29" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="U29" t="n">
-        <v>4.99</v>
+        <v>6.26</v>
       </c>
       <c r="V29" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="W29" t="n">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="X29" t="n">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC29" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z29" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB29" t="n">
+      <c r="AD29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ29" t="n">
         <v>1.02</v>
       </c>
-      <c r="AC29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AK29" t="n">
-        <v>1.84</v>
+        <v>2.11</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6210,13 +6210,13 @@
         <v>2</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="AU29" t="n">
-        <v>4.19</v>
+        <v>4.22</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="AW29" t="n">
         <v>2.14</v>
@@ -6228,25 +6228,25 @@
         <v>1.42</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="BA29" t="n">
-        <v>3.86</v>
+        <v>5.63</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1986,7 +1986,7 @@
         <v>3.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
         <v>2.06</v>
@@ -2025,7 +2025,7 @@
         <v>1.48</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AE8" t="n">
         <v>2.51</v>
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="R9" t="n">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="R11" t="n">
-        <v>5.25</v>
+        <v>3.6</v>
       </c>
       <c r="S11" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="T11" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="U11" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="V11" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W11" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AA11" t="n">
         <v>1.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AD11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BA11" t="n">
         <v>2.7</v>
       </c>
-      <c r="AE11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AF11" t="n">
+      <c r="BB11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.57</v>
       </c>
-      <c r="AG11" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.5</v>
-      </c>
       <c r="BF11" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R12" t="n">
-        <v>4.02</v>
+        <v>2.54</v>
       </c>
       <c r="S12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.22</v>
+        <v>1.65</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.28</v>
+        <v>1.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R13" t="n">
-        <v>2.54</v>
+        <v>4.1</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3165,37 +3165,37 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="S14" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="T14" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="U14" t="n">
-        <v>4.3</v>
+        <v>3.82</v>
       </c>
       <c r="V14" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W14" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="X14" t="n">
         <v>2.45</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Z14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AA14" t="n">
         <v>1.08</v>
@@ -3204,94 +3204,94 @@
         <v>1.04</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AI14" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="AM14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
         <v>1.28</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.27</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.49</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AS14" t="n">
         <v>2.23</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AV14" t="n">
         <v>2.38</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AX14" t="n">
         <v>1.56</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="R18" t="n">
-        <v>4.11</v>
+        <v>4.49</v>
       </c>
       <c r="S18" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="T18" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="U18" t="n">
-        <v>5.1</v>
+        <v>5.41</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W18" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="X18" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AB18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BF18" t="n">
         <v>1.07</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.06</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.95</v>
+        <v>3.16</v>
       </c>
       <c r="R19" t="n">
-        <v>2.94</v>
+        <v>4.11</v>
       </c>
       <c r="S19" t="n">
-        <v>2.87</v>
+        <v>2.49</v>
       </c>
       <c r="T19" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="U19" t="n">
-        <v>4.13</v>
+        <v>5.1</v>
       </c>
       <c r="V19" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
         <v>2.34</v>
       </c>
       <c r="X19" t="n">
-        <v>3.16</v>
+        <v>3.42</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z19" t="n">
         <v>9</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.92</v>
+        <v>4.75</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AI19" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.52</v>
+        <v>1.76</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.01</v>
+        <v>2.26</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.16</v>
+        <v>3.48</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.83</v>
+        <v>2.46</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AZ19" t="n">
         <v>1.62</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.6</v>
+        <v>3.06</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.22</v>
+        <v>2.99</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="R20" t="n">
-        <v>4.49</v>
+        <v>2.94</v>
       </c>
       <c r="S20" t="n">
-        <v>2.47</v>
+        <v>2.87</v>
       </c>
       <c r="T20" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="U20" t="n">
-        <v>5.41</v>
+        <v>4.13</v>
       </c>
       <c r="V20" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W20" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="X20" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA20" t="n">
         <v>1.01</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AD20" t="n">
         <v>2.69</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AG20" t="n">
-        <v>4.33</v>
+        <v>3.92</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AI20" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK20" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.51</v>
+        <v>2.58</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.31</v>
+        <v>4.16</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="BA20" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="BB20" t="n">
         <v>1.29</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="BD20" t="n">
         <v>3.22</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,28 +4544,28 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="R21" t="n">
-        <v>3.28</v>
+        <v>3.7</v>
       </c>
       <c r="S21" t="n">
-        <v>2.73</v>
+        <v>3.02</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="U21" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="V21" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="W21" t="n">
-        <v>2.59</v>
+        <v>2.39</v>
       </c>
       <c r="X21" t="n">
         <v>3.04</v>
@@ -4574,103 +4574,103 @@
         <v>1.33</v>
       </c>
       <c r="Z21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="n">
         <v>1.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG21" t="n">
-        <v>4.2</v>
+        <v>3.54</v>
       </c>
       <c r="AH21" t="n">
         <v>1.22</v>
       </c>
       <c r="AI21" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.43</v>
+        <v>2.85</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="S22" t="n">
-        <v>3.02</v>
+        <v>2.68</v>
       </c>
       <c r="T22" t="n">
-        <v>1.84</v>
+        <v>2.11</v>
       </c>
       <c r="U22" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="V22" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="W22" t="n">
-        <v>2.39</v>
+        <v>2.77</v>
       </c>
       <c r="X22" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AD22" t="n">
         <v>2.94</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.54</v>
+        <v>3.85</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AI22" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.35</v>
+        <v>3.72</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.85</v>
+        <v>2.49</v>
       </c>
       <c r="BB22" t="n">
         <v>1.25</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="BD22" t="n">
         <v>3.42</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,130 +4938,130 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>6.39</v>
+        <v>4.2</v>
       </c>
       <c r="S23" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="T23" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="U23" t="n">
-        <v>5.5</v>
+        <v>4.95</v>
       </c>
       <c r="V23" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W23" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="X23" t="n">
-        <v>2.94</v>
+        <v>3.11</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AA23" t="n">
         <v>1.03</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.99</v>
+        <v>3.18</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.54</v>
+        <v>3.65</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AI23" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BB23" t="n">
         <v>1.25</v>
       </c>
-      <c r="AQ23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC23" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.42</v>
+        <v>3.66</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="BF23" t="n">
         <v>1.12</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.77</v>
+        <v>1.56</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R24" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="T24" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="U24" t="n">
-        <v>4.7</v>
+        <v>6.1</v>
       </c>
       <c r="V24" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W24" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="X24" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z24" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AD24" t="n">
         <v>2.99</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.75</v>
+        <v>3.54</v>
       </c>
       <c r="AH24" t="n">
         <v>1.22</v>
       </c>
       <c r="AI24" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.75</v>
+        <v>3.46</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="BE24" t="n">
         <v>1.59</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5332,10 +5332,10 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R25" t="n">
         <v>2.91</v>
@@ -5347,7 +5347,7 @@
         <v>2.05</v>
       </c>
       <c r="U25" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="V25" t="n">
         <v>1.46</v>
@@ -5356,10 +5356,10 @@
         <v>2.53</v>
       </c>
       <c r="X25" t="n">
-        <v>3.33</v>
+        <v>3.15</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
         <v>8.4</v>
@@ -5419,7 +5419,7 @@
         <v>1.68</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AT25" t="n">
         <v>2.65</v>
@@ -5431,7 +5431,7 @@
         <v>2.65</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="AX25" t="n">
         <v>1.66</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R28" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="S28" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="T28" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U28" t="n">
-        <v>4.5</v>
+        <v>6.26</v>
       </c>
       <c r="V28" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W28" t="n">
         <v>2.47</v>
       </c>
       <c r="X28" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AG28" t="n">
-        <v>4.1</v>
+        <v>3.94</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AI28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AJ28" t="n">
         <v>1.02</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="AL28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AX28" t="n">
         <v>1.72</v>
       </c>
-      <c r="AM28" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AY28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="BB28" t="n">
         <v>1.33</v>
       </c>
-      <c r="AZ28" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BC28" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="S29" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="T29" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="U29" t="n">
-        <v>6.26</v>
+        <v>4.5</v>
       </c>
       <c r="V29" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W29" t="n">
         <v>2.47</v>
       </c>
       <c r="X29" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.94</v>
+        <v>4.1</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AI29" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ29" t="n">
         <v>1.02</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="AS29" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.56</v>
+        <v>3.07</v>
       </c>
       <c r="AU29" t="n">
-        <v>4.22</v>
+        <v>3.18</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.86</v>
+        <v>2.37</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.63</v>
+        <v>2.8</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="BD29" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI29"/>
+  <dimension ref="A1:BI32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1930,27 +1930,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.77</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2118,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="BI8" s="3" t="n">
-        <v>46113.5625</v>
+        <v>46113.45833333334</v>
       </c>
     </row>
     <row r="9">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,112 +2180,112 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
+        <v>5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U9" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE9" t="n">
         <v>3</v>
       </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="BI9" s="3" t="n">
-        <v>46113.58333333334</v>
+        <v>46113.5</v>
       </c>
     </row>
     <row r="10">
@@ -2324,27 +2324,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>2.55</v>
+        <v>6.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="T10" t="n">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="U10" t="n">
-        <v>3.32</v>
+        <v>8.15</v>
       </c>
       <c r="V10" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="W10" t="n">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="X10" t="n">
-        <v>2.82</v>
+        <v>3.42</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AA10" t="n">
         <v>1.03</v>
       </c>
       <c r="AB10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.01</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AK10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX10" t="n">
         <v>1.28</v>
       </c>
-      <c r="AD10" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AQ10" t="n">
+      <c r="AY10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="BB10" t="n">
         <v>1.31</v>
       </c>
-      <c r="AR10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW10" t="n">
+      <c r="BC10" t="n">
         <v>2.2</v>
       </c>
-      <c r="AX10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.18</v>
-      </c>
       <c r="BD10" t="n">
-        <v>3.75</v>
+        <v>3.02</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="BI10" s="3" t="n">
-        <v>46113.625</v>
+        <v>46113.5</v>
       </c>
     </row>
     <row r="11">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>3.6</v>
+        <v>2.06</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>4.27</v>
       </c>
       <c r="T11" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="U11" t="n">
-        <v>4.8</v>
+        <v>2.91</v>
       </c>
       <c r="V11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC11" t="n">
         <v>1.48</v>
       </c>
-      <c r="W11" t="n">
+      <c r="AD11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="AU11" t="n">
         <v>2.65</v>
       </c>
-      <c r="X11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ11" t="n">
+      <c r="AV11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BA11" t="n">
         <v>1.58</v>
       </c>
-      <c r="AR11" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>2.7</v>
-      </c>
       <c r="BB11" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.31</v>
+        <v>2.56</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.34</v>
+        <v>2.99</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>46113.625</v>
+        <v>46113.5625</v>
       </c>
     </row>
     <row r="12">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="R12" t="n">
-        <v>2.54</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46113.625</v>
+        <v>46113.58333333334</v>
       </c>
     </row>
     <row r="13">
@@ -3112,27 +3112,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
         <v>3.3</v>
       </c>
       <c r="R14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG14" t="n">
         <v>3.2</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC14" t="n">
+      <c r="AH14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
         <v>1.19</v>
       </c>
-      <c r="AD14" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BC14" t="n">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.82</v>
+        <v>1.64</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>46113.6875</v>
+        <v>46113.625</v>
       </c>
     </row>
     <row r="15">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46113.72916666666</v>
+        <v>46113.625</v>
       </c>
     </row>
     <row r="16">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46113.72916666666</v>
+        <v>46113.625</v>
       </c>
     </row>
     <row r="17">
@@ -3703,27 +3703,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="S17" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>2.01</v>
+        <v>2.16</v>
       </c>
       <c r="U17" t="n">
-        <v>4.66</v>
+        <v>3.82</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W17" t="n">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="X17" t="n">
-        <v>2.99</v>
+        <v>2.45</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.5</v>
+        <v>5.6</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB17" t="n">
         <v>1.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.83</v>
+        <v>3.76</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.15</v>
+        <v>1.76</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.66</v>
+        <v>2.09</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.58</v>
+        <v>2.64</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.21</v>
+        <v>1.38</v>
       </c>
       <c r="AI17" t="n">
-        <v>7.5</v>
+        <v>4.75</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.83</v>
+        <v>2.19</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AY17" t="n">
         <v>1.33</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.54</v>
+        <v>1.82</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>46113.75</v>
+        <v>46113.6875</v>
       </c>
     </row>
     <row r="18">
@@ -3900,27 +3900,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46113.79166666666</v>
+        <v>46113.72916666666</v>
       </c>
     </row>
     <row r="19">
@@ -4097,27 +4097,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46113.79166666666</v>
+        <v>46113.72916666666</v>
       </c>
     </row>
     <row r="20">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.95</v>
+        <v>3.26</v>
       </c>
       <c r="R20" t="n">
-        <v>2.94</v>
+        <v>4.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.87</v>
+        <v>2.58</v>
       </c>
       <c r="T20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK20" t="n">
         <v>1.85</v>
       </c>
-      <c r="U20" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="Y20" t="n">
+      <c r="AL20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM20" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AN20" t="n">
-        <v>1.52</v>
+        <v>1.76</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.01</v>
+        <v>2.19</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.58</v>
+        <v>2.88</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.16</v>
+        <v>3.65</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.83</v>
+        <v>2.55</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AZ20" t="n">
         <v>1.62</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46113.79166666666</v>
+        <v>46113.75</v>
       </c>
     </row>
     <row r="21">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="R21" t="n">
-        <v>3.7</v>
+        <v>2.94</v>
       </c>
       <c r="S21" t="n">
-        <v>3.02</v>
+        <v>2.87</v>
       </c>
       <c r="T21" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="U21" t="n">
-        <v>4.33</v>
+        <v>4.13</v>
       </c>
       <c r="V21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BE21" t="n">
         <v>1.51</v>
       </c>
-      <c r="W21" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.6</v>
-      </c>
       <c r="BF21" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46113.8125</v>
+        <v>46113.79166666666</v>
       </c>
     </row>
     <row r="22">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R22" t="n">
-        <v>3.3</v>
+        <v>4.49</v>
       </c>
       <c r="S22" t="n">
-        <v>2.68</v>
+        <v>2.47</v>
       </c>
       <c r="T22" t="n">
-        <v>2.11</v>
+        <v>1.96</v>
       </c>
       <c r="U22" t="n">
-        <v>4</v>
+        <v>5.41</v>
       </c>
       <c r="V22" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="W22" t="n">
-        <v>2.77</v>
+        <v>2.47</v>
       </c>
       <c r="X22" t="n">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="Z22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB22" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AC22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>1.01</v>
       </c>
-      <c r="AC22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AK22" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.71</v>
+        <v>1.92</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.83</v>
+        <v>2.51</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.72</v>
+        <v>4.31</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.55</v>
+        <v>2.91</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.71</v>
+        <v>1.37</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.49</v>
+        <v>3.5</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46113.8125</v>
+        <v>46113.79166666666</v>
       </c>
     </row>
     <row r="23">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="R23" t="n">
-        <v>4.2</v>
+        <v>4.11</v>
       </c>
       <c r="S23" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE23" t="n">
         <v>2.38</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U23" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA23" t="n">
+      <c r="AF23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AK23" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AM23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY23" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AY23" t="n">
+      <c r="AZ23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="BB23" t="n">
         <v>1.33</v>
       </c>
-      <c r="AZ23" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC23" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.66</v>
+        <v>2.99</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46113.83333333334</v>
+        <v>46113.79166666666</v>
       </c>
     </row>
     <row r="24">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,55 +5135,55 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.56</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="R24" t="n">
-        <v>5.3</v>
+        <v>3.7</v>
       </c>
       <c r="S24" t="n">
-        <v>2.12</v>
+        <v>3.02</v>
       </c>
       <c r="T24" t="n">
-        <v>2.13</v>
+        <v>1.84</v>
       </c>
       <c r="U24" t="n">
-        <v>6.1</v>
+        <v>4.33</v>
       </c>
       <c r="V24" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="W24" t="n">
-        <v>2.69</v>
+        <v>2.39</v>
       </c>
       <c r="X24" t="n">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC24" t="n">
         <v>1.35</v>
       </c>
-      <c r="Z24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AD24" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AG24" t="n">
         <v>3.54</v>
@@ -5192,73 +5192,73 @@
         <v>1.22</v>
       </c>
       <c r="AI24" t="n">
-        <v>6.9</v>
+        <v>8.5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.06</v>
+        <v>1.81</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.38</v>
+        <v>1.61</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BB24" t="n">
         <v>1.25</v>
       </c>
-      <c r="AQ24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC24" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="BD24" t="n">
         <v>3.42</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="BF24" t="n">
         <v>1.12</v>
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46113.83333333334</v>
+        <v>46113.8125</v>
       </c>
     </row>
     <row r="25">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.55</v>
+        <v>2.04</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>2.91</v>
+        <v>3.3</v>
       </c>
       <c r="S25" t="n">
-        <v>3.1</v>
+        <v>2.68</v>
       </c>
       <c r="T25" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="U25" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="V25" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="W25" t="n">
-        <v>2.53</v>
+        <v>2.77</v>
       </c>
       <c r="X25" t="n">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z25" t="n">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AA25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB25" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AC25" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.85</v>
+        <v>2.94</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AI25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.32</v>
+        <v>2.49</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46113.85416666666</v>
+        <v>46113.8125</v>
       </c>
     </row>
     <row r="26">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q26" t="n">
         <v>3.8</v>
       </c>
-      <c r="Q26" t="n">
-        <v>3.2</v>
-      </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>2.12</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="U26" t="n">
-        <v>2.77</v>
+        <v>6.1</v>
       </c>
       <c r="V26" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="W26" t="n">
-        <v>2.32</v>
+        <v>2.69</v>
       </c>
       <c r="X26" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="AA26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB26" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AC26" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.46</v>
+        <v>2.99</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.52</v>
+        <v>1.78</v>
       </c>
       <c r="AG26" t="n">
-        <v>4.75</v>
+        <v>3.54</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AI26" t="n">
-        <v>8.6</v>
+        <v>6.9</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AK26" t="n">
         <v>2.06</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.24</v>
+        <v>2.38</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AS26" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC26" t="n">
         <v>2.27</v>
       </c>
-      <c r="AT26" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2.6</v>
-      </c>
       <c r="BD26" t="n">
-        <v>2.99</v>
+        <v>3.42</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46113.875</v>
+        <v>46113.83333333334</v>
       </c>
     </row>
     <row r="27">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="Q27" t="n">
         <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="S27" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="T27" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="U27" t="n">
-        <v>4.6</v>
+        <v>4.95</v>
       </c>
       <c r="V27" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W27" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="X27" t="n">
-        <v>2.85</v>
+        <v>3.11</v>
       </c>
       <c r="Y27" t="n">
         <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.04</v>
+        <v>3.18</v>
       </c>
       <c r="AE27" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW27" t="n">
         <v>2.01</v>
       </c>
-      <c r="AF27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AH27" t="n">
+      <c r="AX27" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BB27" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI27" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.24</v>
-      </c>
       <c r="BC27" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.44</v>
+        <v>3.66</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46113.89583333334</v>
+        <v>46113.83333333334</v>
       </c>
     </row>
     <row r="28">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,130 +5923,130 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.66</v>
+        <v>2.55</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>5</v>
+        <v>2.91</v>
       </c>
       <c r="S28" t="n">
-        <v>2.29</v>
+        <v>3.1</v>
       </c>
       <c r="T28" t="n">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="U28" t="n">
-        <v>6.26</v>
+        <v>3.3</v>
       </c>
       <c r="V28" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W28" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="X28" t="n">
         <v>3.15</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI28" t="n">
         <v>8</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>8.5</v>
       </c>
       <c r="AJ28" t="n">
         <v>1.02</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AM28" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BB28" t="n">
         <v>1.27</v>
       </c>
-      <c r="AN28" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BC28" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="BD28" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BF28" t="n">
         <v>1.09</v>
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46113.89583333334</v>
+        <v>46113.85416666666</v>
       </c>
     </row>
     <row r="29">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,141 +6120,732 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.85</v>
+        <v>3.8</v>
       </c>
       <c r="Q29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="X29" t="n">
         <v>3.3</v>
       </c>
-      <c r="R29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U29" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.22</v>
-      </c>
       <c r="Y29" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z29" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="AA29" t="n">
         <v>1.01</v>
       </c>
       <c r="AB29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI29" s="3" t="n">
+        <v>46113.875</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.09</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AC30" t="n">
         <v>1.37</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AD30" t="n">
         <v>2.82</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AE30" t="n">
         <v>2.35</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AF30" t="n">
         <v>1.57</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AG30" t="n">
         <v>4.1</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AH30" t="n">
         <v>1.16</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AI30" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AJ30" t="n">
         <v>1.02</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AK30" t="n">
         <v>2.23</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="AL30" t="n">
         <v>1.72</v>
       </c>
-      <c r="AM29" t="n">
+      <c r="AM30" t="n">
         <v>1.34</v>
       </c>
-      <c r="AN29" t="n">
+      <c r="AN30" t="n">
         <v>1.85</v>
       </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
         <v>1.28</v>
       </c>
-      <c r="AQ29" t="n">
+      <c r="AQ30" t="n">
         <v>1.52</v>
       </c>
-      <c r="AR29" t="n">
+      <c r="AR30" t="n">
         <v>2.1</v>
       </c>
-      <c r="AS29" t="n">
+      <c r="AS30" t="n">
         <v>2.35</v>
       </c>
-      <c r="AT29" t="n">
+      <c r="AT30" t="n">
         <v>3.07</v>
       </c>
-      <c r="AU29" t="n">
+      <c r="AU30" t="n">
         <v>3.18</v>
       </c>
-      <c r="AV29" t="n">
+      <c r="AV30" t="n">
         <v>2.37</v>
       </c>
-      <c r="AW29" t="n">
+      <c r="AW30" t="n">
         <v>1.87</v>
       </c>
-      <c r="AX29" t="n">
+      <c r="AX30" t="n">
         <v>1.53</v>
       </c>
-      <c r="AY29" t="n">
+      <c r="AY30" t="n">
         <v>1.33</v>
       </c>
-      <c r="AZ29" t="n">
+      <c r="AZ30" t="n">
         <v>1.56</v>
       </c>
-      <c r="BA29" t="n">
+      <c r="BA30" t="n">
         <v>2.8</v>
       </c>
-      <c r="BB29" t="n">
+      <c r="BB30" t="n">
         <v>1.3</v>
       </c>
-      <c r="BC29" t="n">
+      <c r="BC30" t="n">
         <v>2.44</v>
       </c>
-      <c r="BD29" t="n">
+      <c r="BD30" t="n">
         <v>3.22</v>
       </c>
-      <c r="BE29" t="n">
+      <c r="BE30" t="n">
         <v>1.49</v>
       </c>
-      <c r="BF29" t="n">
+      <c r="BF30" t="n">
         <v>1.08</v>
       </c>
-      <c r="BG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI29" s="3" t="n">
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI30" s="3" t="n">
+        <v>46113.89583333334</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Avaí</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R31" t="n">
+        <v>4</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI31" s="3" t="n">
+        <v>46113.89583333334</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R32" t="n">
+        <v>5</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U32" t="n">
+        <v>6.26</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>3</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI32" s="3" t="n">
         <v>46113.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R9" t="n">
-        <v>5</v>
+        <v>6.25</v>
       </c>
       <c r="S9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U9" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X9" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK9" t="n">
         <v>2.45</v>
       </c>
-      <c r="T9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U9" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="X9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.78</v>
-      </c>
       <c r="AL9" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AR9" t="n">
-        <v>3</v>
+        <v>2.79</v>
       </c>
       <c r="AS9" t="n">
-        <v>3.34</v>
+        <v>3.11</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.97</v>
+        <v>4.54</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.37</v>
+        <v>2.51</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>7.39</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="BC9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD9" t="n">
         <v>3.02</v>
       </c>
-      <c r="BD9" t="n">
-        <v>2.53</v>
-      </c>
       <c r="BE9" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U10" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AG10" t="n">
         <v>6.25</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U10" t="n">
-        <v>8.15</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="X10" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AA10" t="n">
+      <c r="AH10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AK10" t="n">
-        <v>2.45</v>
+        <v>2.78</v>
       </c>
       <c r="AL10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AW10" t="n">
         <v>1.48</v>
       </c>
-      <c r="AM10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AX10" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.39</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BE10" t="n">
         <v>1.31</v>
       </c>
-      <c r="BC10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.44</v>
-      </c>
       <c r="BF10" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>3.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="R11" t="n">
         <v>2.06</v>
@@ -2622,7 +2622,7 @@
         <v>2.51</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AG11" t="n">
         <v>4.83</v>
@@ -2643,7 +2643,7 @@
         <v>1.69</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AN11" t="n">
         <v>1.31</v>
@@ -2774,10 +2774,10 @@
         <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>3.23</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,34 +2968,34 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R13" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="S13" t="n">
-        <v>2.49</v>
+        <v>2.6</v>
       </c>
       <c r="T13" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="U13" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="V13" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="W13" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="X13" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z13" t="n">
         <v>8.1</v>
@@ -3004,97 +3004,97 @@
         <v>1.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG13" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AI13" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="AM13" t="n">
         <v>1.36</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.97</v>
+        <v>1.74</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.75</v>
+        <v>1.93</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.14</v>
+        <v>2.48</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AX13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY13" t="n">
         <v>1.27</v>
       </c>
-      <c r="AY13" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AZ13" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BA13" t="n">
-        <v>3.15</v>
+        <v>2.65</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.15</v>
+        <v>3.34</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA15" t="n">
         <v>2.8</v>
       </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.18</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="Q17" t="n">
         <v>3.3</v>
@@ -3765,25 +3765,25 @@
         <v>3.2</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="T17" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="U17" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="V17" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W17" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="X17" t="n">
         <v>2.45</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Z17" t="n">
         <v>5.6</v>
@@ -3792,19 +3792,19 @@
         <v>1.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="AE17" t="n">
         <v>1.76</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AG17" t="n">
         <v>2.64</v>
@@ -3813,10 +3813,10 @@
         <v>1.38</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK17" t="n">
         <v>1.6</v>
@@ -3825,10 +3825,10 @@
         <v>2.19</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,16 +3873,16 @@
         <v>1.17</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="BD17" t="n">
         <v>4.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.95</v>
+        <v>3.16</v>
       </c>
       <c r="R21" t="n">
-        <v>2.94</v>
+        <v>4.11</v>
       </c>
       <c r="S21" t="n">
-        <v>2.87</v>
+        <v>2.49</v>
       </c>
       <c r="T21" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="U21" t="n">
-        <v>4.13</v>
+        <v>5.1</v>
       </c>
       <c r="V21" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W21" t="n">
         <v>2.34</v>
       </c>
       <c r="X21" t="n">
-        <v>3.16</v>
+        <v>3.42</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z21" t="n">
         <v>9</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AG21" t="n">
-        <v>3.92</v>
+        <v>4.75</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AI21" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.52</v>
+        <v>1.76</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.01</v>
+        <v>2.26</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="AU21" t="n">
-        <v>4.16</v>
+        <v>3.48</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.83</v>
+        <v>2.46</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AZ21" t="n">
         <v>1.62</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.6</v>
+        <v>3.06</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.22</v>
+        <v>2.99</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="R22" t="n">
-        <v>4.49</v>
+        <v>2.94</v>
       </c>
       <c r="S22" t="n">
-        <v>2.47</v>
+        <v>2.87</v>
       </c>
       <c r="T22" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="U22" t="n">
-        <v>5.41</v>
+        <v>4.13</v>
       </c>
       <c r="V22" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W22" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="X22" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA22" t="n">
         <v>1.01</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AD22" t="n">
         <v>2.69</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AG22" t="n">
-        <v>4.33</v>
+        <v>3.92</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AI22" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK22" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.97</v>
+        <v>2.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.51</v>
+        <v>2.58</v>
       </c>
       <c r="AU22" t="n">
-        <v>4.31</v>
+        <v>4.16</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="BA22" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="BB22" t="n">
         <v>1.29</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="BD22" t="n">
         <v>3.22</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="R23" t="n">
-        <v>4.11</v>
+        <v>4.49</v>
       </c>
       <c r="S23" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="T23" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="U23" t="n">
-        <v>5.1</v>
+        <v>5.41</v>
       </c>
       <c r="V23" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W23" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="X23" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BF23" t="n">
         <v>1.07</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>1.06</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="S24" t="n">
-        <v>3.02</v>
+        <v>2.68</v>
       </c>
       <c r="T24" t="n">
-        <v>1.84</v>
+        <v>2.11</v>
       </c>
       <c r="U24" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="V24" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="W24" t="n">
-        <v>2.39</v>
+        <v>2.77</v>
       </c>
       <c r="X24" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY24" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AZ24" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.85</v>
+        <v>2.49</v>
       </c>
       <c r="BB24" t="n">
         <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="BD24" t="n">
         <v>3.42</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="R25" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="S25" t="n">
-        <v>2.68</v>
+        <v>3.02</v>
       </c>
       <c r="T25" t="n">
-        <v>2.11</v>
+        <v>1.84</v>
       </c>
       <c r="U25" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="V25" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="W25" t="n">
-        <v>2.77</v>
+        <v>2.39</v>
       </c>
       <c r="X25" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.85</v>
+        <v>3.54</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AI25" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.49</v>
+        <v>2.85</v>
       </c>
       <c r="BB25" t="n">
         <v>1.25</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="BD25" t="n">
         <v>3.42</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,130 +5529,130 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="S26" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="T26" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="U26" t="n">
-        <v>6.1</v>
+        <v>4.95</v>
       </c>
       <c r="V26" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W26" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="X26" t="n">
-        <v>2.94</v>
+        <v>3.11</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z26" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AA26" t="n">
         <v>1.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.99</v>
+        <v>3.18</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.54</v>
+        <v>3.65</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AI26" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BB26" t="n">
         <v>1.25</v>
       </c>
-      <c r="AQ26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC26" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.42</v>
+        <v>3.66</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="BF26" t="n">
         <v>1.12</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,130 +5726,130 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="R27" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="S27" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="T27" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="U27" t="n">
-        <v>4.95</v>
+        <v>6.1</v>
       </c>
       <c r="V27" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W27" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="X27" t="n">
-        <v>3.11</v>
+        <v>2.94</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z27" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AA27" t="n">
         <v>1.03</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.18</v>
+        <v>2.99</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="AF27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR27" t="n">
         <v>1.73</v>
       </c>
-      <c r="AG27" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM27" t="n">
+      <c r="AS27" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ27" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AX27" t="n">
+      <c r="BA27" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BE27" t="n">
         <v>1.59</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>1.62</v>
       </c>
       <c r="BF27" t="n">
         <v>1.12</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2583,7 +2583,7 @@
         <v>2.06</v>
       </c>
       <c r="S11" t="n">
-        <v>4.27</v>
+        <v>3.66</v>
       </c>
       <c r="T11" t="n">
         <v>1.88</v>
@@ -2604,7 +2604,7 @@
         <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AA11" t="n">
         <v>1</v>
@@ -2616,22 +2616,22 @@
         <v>1.48</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AE11" t="n">
         <v>2.51</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AG11" t="n">
         <v>4.83</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AI11" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="AJ11" t="n">
         <v>1</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,34 +2968,34 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="T13" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U13" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="V13" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="W13" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="X13" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
         <v>8.1</v>
@@ -3004,94 +3004,94 @@
         <v>1.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.8</v>
+        <v>2.61</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.19</v>
+        <v>2.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG13" t="n">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AI13" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AM13" t="n">
         <v>1.36</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.74</v>
+        <v>1.96</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.93</v>
+        <v>2.75</v>
       </c>
       <c r="AS13" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU13" t="n">
         <v>2.48</v>
       </c>
-      <c r="AT13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.95</v>
-      </c>
       <c r="AV13" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="BF13" t="n">
         <v>1.1</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="S15" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="R16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD16" t="n">
         <v>2.8</v>
       </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
       <c r="AE16" t="n">
-        <v>1.65</v>
+        <v>2.19</v>
       </c>
       <c r="AF16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AV16" t="n">
         <v>2.2</v>
       </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4347,40 +4347,40 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="R20" t="n">
         <v>4.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.58</v>
+        <v>2.41</v>
       </c>
       <c r="T20" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>4.66</v>
+        <v>3.98</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W20" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="X20" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
         <v>8.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AB20" t="n">
         <v>1.04</v>
@@ -4401,16 +4401,16 @@
         <v>3.58</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AI20" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AJ20" t="n">
         <v>1.04</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AL20" t="n">
         <v>1.83</v>
@@ -4419,61 +4419,61 @@
         <v>1.3</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.96</v>
+        <v>1.72</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.65</v>
+        <v>3.78</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.9</v>
+        <v>2.53</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="BC20" t="n">
         <v>2.25</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>4.11</v>
+        <v>4.33</v>
       </c>
       <c r="S21" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="T21" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="U21" t="n">
-        <v>5.1</v>
+        <v>5.41</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W21" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="X21" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AC21" t="n">
         <v>1.42</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="AG21" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AI21" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AK21" t="n">
         <v>2.05</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AN21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR21" t="n">
         <v>1.76</v>
       </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AS21" t="n">
-        <v>2.26</v>
+        <v>1.97</v>
       </c>
       <c r="AT21" t="n">
-        <v>3</v>
+        <v>2.51</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.48</v>
+        <v>4.31</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.46</v>
+        <v>2.97</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.62</v>
+        <v>1.14</v>
       </c>
       <c r="BA21" t="n">
-        <v>3.06</v>
+        <v>3.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.99</v>
+        <v>3.22</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4744,7 +4744,7 @@
         <v>2.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
         <v>2.94</v>
@@ -4753,34 +4753,34 @@
         <v>2.87</v>
       </c>
       <c r="T22" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="U22" t="n">
         <v>4.13</v>
       </c>
       <c r="V22" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="W22" t="n">
-        <v>2.34</v>
+        <v>2.63</v>
       </c>
       <c r="X22" t="n">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z22" t="n">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AB22" t="n">
         <v>1.06</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AD22" t="n">
         <v>2.69</v>
@@ -4789,7 +4789,7 @@
         <v>2.28</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG22" t="n">
         <v>3.92</v>
@@ -4807,7 +4807,7 @@
         <v>1.95</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AM22" t="n">
         <v>1.37</v>
@@ -4819,7 +4819,7 @@
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.34</v>
@@ -4828,7 +4828,7 @@
         <v>1.8</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AT22" t="n">
         <v>2.58</v>
@@ -4837,16 +4837,16 @@
         <v>4.16</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AX22" t="n">
         <v>1.71</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AZ22" t="n">
         <v>1.62</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R23" t="n">
-        <v>4.49</v>
+        <v>4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.47</v>
+        <v>2.67</v>
       </c>
       <c r="T23" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="U23" t="n">
-        <v>5.41</v>
+        <v>4.17</v>
       </c>
       <c r="V23" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W23" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="X23" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z23" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>1.03</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AK23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ23" t="n">
         <v>1.43</v>
       </c>
-      <c r="AD23" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AR23" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.51</v>
+        <v>3.02</v>
       </c>
       <c r="AU23" t="n">
-        <v>4.31</v>
+        <v>3.46</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.91</v>
+        <v>2.28</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="AY23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="BE23" t="n">
         <v>1.44</v>
       </c>
-      <c r="AZ23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.48</v>
-      </c>
       <c r="BF23" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
         <v>3.3</v>
       </c>
       <c r="S24" t="n">
-        <v>2.68</v>
+        <v>2.91</v>
       </c>
       <c r="T24" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="U24" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="V24" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="W24" t="n">
-        <v>2.77</v>
+        <v>2.47</v>
       </c>
       <c r="X24" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AC24" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.85</v>
+        <v>3.54</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AI24" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AJ24" t="n">
         <v>1.03</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.72</v>
+        <v>3.35</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.55</v>
+        <v>2.34</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.49</v>
+        <v>2.85</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="BD24" t="n">
         <v>3.42</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="S25" t="n">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="T25" t="n">
-        <v>1.84</v>
+        <v>2.11</v>
       </c>
       <c r="U25" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="V25" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="W25" t="n">
-        <v>2.39</v>
+        <v>2.77</v>
       </c>
       <c r="X25" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z25" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC25" t="n">
         <v>1.35</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.19</v>
+        <v>2.08</v>
       </c>
       <c r="AF25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN25" t="n">
         <v>1.68</v>
       </c>
-      <c r="AG25" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.61</v>
-      </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.37</v>
+        <v>2.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.85</v>
+        <v>2.49</v>
       </c>
       <c r="BB25" t="n">
         <v>1.25</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="BD25" t="n">
         <v>3.42</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="R26" t="n">
         <v>4.2</v>
@@ -5541,25 +5541,25 @@
         <v>2.38</v>
       </c>
       <c r="T26" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="U26" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="V26" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W26" t="n">
         <v>2.77</v>
       </c>
       <c r="X26" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="Y26" t="n">
         <v>1.36</v>
       </c>
       <c r="Z26" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AA26" t="n">
         <v>1.03</v>
@@ -5574,28 +5574,28 @@
         <v>3.18</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.99</v>
+        <v>2.09</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AH26" t="n">
         <v>1.24</v>
       </c>
       <c r="AI26" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK26" t="n">
         <v>1.85</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AM26" t="n">
         <v>1.3</v>
@@ -5610,52 +5610,52 @@
         <v>1.28</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.78</v>
+        <v>3.25</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="AW26" t="n">
         <v>2.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5726,28 +5726,28 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.8</v>
+        <v>3.86</v>
       </c>
       <c r="R27" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="S27" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="T27" t="n">
         <v>2.13</v>
       </c>
       <c r="U27" t="n">
-        <v>6.1</v>
+        <v>6.35</v>
       </c>
       <c r="V27" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W27" t="n">
-        <v>2.69</v>
+        <v>2.82</v>
       </c>
       <c r="X27" t="n">
         <v>2.94</v>
@@ -5756,7 +5756,7 @@
         <v>1.35</v>
       </c>
       <c r="Z27" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AA27" t="n">
         <v>1.03</v>
@@ -5774,7 +5774,7 @@
         <v>2.11</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG27" t="n">
         <v>3.54</v>
@@ -5783,13 +5783,13 @@
         <v>1.22</v>
       </c>
       <c r="AI27" t="n">
-        <v>6.9</v>
+        <v>6.95</v>
       </c>
       <c r="AJ27" t="n">
         <v>1.09</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="AL27" t="n">
         <v>1.68</v>
@@ -5798,13 +5798,13 @@
         <v>1.26</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.44</v>
@@ -5816,10 +5816,10 @@
         <v>2.16</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AV27" t="n">
         <v>2.55</v>
@@ -5828,28 +5828,28 @@
         <v>1.96</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="BA27" t="n">
-        <v>3.46</v>
+        <v>3.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="BD27" t="n">
         <v>3.42</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="BF27" t="n">
         <v>1.12</v>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="R28" t="n">
         <v>2.91</v>
@@ -5938,7 +5938,7 @@
         <v>2.05</v>
       </c>
       <c r="U28" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="V28" t="n">
         <v>1.46</v>
@@ -5953,43 +5953,43 @@
         <v>1.33</v>
       </c>
       <c r="Z28" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA28" t="n">
         <v>1.01</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="AE28" t="n">
         <v>2.26</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AI28" t="n">
         <v>8</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AK28" t="n">
         <v>1.95</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AM28" t="n">
         <v>1.36</v>
@@ -6001,55 +6001,55 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AR28" t="n">
         <v>1.68</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="AV28" t="n">
         <v>2.65</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="BC28" t="n">
         <v>2.4</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="BE28" t="n">
         <v>1.53</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6120,16 +6120,16 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
         <v>2</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>4.78</v>
       </c>
       <c r="T29" t="n">
         <v>2</v>
@@ -6144,7 +6144,7 @@
         <v>2.32</v>
       </c>
       <c r="X29" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Y29" t="n">
         <v>1.27</v>
@@ -6156,19 +6156,19 @@
         <v>1.01</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="AE29" t="n">
         <v>2.4</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG29" t="n">
         <v>4.75</v>
@@ -6186,7 +6186,7 @@
         <v>2.06</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AM29" t="n">
         <v>1.33</v>
@@ -6201,10 +6201,10 @@
         <v>1.22</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.66</v>
+        <v>2.04</v>
       </c>
       <c r="AS29" t="n">
         <v>2.27</v>
@@ -6213,13 +6213,13 @@
         <v>3.02</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AX29" t="n">
         <v>1.55</v>
@@ -6228,19 +6228,19 @@
         <v>1.3</v>
       </c>
       <c r="AZ29" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="BB29" t="n">
         <v>1.33</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BD29" t="n">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="BE29" t="n">
         <v>1.44</v>
@@ -6317,19 +6317,19 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="S30" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="T30" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U30" t="n">
         <v>4.5</v>
@@ -6341,22 +6341,22 @@
         <v>2.47</v>
       </c>
       <c r="X30" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AB30" t="n">
         <v>1.09</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AD30" t="n">
         <v>2.82</v>
@@ -6371,76 +6371,76 @@
         <v>4.1</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AI30" t="n">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK30" t="n">
         <v>2.23</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AR30" t="n">
         <v>2.1</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.18</v>
+        <v>3.42</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.37</v>
+        <v>2.46</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AY30" t="n">
         <v>1.33</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="BB30" t="n">
         <v>1.3</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="BD30" t="n">
         <v>3.22</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="BF30" t="n">
         <v>1.08</v>
@@ -6523,13 +6523,13 @@
         <v>4</v>
       </c>
       <c r="S31" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T31" t="n">
         <v>2.05</v>
       </c>
       <c r="U31" t="n">
-        <v>4.6</v>
+        <v>5.03</v>
       </c>
       <c r="V31" t="n">
         <v>1.41</v>
@@ -6538,13 +6538,13 @@
         <v>2.66</v>
       </c>
       <c r="X31" t="n">
-        <v>2.85</v>
+        <v>3.02</v>
       </c>
       <c r="Y31" t="n">
         <v>1.36</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="AA31" t="n">
         <v>1.04</v>
@@ -6559,10 +6559,10 @@
         <v>3.04</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG31" t="n">
         <v>3.35</v>
@@ -6574,52 +6574,52 @@
         <v>6.25</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AL31" t="n">
         <v>1.86</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.68</v>
+        <v>2.85</v>
       </c>
       <c r="AW31" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AZ31" t="n">
         <v>1.35</v>
@@ -6637,7 +6637,7 @@
         <v>3.44</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BF31" t="n">
         <v>1.13</v>
@@ -6711,7 +6711,7 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q32" t="n">
         <v>3.4</v>
@@ -6720,13 +6720,13 @@
         <v>5</v>
       </c>
       <c r="S32" t="n">
-        <v>2.29</v>
+        <v>2.16</v>
       </c>
       <c r="T32" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>6.26</v>
+        <v>6.21</v>
       </c>
       <c r="V32" t="n">
         <v>1.47</v>
@@ -6735,13 +6735,13 @@
         <v>2.47</v>
       </c>
       <c r="X32" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA32" t="n">
         <v>1.02</v>
@@ -6759,7 +6759,7 @@
         <v>2.25</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG32" t="n">
         <v>3.94</v>
@@ -6774,10 +6774,10 @@
         <v>1.02</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.11</v>
+        <v>2.27</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AM32" t="n">
         <v>1.27</v>
@@ -6819,19 +6819,19 @@
         <v>1.42</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="BA32" t="n">
         <v>5.63</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="BC32" t="n">
         <v>2.39</v>
       </c>
       <c r="BD32" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BE32" t="n">
         <v>1.5</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.95</v>
+        <v>3.21</v>
       </c>
       <c r="R4" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="S4" t="n">
-        <v>5.4</v>
+        <v>5.18</v>
       </c>
       <c r="T4" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U4" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="V4" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="W4" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="X4" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AB4" t="n">
         <v>1.07</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AI4" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AM4" t="n">
         <v>1.26</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1276,10 +1276,10 @@
         <v>1.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AR4" t="n">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="AS4" t="n">
         <v>3.34</v>
@@ -1291,7 +1291,7 @@
         <v>2.38</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AW4" t="n">
         <v>1.48</v>
@@ -1306,22 +1306,22 @@
         <v>2.88</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2189,19 +2189,19 @@
         <v>6.25</v>
       </c>
       <c r="S9" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="T9" t="n">
         <v>1.92</v>
       </c>
       <c r="U9" t="n">
-        <v>8.15</v>
+        <v>7.95</v>
       </c>
       <c r="V9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W9" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="X9" t="n">
         <v>3.42</v>
@@ -2210,37 +2210,37 @@
         <v>1.23</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AA9" t="n">
         <v>1.03</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="AE9" t="n">
         <v>2.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AG9" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AI9" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AK9" t="n">
         <v>2.45</v>
@@ -2252,7 +2252,7 @@
         <v>1.23</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2291,7 +2291,7 @@
         <v>1.18</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.39</v>
+        <v>4.85</v>
       </c>
       <c r="BB9" t="n">
         <v>1.31</v>
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="R10" t="n">
-        <v>5</v>
+        <v>5.81</v>
       </c>
       <c r="S10" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="T10" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="U10" t="n">
-        <v>7.55</v>
+        <v>7.37</v>
       </c>
       <c r="V10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W10" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X10" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.9</v>
+        <v>10.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB10" t="n">
         <v>1.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AE10" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AG10" t="n">
-        <v>6.25</v>
+        <v>4.75</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AI10" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2461,7 +2461,7 @@
         <v>1.87</v>
       </c>
       <c r="AR10" t="n">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="AS10" t="n">
         <v>3.34</v>
@@ -2491,16 +2491,16 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="BF10" t="n">
         <v>1.05</v>
@@ -2622,19 +2622,19 @@
         <v>2.51</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AG11" t="n">
         <v>4.83</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AI11" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AK11" t="n">
         <v>2.05</v>
@@ -2643,10 +2643,10 @@
         <v>1.69</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.51</v>
+        <v>3.44</v>
       </c>
       <c r="R12" t="n">
-        <v>3.23</v>
+        <v>3.04</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2971,16 +2971,16 @@
         <v>1.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="R13" t="n">
-        <v>4.2</v>
+        <v>5.24</v>
       </c>
       <c r="S13" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U13" t="n">
         <v>4.75</v>
@@ -3007,19 +3007,19 @@
         <v>1.06</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AF13" t="n">
         <v>1.62</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="AH13" t="n">
         <v>1.17</v>
@@ -3028,7 +3028,7 @@
         <v>9</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK13" t="n">
         <v>2.05</v>
@@ -3058,10 +3058,10 @@
         <v>3.14</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AV13" t="n">
         <v>1.89</v>
@@ -3073,10 +3073,10 @@
         <v>1.27</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BA13" t="n">
         <v>2.8</v>
@@ -3091,10 +3091,10 @@
         <v>3.15</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="R15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD15" t="n">
         <v>2.8</v>
       </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AF15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AV15" t="n">
         <v>2.2</v>
       </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.19</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.07</v>
+        <v>1.96</v>
       </c>
       <c r="Q17" t="n">
         <v>3.3</v>
@@ -3765,22 +3765,22 @@
         <v>3.2</v>
       </c>
       <c r="S17" t="n">
-        <v>2.57</v>
+        <v>2.49</v>
       </c>
       <c r="T17" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="U17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="V17" t="n">
         <v>1.35</v>
       </c>
       <c r="W17" t="n">
-        <v>2.94</v>
+        <v>3.24</v>
       </c>
       <c r="X17" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Y17" t="n">
         <v>1.47</v>
@@ -3795,7 +3795,7 @@
         <v>1.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AD17" t="n">
         <v>3.78</v>
@@ -3804,19 +3804,19 @@
         <v>1.76</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="n">
         <v>2.64</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AI17" t="n">
         <v>4.7</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AK17" t="n">
         <v>1.6</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4347,37 +4347,37 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="R20" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.41</v>
+        <v>2.64</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U20" t="n">
-        <v>3.98</v>
+        <v>4.56</v>
       </c>
       <c r="V20" t="n">
         <v>1.44</v>
       </c>
       <c r="W20" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="Y20" t="n">
         <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="AA20" t="n">
         <v>1.03</v>
@@ -4401,25 +4401,25 @@
         <v>3.58</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AI20" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AJ20" t="n">
         <v>1.04</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AL20" t="n">
         <v>1.83</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4431,46 +4431,46 @@
         <v>1.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.78</v>
+        <v>3.81</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AW20" t="n">
         <v>2.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.53</v>
+        <v>2.78</v>
       </c>
       <c r="BB20" t="n">
         <v>1.26</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="BF20" t="n">
         <v>1.12</v>
@@ -4568,7 +4568,7 @@
         <v>2.47</v>
       </c>
       <c r="X21" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Y21" t="n">
         <v>1.28</v>
@@ -4598,10 +4598,10 @@
         <v>4.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AI21" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AJ21" t="n">
         <v>1.01</v>
@@ -4622,7 +4622,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AQ21" t="n">
         <v>1.3</v>
@@ -4655,19 +4655,19 @@
         <v>1.14</v>
       </c>
       <c r="BA21" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="BB21" t="n">
         <v>1.29</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="BD21" t="n">
         <v>3.22</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BF21" t="n">
         <v>1.07</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AE22" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q22" t="n">
-        <v>3</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U22" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="AF22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BF22" t="n">
         <v>1.06</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.09</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,22 +4938,22 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.97</v>
+        <v>2.38</v>
       </c>
       <c r="Q23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R23" t="n">
         <v>3.2</v>
       </c>
-      <c r="R23" t="n">
-        <v>4</v>
-      </c>
       <c r="S23" t="n">
-        <v>2.67</v>
+        <v>3.14</v>
       </c>
       <c r="T23" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U23" t="n">
-        <v>4.17</v>
+        <v>4.13</v>
       </c>
       <c r="V23" t="n">
         <v>1.52</v>
@@ -4962,109 +4962,109 @@
         <v>2.34</v>
       </c>
       <c r="X23" t="n">
-        <v>3.42</v>
+        <v>3.33</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA23" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.49</v>
+        <v>2.66</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AG23" t="n">
-        <v>4.75</v>
+        <v>3.92</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AI23" t="n">
-        <v>9.5</v>
+        <v>7.9</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.76</v>
+        <v>1.52</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.02</v>
+        <v>2.58</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.46</v>
+        <v>4.16</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.28</v>
+        <v>2.83</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.8</v>
+        <v>2.13</v>
       </c>
       <c r="AX23" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AY23" t="n">
         <v>1.54</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.3</v>
       </c>
       <c r="AZ23" t="n">
         <v>1.62</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.08</v>
+        <v>2.6</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="BD23" t="n">
-        <v>2.99</v>
+        <v>3.22</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,121 +5135,121 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
         <v>3.3</v>
       </c>
       <c r="S24" t="n">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="T24" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="U24" t="n">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="V24" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="W24" t="n">
-        <v>2.47</v>
+        <v>2.77</v>
       </c>
       <c r="X24" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
         <v>1.35</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.54</v>
+        <v>4.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AI24" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AJ24" t="n">
         <v>1.03</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BB24" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.3</v>
       </c>
       <c r="BC24" t="n">
         <v>2.3</v>
@@ -5258,10 +5258,10 @@
         <v>3.42</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,121 +5332,121 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
         <v>3.3</v>
       </c>
       <c r="S25" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="T25" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="U25" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="V25" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="W25" t="n">
-        <v>2.77</v>
+        <v>2.47</v>
       </c>
       <c r="X25" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.03</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.01</v>
       </c>
       <c r="AC25" t="n">
         <v>1.35</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AG25" t="n">
-        <v>4.2</v>
+        <v>3.54</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AI25" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AJ25" t="n">
         <v>1.03</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.49</v>
+        <v>2.85</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="BC25" t="n">
         <v>2.3</v>
@@ -5455,10 +5455,10 @@
         <v>3.42</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.64</v>
+        <v>3.86</v>
       </c>
       <c r="R26" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="S26" t="n">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="T26" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="U26" t="n">
-        <v>4.9</v>
+        <v>6.35</v>
       </c>
       <c r="V26" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W26" t="n">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="X26" t="n">
-        <v>3.12</v>
+        <v>2.94</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AA26" t="n">
         <v>1.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.18</v>
+        <v>2.99</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AG26" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU26" t="n">
         <v>3.7</v>
       </c>
-      <c r="AH26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AV26" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.65</v>
+        <v>3.42</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.86</v>
+        <v>3.64</v>
       </c>
       <c r="R27" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="S27" t="n">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="T27" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="U27" t="n">
-        <v>6.35</v>
+        <v>4.9</v>
       </c>
       <c r="V27" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W27" t="n">
-        <v>2.82</v>
+        <v>2.77</v>
       </c>
       <c r="X27" t="n">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z27" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AA27" t="n">
         <v>1.03</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.99</v>
+        <v>3.18</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AI27" t="n">
-        <v>6.95</v>
+        <v>6.7</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -6123,16 +6123,16 @@
         <v>3.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="R29" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="S29" t="n">
         <v>4.78</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="U29" t="n">
         <v>2.77</v>
@@ -6144,7 +6144,7 @@
         <v>2.32</v>
       </c>
       <c r="X29" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="Y29" t="n">
         <v>1.27</v>
@@ -6162,13 +6162,13 @@
         <v>1.48</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AE29" t="n">
         <v>2.4</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG29" t="n">
         <v>4.75</v>
@@ -6180,7 +6180,7 @@
         <v>8.6</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AK29" t="n">
         <v>2.06</v>
@@ -6213,7 +6213,7 @@
         <v>3.02</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="AV29" t="n">
         <v>2.45</v>
@@ -6234,7 +6234,7 @@
         <v>1.83</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BC29" t="n">
         <v>2.56</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="S30" t="n">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="T30" t="n">
-        <v>1.96</v>
+        <v>2.13</v>
       </c>
       <c r="U30" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="V30" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W30" t="n">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="X30" t="n">
-        <v>3.28</v>
+        <v>2.85</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
-        <v>8</v>
+        <v>6.75</v>
       </c>
       <c r="AA30" t="n">
         <v>1.04</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.82</v>
+        <v>3.04</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.35</v>
+        <v>1.91</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AG30" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AI30" t="n">
-        <v>9</v>
+        <v>6.25</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.23</v>
+        <v>1.84</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AR30" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BC30" t="n">
         <v>2.1</v>
       </c>
-      <c r="AS30" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>3</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>2.47</v>
-      </c>
       <c r="BD30" t="n">
-        <v>3.22</v>
+        <v>3.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="S31" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="T31" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="U31" t="n">
-        <v>5.03</v>
+        <v>4.5</v>
       </c>
       <c r="V31" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="W31" t="n">
-        <v>2.66</v>
+        <v>2.47</v>
       </c>
       <c r="X31" t="n">
-        <v>3.02</v>
+        <v>3.28</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z31" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA31" t="n">
         <v>1.04</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.04</v>
+        <v>2.82</v>
       </c>
       <c r="AE31" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AG31" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AI31" t="n">
-        <v>6.25</v>
+        <v>9</v>
       </c>
       <c r="AJ31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BF31" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>1.13</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6729,10 +6729,10 @@
         <v>6.21</v>
       </c>
       <c r="V32" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W32" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="X32" t="n">
         <v>3.16</v>
@@ -6762,10 +6762,10 @@
         <v>1.62</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AI32" t="n">
         <v>8.5</v>
@@ -6774,7 +6774,7 @@
         <v>1.02</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="AL32" t="n">
         <v>1.65</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.44</v>
+        <v>3.05</v>
       </c>
       <c r="R12" t="n">
-        <v>3.04</v>
+        <v>2.78</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.03</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>5.24</v>
+        <v>2.8</v>
       </c>
       <c r="S13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.51</v>
+        <v>1.65</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>2.55</v>
+        <v>3.9</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>2.69</v>
       </c>
       <c r="T14" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="U14" t="n">
-        <v>3.32</v>
+        <v>4.6</v>
       </c>
       <c r="V14" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="W14" t="n">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="X14" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AA14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AC14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AM14" t="n">
         <v>1.28</v>
       </c>
-      <c r="AD14" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AN14" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="AR14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW14" t="n">
         <v>1.74</v>
       </c>
-      <c r="AS14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AX14" t="n">
-        <v>1.76</v>
+        <v>1.45</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="R15" t="n">
-        <v>3.7</v>
+        <v>2.55</v>
       </c>
       <c r="S15" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="U15" t="n">
-        <v>4.55</v>
+        <v>3.32</v>
       </c>
       <c r="V15" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="W15" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="X15" t="n">
-        <v>3.15</v>
+        <v>2.82</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.8</v>
+        <v>3.28</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AI15" t="n">
-        <v>7.5</v>
+        <v>6.45</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.76</v>
+        <v>2.01</v>
       </c>
       <c r="AM15" t="n">
         <v>1.36</v>
       </c>
       <c r="AN15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR15" t="n">
         <v>1.74</v>
       </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AS15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT15" t="n">
         <v>2.48</v>
       </c>
-      <c r="AT15" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AU15" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AV15" t="n">
         <v>2.95</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="AW15" t="n">
         <v>2.2</v>
       </c>
-      <c r="AW15" t="n">
-        <v>1.74</v>
-      </c>
       <c r="AX15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AY15" t="n">
         <v>1.45</v>
       </c>
-      <c r="AY15" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AZ15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.34</v>
+        <v>3.75</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>3.03</v>
       </c>
       <c r="R16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BA16" t="n">
         <v>2.8</v>
       </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3762,22 +3762,22 @@
         <v>3.3</v>
       </c>
       <c r="R17" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="S17" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="T17" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="U17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="V17" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W17" t="n">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="X17" t="n">
         <v>2.5</v>
@@ -3795,28 +3795,28 @@
         <v>1.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
         <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK17" t="n">
         <v>1.6</v>
@@ -3828,7 +3828,7 @@
         <v>1.3</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3873,13 +3873,13 @@
         <v>1.17</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="BF17" t="n">
         <v>1.22</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S30" t="n">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="T30" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>4.6</v>
+        <v>6.21</v>
       </c>
       <c r="V30" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W30" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="X30" t="n">
-        <v>2.85</v>
+        <v>3.16</v>
       </c>
       <c r="Y30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC30" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z30" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB30" t="n">
+      <c r="AD30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>1.02</v>
       </c>
-      <c r="AC30" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AK30" t="n">
-        <v>1.84</v>
+        <v>2.11</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6410,13 +6410,13 @@
         <v>2.56</v>
       </c>
       <c r="AU30" t="n">
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AW30" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AX30" t="n">
         <v>1.72</v>
@@ -6425,25 +6425,25 @@
         <v>1.42</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="BA30" t="n">
-        <v>3.6</v>
+        <v>5.63</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S32" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="T32" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="U32" t="n">
-        <v>6.21</v>
+        <v>4.6</v>
       </c>
       <c r="V32" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W32" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="X32" t="n">
-        <v>3.16</v>
+        <v>2.85</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z32" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="AA32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB32" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB32" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AC32" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.92</v>
+        <v>3.35</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AI32" t="n">
-        <v>8.5</v>
+        <v>6.25</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.11</v>
+        <v>1.84</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AN32" t="n">
-        <v>2.11</v>
+        <v>1.88</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6804,13 +6804,13 @@
         <v>2.56</v>
       </c>
       <c r="AU32" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="AW32" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AX32" t="n">
         <v>1.72</v>
@@ -6819,25 +6819,25 @@
         <v>1.42</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.63</v>
+        <v>3.6</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,133 +1983,133 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="Q11" t="n">
         <v>2.97</v>
@@ -2583,10 +2583,10 @@
         <v>2.06</v>
       </c>
       <c r="S11" t="n">
-        <v>3.66</v>
+        <v>3.9</v>
       </c>
       <c r="T11" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="U11" t="n">
         <v>2.91</v>
@@ -2607,46 +2607,46 @@
         <v>9.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AC11" t="n">
         <v>1.48</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AG11" t="n">
-        <v>4.83</v>
+        <v>4.87</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AI11" t="n">
         <v>10</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.64</v>
+        <v>1.37</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2691,13 +2691,13 @@
         <v>1.33</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="BD11" t="n">
         <v>2.99</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="BF11" t="n">
         <v>1.06</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AE15" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="AF15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF15" t="n">
+      <c r="AK15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>1.79</v>
       </c>
-      <c r="AG15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN15" t="n">
+      <c r="AR15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AW15" t="n">
         <v>1.5</v>
       </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
+      <c r="AX15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AY15" t="n">
         <v>1.13</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AZ15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB15" t="n">
         <v>1.31</v>
       </c>
-      <c r="AR15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.19</v>
-      </c>
       <c r="BC15" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.03</v>
+        <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>4.5</v>
+        <v>2.55</v>
       </c>
       <c r="S16" t="n">
-        <v>2.46</v>
+        <v>3.1</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="U16" t="n">
-        <v>5.8</v>
+        <v>3.32</v>
       </c>
       <c r="V16" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="W16" t="n">
-        <v>2.32</v>
+        <v>2.7</v>
       </c>
       <c r="X16" t="n">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.1</v>
+        <v>7.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.61</v>
+        <v>3.28</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.98</v>
+        <v>3.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AI16" t="n">
-        <v>9.5</v>
+        <v>6.45</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.66</v>
+        <v>2.01</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.98</v>
+        <v>1.5</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.79</v>
+        <v>1.31</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.75</v>
+        <v>1.74</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.14</v>
+        <v>1.95</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.5</v>
+        <v>2.48</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.48</v>
+        <v>4.39</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.89</v>
+        <v>2.95</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.27</v>
+        <v>1.76</v>
       </c>
       <c r="AY16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BF16" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1.1</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>4.33</v>
+        <v>3.35</v>
       </c>
       <c r="S21" t="n">
-        <v>2.47</v>
+        <v>2.67</v>
       </c>
       <c r="T21" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="U21" t="n">
-        <v>5.41</v>
+        <v>4.17</v>
       </c>
       <c r="V21" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W21" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="X21" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="Z21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AC21" t="n">
         <v>1.42</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.69</v>
+        <v>2.49</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="AG21" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AI21" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AK21" t="n">
         <v>2.05</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AQ21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY21" t="n">
         <v>1.3</v>
       </c>
-      <c r="AR21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AY21" t="n">
+      <c r="AZ21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="BE21" t="n">
         <v>1.44</v>
       </c>
-      <c r="AZ21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.48</v>
-      </c>
       <c r="BF21" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="Q22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R22" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U22" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X22" t="n">
         <v>3.1</v>
       </c>
-      <c r="R22" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U22" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.42</v>
-      </c>
       <c r="Y22" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Z22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA22" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AC22" t="n">
         <v>1.42</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="AG22" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AI22" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AK22" t="n">
         <v>2.05</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AN22" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR22" t="n">
         <v>1.76</v>
       </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AS22" t="n">
-        <v>2.38</v>
+        <v>1.97</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.03</v>
+        <v>2.51</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.46</v>
+        <v>4.31</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.28</v>
+        <v>2.97</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.54</v>
+        <v>1.74</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.66</v>
+        <v>1.14</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.55</v>
+        <v>4.3</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.99</v>
+        <v>3.22</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R24" t="n">
-        <v>3.3</v>
+        <v>3.63</v>
       </c>
       <c r="S24" t="n">
-        <v>2.7</v>
+        <v>2.91</v>
       </c>
       <c r="T24" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="U24" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="V24" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="W24" t="n">
-        <v>2.77</v>
+        <v>2.47</v>
       </c>
       <c r="X24" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AC24" t="n">
         <v>1.35</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AG24" t="n">
-        <v>4.2</v>
+        <v>3.54</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AI24" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.49</v>
+        <v>2.9</v>
       </c>
       <c r="BB24" t="n">
         <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.42</v>
+        <v>3.45</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U25" t="n">
+        <v>4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD25" t="n">
         <v>3.2</v>
       </c>
-      <c r="R25" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U25" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="X25" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3</v>
-      </c>
       <c r="AE25" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AF25" t="n">
         <v>1.68</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.54</v>
+        <v>4.1</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AI25" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BB25" t="n">
         <v>1.25</v>
       </c>
-      <c r="AQ25" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV25" t="n">
+      <c r="BC25" t="n">
         <v>2.34</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.3</v>
       </c>
       <c r="BD25" t="n">
         <v>3.42</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5529,58 +5529,58 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="S26" t="n">
         <v>2.13</v>
       </c>
       <c r="T26" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="U26" t="n">
-        <v>6.35</v>
+        <v>5.6</v>
       </c>
       <c r="V26" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W26" t="n">
-        <v>2.82</v>
+        <v>2.69</v>
       </c>
       <c r="X26" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="Y26" t="n">
         <v>1.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AA26" t="n">
         <v>1.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AC26" t="n">
         <v>1.36</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.99</v>
+        <v>3.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="AF26" t="n">
         <v>1.76</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.54</v>
+        <v>3.75</v>
       </c>
       <c r="AH26" t="n">
         <v>1.22</v>
@@ -5589,16 +5589,16 @@
         <v>6.95</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AN26" t="n">
         <v>2.36</v>
@@ -5610,10 +5610,10 @@
         <v>1.2</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AS26" t="n">
         <v>2.16</v>
@@ -5625,25 +5625,25 @@
         <v>3.7</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AX26" t="n">
         <v>1.57</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BA26" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BC26" t="n">
         <v>2.29</v>
@@ -5652,7 +5652,7 @@
         <v>3.42</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="BF26" t="n">
         <v>1.12</v>
@@ -5726,31 +5726,31 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.64</v>
+        <v>3.2</v>
       </c>
       <c r="R27" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="S27" t="n">
         <v>2.38</v>
       </c>
       <c r="T27" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="U27" t="n">
         <v>4.9</v>
       </c>
       <c r="V27" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W27" t="n">
         <v>2.77</v>
       </c>
       <c r="X27" t="n">
-        <v>3.12</v>
+        <v>2.75</v>
       </c>
       <c r="Y27" t="n">
         <v>1.36</v>
@@ -5762,22 +5762,22 @@
         <v>1.03</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AD27" t="n">
         <v>3.18</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AH27" t="n">
         <v>1.24</v>
@@ -5789,13 +5789,13 @@
         <v>1.04</v>
       </c>
       <c r="AK27" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL27" t="n">
         <v>1.85</v>
       </c>
-      <c r="AL27" t="n">
-        <v>1.88</v>
-      </c>
       <c r="AM27" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AN27" t="n">
         <v>2</v>
@@ -5804,52 +5804,52 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.95</v>
+        <v>2.83</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.25</v>
+        <v>3.78</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="AW27" t="n">
-        <v>2.01</v>
+        <v>1.89</v>
       </c>
       <c r="AX27" t="n">
         <v>1.55</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="BF27" t="n">
         <v>1.13</v>
@@ -5923,31 +5923,31 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="R28" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="S28" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="T28" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="U28" t="n">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="V28" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W28" t="n">
-        <v>2.53</v>
+        <v>2.71</v>
       </c>
       <c r="X28" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="Y28" t="n">
         <v>1.33</v>
@@ -5959,55 +5959,55 @@
         <v>1.01</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AE28" t="n">
         <v>2.26</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AG28" t="n">
-        <v>3.95</v>
+        <v>4.14</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AI28" t="n">
         <v>8</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AM28" t="n">
         <v>1.36</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AQ28" t="n">
         <v>1.41</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AS28" t="n">
         <v>2.11</v>
@@ -6019,10 +6019,10 @@
         <v>3.84</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="AW28" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="AX28" t="n">
         <v>1.6</v>
@@ -6031,7 +6031,7 @@
         <v>1.34</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="BA28" t="n">
         <v>2.52</v>
@@ -6040,7 +6040,7 @@
         <v>1.24</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="BD28" t="n">
         <v>3.55</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S30" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="U30" t="n">
-        <v>6.21</v>
+        <v>4.6</v>
       </c>
       <c r="V30" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W30" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="X30" t="n">
-        <v>3.16</v>
+        <v>2.85</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="AA30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB30" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AC30" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.92</v>
+        <v>3.35</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AI30" t="n">
-        <v>8.5</v>
+        <v>6.25</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.11</v>
+        <v>1.84</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.11</v>
+        <v>1.88</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6410,13 +6410,13 @@
         <v>2.56</v>
       </c>
       <c r="AU30" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="AW30" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AX30" t="n">
         <v>1.72</v>
@@ -6425,25 +6425,25 @@
         <v>1.42</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="BA30" t="n">
-        <v>5.63</v>
+        <v>3.6</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="S31" t="n">
-        <v>2.56</v>
+        <v>2.16</v>
       </c>
       <c r="T31" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>4.5</v>
+        <v>6.21</v>
       </c>
       <c r="V31" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W31" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="X31" t="n">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AC31" t="n">
         <v>1.36</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AG31" t="n">
-        <v>4.1</v>
+        <v>3.92</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AI31" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.9</v>
+        <v>2.11</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.05</v>
+        <v>2.56</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.42</v>
+        <v>4.22</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.46</v>
+        <v>2.86</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="BA31" t="n">
-        <v>3</v>
+        <v>5.63</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="S32" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.13</v>
+        <v>1.96</v>
       </c>
       <c r="U32" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="V32" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="W32" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="X32" t="n">
-        <v>2.85</v>
+        <v>3.28</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.75</v>
+        <v>8</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.04</v>
+        <v>2.7</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.91</v>
+        <v>2.35</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.35</v>
+        <v>4.55</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="AI32" t="n">
-        <v>6.25</v>
+        <v>9</v>
       </c>
       <c r="AJ32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BF32" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1.13</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>5.18</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.4</v>
+        <v>2.97</v>
       </c>
       <c r="R9" t="n">
-        <v>6.25</v>
+        <v>5.81</v>
       </c>
       <c r="S9" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="T9" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="U9" t="n">
-        <v>7.95</v>
+        <v>7.37</v>
       </c>
       <c r="V9" t="n">
-        <v>1.54</v>
+        <v>1.7</v>
       </c>
       <c r="W9" t="n">
-        <v>2.31</v>
+        <v>2.02</v>
       </c>
       <c r="X9" t="n">
-        <v>3.42</v>
+        <v>4.33</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AA9" t="n">
         <v>1.03</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.05</v>
       </c>
-      <c r="AC9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AE9" t="n">
+      <c r="AI9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BD9" t="n">
         <v>2.5</v>
       </c>
-      <c r="AF9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX9" t="n">
+      <c r="BE9" t="n">
         <v>1.28</v>
       </c>
-      <c r="AY9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.44</v>
-      </c>
       <c r="BF9" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>5.81</v>
+        <v>6.25</v>
       </c>
       <c r="S10" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="T10" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="U10" t="n">
-        <v>7.37</v>
+        <v>7.95</v>
       </c>
       <c r="V10" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="W10" t="n">
-        <v>2.02</v>
+        <v>2.31</v>
       </c>
       <c r="X10" t="n">
-        <v>4.33</v>
+        <v>3.42</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA10" t="n">
         <v>1.03</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.02</v>
+        <v>2.46</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.25</v>
+        <v>2.5</v>
       </c>
       <c r="AF10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX10" t="n">
         <v>1.28</v>
       </c>
-      <c r="AG10" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AM10" t="n">
+      <c r="AY10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="BB10" t="n">
         <v>1.31</v>
       </c>
-      <c r="AN10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
+      <c r="BC10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BE10" t="n">
         <v>1.44</v>
       </c>
-      <c r="BC10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.28</v>
-      </c>
       <c r="BF10" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2574,28 +2574,28 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.42</v>
+        <v>3.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.97</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S11" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="U11" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W11" t="n">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="X11" t="n">
         <v>3.44</v>
@@ -2607,7 +2607,7 @@
         <v>9.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AB11" t="n">
         <v>1.05</v>
@@ -2622,16 +2622,16 @@
         <v>2.54</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="AG11" t="n">
-        <v>4.87</v>
+        <v>4.65</v>
       </c>
       <c r="AH11" t="n">
         <v>1.12</v>
       </c>
       <c r="AI11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ11" t="n">
         <v>1</v>
@@ -2643,10 +2643,10 @@
         <v>1.66</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>3.03</v>
       </c>
       <c r="R13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BA13" t="n">
         <v>2.8</v>
       </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.03</v>
+        <v>3.3</v>
       </c>
       <c r="R15" t="n">
-        <v>4.5</v>
+        <v>2.37</v>
       </c>
       <c r="S15" t="n">
-        <v>2.46</v>
+        <v>3.05</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="U15" t="n">
-        <v>5.8</v>
+        <v>2.9</v>
       </c>
       <c r="V15" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>2.32</v>
+        <v>2.91</v>
       </c>
       <c r="X15" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.32</v>
       </c>
-      <c r="Z15" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AI15" t="n">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.66</v>
+        <v>2.18</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.98</v>
+        <v>1.4</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.79</v>
+        <v>1.31</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.75</v>
+        <v>1.74</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.14</v>
+        <v>1.95</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.5</v>
+        <v>2.48</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.48</v>
+        <v>4.39</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.89</v>
+        <v>2.95</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.27</v>
+        <v>1.76</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.13</v>
+        <v>1.45</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,112 +3559,112 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="S16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.79</v>
+        <v>2.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4347,25 +4347,25 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q20" t="n">
         <v>3.2</v>
       </c>
       <c r="R20" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="S20" t="n">
         <v>2.64</v>
       </c>
       <c r="T20" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="U20" t="n">
         <v>4.56</v>
       </c>
       <c r="V20" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W20" t="n">
         <v>2.54</v>
@@ -4383,7 +4383,7 @@
         <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC20" t="n">
         <v>1.33</v>
@@ -4401,16 +4401,16 @@
         <v>3.58</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AI20" t="n">
         <v>7.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AL20" t="n">
         <v>1.83</v>
@@ -4431,16 +4431,16 @@
         <v>1.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="AV20" t="n">
         <v>2.64</v>
@@ -4449,16 +4449,16 @@
         <v>2.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="BB20" t="n">
         <v>1.26</v>
@@ -4467,7 +4467,7 @@
         <v>2.31</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="BE20" t="n">
         <v>1.56</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R21" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T21" t="n">
         <v>2</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="U21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4.18</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BD21" t="n">
         <v>3.1</v>
       </c>
-      <c r="R21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U21" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="V21" t="n">
+      <c r="BE21" t="n">
         <v>1.52</v>
       </c>
-      <c r="W21" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.44</v>
-      </c>
       <c r="BF21" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R22" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="T22" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U22" t="n">
-        <v>5.41</v>
+        <v>5.1</v>
       </c>
       <c r="V22" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="W22" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="X22" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="Y22" t="n">
         <v>1.28</v>
       </c>
       <c r="Z22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AC22" t="n">
         <v>1.42</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.69</v>
+        <v>2.49</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="AG22" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AI22" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AK22" t="n">
         <v>2.05</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AQ22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY22" t="n">
         <v>1.3</v>
       </c>
-      <c r="AR22" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AZ22" t="n">
-        <v>1.14</v>
+        <v>1.66</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.3</v>
+        <v>3.08</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.22</v>
+        <v>2.99</v>
       </c>
       <c r="BE22" t="n">
         <v>1.48</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="R23" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="S23" t="n">
-        <v>3.14</v>
+        <v>2.45</v>
       </c>
       <c r="T23" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="U23" t="n">
-        <v>4.13</v>
+        <v>5.2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="W23" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="X23" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="AA23" t="n">
         <v>1.01</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.92</v>
+        <v>4.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AI23" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>1.14</v>
       </c>
-      <c r="AQ23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.62</v>
-      </c>
       <c r="BA23" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="BB23" t="n">
         <v>1.29</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="X24" t="n">
         <v>3.25</v>
       </c>
-      <c r="R24" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.04</v>
-      </c>
       <c r="Y24" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z24" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC24" t="n">
         <v>1.35</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AE24" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS24" t="n">
         <v>2.16</v>
       </c>
-      <c r="AF24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AT24" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.28</v>
+        <v>3.72</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.9</v>
+        <v>2.49</v>
       </c>
       <c r="BB24" t="n">
         <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="S25" t="n">
-        <v>2.62</v>
+        <v>2.91</v>
       </c>
       <c r="T25" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="U25" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="V25" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>2.77</v>
+        <v>2.47</v>
       </c>
       <c r="X25" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AD25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AT25" t="n">
         <v>3.2</v>
       </c>
-      <c r="AE25" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
+      <c r="AU25" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY25" t="n">
         <v>1.26</v>
       </c>
-      <c r="AQ25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AZ25" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.49</v>
+        <v>2.9</v>
       </c>
       <c r="BB25" t="n">
         <v>1.25</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="BD25" t="n">
         <v>3.42</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,34 +5529,34 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
-        <v>5.5</v>
+        <v>3.85</v>
       </c>
       <c r="S26" t="n">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="T26" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U26" t="n">
-        <v>5.6</v>
+        <v>4.15</v>
       </c>
       <c r="V26" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W26" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="X26" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z26" t="n">
         <v>7.4</v>
@@ -5565,97 +5565,97 @@
         <v>1.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AH26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM26" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI26" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AN26" t="n">
-        <v>2.36</v>
+        <v>1.94</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="AT26" t="n">
         <v>2.83</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AX26" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ26" t="n">
         <v>1.57</v>
       </c>
-      <c r="AY26" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BA26" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.42</v>
+        <v>3.66</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,34 +5726,34 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.79</v>
+        <v>1.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="S27" t="n">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="T27" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U27" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="V27" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W27" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="X27" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z27" t="n">
         <v>7.4</v>
@@ -5762,97 +5762,97 @@
         <v>1.03</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="AE27" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AI27" t="n">
-        <v>6.7</v>
+        <v>6.95</v>
       </c>
       <c r="AJ27" t="n">
         <v>1.04</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AM27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
         <v>1.22</v>
       </c>
-      <c r="AN27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AQ27" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.83</v>
+        <v>2.65</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5923,16 +5923,16 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="Q28" t="n">
         <v>3.15</v>
       </c>
       <c r="R28" t="n">
-        <v>2.89</v>
+        <v>2.91</v>
       </c>
       <c r="S28" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="T28" t="n">
         <v>1.95</v>
@@ -5941,16 +5941,16 @@
         <v>3.56</v>
       </c>
       <c r="V28" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W28" t="n">
-        <v>2.71</v>
+        <v>2.53</v>
       </c>
       <c r="X28" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z28" t="n">
         <v>7.5</v>
@@ -5980,7 +5980,7 @@
         <v>1.18</v>
       </c>
       <c r="AI28" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="AJ28" t="n">
         <v>1.02</v>
@@ -5989,13 +5989,13 @@
         <v>1.85</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6031,25 +6031,25 @@
         <v>1.34</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="BA28" t="n">
         <v>2.52</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BC28" t="n">
         <v>2.34</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6120,22 +6120,22 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="R29" t="n">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="S29" t="n">
-        <v>4.78</v>
+        <v>4.84</v>
       </c>
       <c r="T29" t="n">
         <v>1.89</v>
       </c>
       <c r="U29" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="V29" t="n">
         <v>1.53</v>
@@ -6144,31 +6144,31 @@
         <v>2.32</v>
       </c>
       <c r="X29" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z29" t="n">
         <v>8.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AB29" t="n">
         <v>1.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.46</v>
+        <v>2.67</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AG29" t="n">
         <v>4.75</v>
@@ -6177,28 +6177,28 @@
         <v>1.14</v>
       </c>
       <c r="AI29" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AQ29" t="n">
         <v>1.46</v>
@@ -6231,16 +6231,16 @@
         <v>2.25</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.83</v>
+        <v>2.21</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BC29" t="n">
         <v>2.56</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="BE29" t="n">
         <v>1.44</v>
@@ -6326,25 +6326,25 @@
         <v>4</v>
       </c>
       <c r="S30" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="U30" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="V30" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W30" t="n">
         <v>2.66</v>
       </c>
       <c r="X30" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z30" t="n">
         <v>6.75</v>
@@ -6353,43 +6353,43 @@
         <v>1.04</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.04</v>
+        <v>3.45</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AG30" t="n">
         <v>3.35</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AI30" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6398,31 +6398,31 @@
         <v>1.14</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="AS30" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="AU30" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AV30" t="n">
         <v>2.85</v>
       </c>
       <c r="AW30" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AX30" t="n">
         <v>1.72</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AZ30" t="n">
         <v>1.35</v>
@@ -6431,13 +6431,13 @@
         <v>3.6</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.8</v>
+        <v>3.44</v>
       </c>
       <c r="BE30" t="n">
         <v>1.62</v>
@@ -6514,7 +6514,7 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q31" t="n">
         <v>3.4</v>
@@ -6523,22 +6523,22 @@
         <v>5</v>
       </c>
       <c r="S31" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="T31" t="n">
         <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>6.21</v>
+        <v>5.2</v>
       </c>
       <c r="V31" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W31" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="X31" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="Y31" t="n">
         <v>1.3</v>
@@ -6547,28 +6547,28 @@
         <v>7.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AC31" t="n">
         <v>1.36</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AE31" t="n">
         <v>2.25</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG31" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AI31" t="n">
         <v>8.5</v>
@@ -6598,10 +6598,10 @@
         <v>1.34</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AS31" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AT31" t="n">
         <v>2.56</v>
@@ -6619,7 +6619,7 @@
         <v>1.72</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AZ31" t="n">
         <v>1.41</v>
@@ -6628,19 +6628,19 @@
         <v>5.63</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="BC31" t="n">
         <v>2.39</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6723,31 +6723,31 @@
         <v>2.5</v>
       </c>
       <c r="T32" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="U32" t="n">
         <v>5</v>
       </c>
       <c r="V32" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W32" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="X32" t="n">
         <v>3.28</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z32" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AC32" t="n">
         <v>1.38</v>
@@ -6789,13 +6789,13 @@
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AQ32" t="n">
         <v>1.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="AS32" t="n">
         <v>2.29</v>
@@ -6807,7 +6807,7 @@
         <v>3.42</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="AW32" t="n">
         <v>1.88</v>
@@ -6831,7 +6831,7 @@
         <v>2.32</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="BE32" t="n">
         <v>1.48</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>5.18</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="R9" t="n">
-        <v>5.81</v>
+        <v>6.25</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="T9" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>7.37</v>
+        <v>6.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="X9" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AA9" t="n">
         <v>1.03</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH9" t="n">
         <v>1.1</v>
       </c>
-      <c r="AC9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AF9" t="n">
+      <c r="AI9" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX9" t="n">
         <v>1.28</v>
       </c>
-      <c r="AG9" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AM9" t="n">
+      <c r="AY9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="BB9" t="n">
         <v>1.31</v>
       </c>
-      <c r="AN9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.44</v>
-      </c>
       <c r="BC9" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.5</v>
+        <v>3.02</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R10" t="n">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.18</v>
+        <v>2.79</v>
       </c>
       <c r="T10" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="U10" t="n">
-        <v>7.95</v>
+        <v>5.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="W10" t="n">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="X10" t="n">
-        <v>3.42</v>
+        <v>4.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="Z10" t="n">
         <v>10</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BF10" t="n">
         <v>1.05</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.08</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="R12" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.03</v>
+        <v>3.3</v>
       </c>
       <c r="R13" t="n">
-        <v>4.5</v>
+        <v>2.37</v>
       </c>
       <c r="S13" t="n">
-        <v>2.46</v>
+        <v>3.05</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="U13" t="n">
-        <v>5.8</v>
+        <v>2.9</v>
       </c>
       <c r="V13" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>2.32</v>
+        <v>2.91</v>
       </c>
       <c r="X13" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.32</v>
       </c>
-      <c r="Z13" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AI13" t="n">
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.66</v>
+        <v>2.18</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.98</v>
+        <v>1.4</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.79</v>
+        <v>1.31</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.75</v>
+        <v>1.74</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.14</v>
+        <v>1.95</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.5</v>
+        <v>2.48</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.48</v>
+        <v>4.39</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.89</v>
+        <v>2.95</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.27</v>
+        <v>1.76</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.13</v>
+        <v>1.45</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="S14" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.18</v>
+        <v>1.65</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="AG14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.5</v>
+        <v>1.86</v>
       </c>
       <c r="Q15" t="n">
         <v>3.3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.37</v>
+        <v>5.15</v>
       </c>
       <c r="S15" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AS15" t="n">
         <v>3.05</v>
       </c>
-      <c r="T15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U15" t="n">
+      <c r="AT15" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BD15" t="n">
         <v>2.9</v>
       </c>
-      <c r="V15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BE15" t="n">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD16" t="n">
         <v>3.4</v>
       </c>
-      <c r="R16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3756,7 +3756,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
         <v>3.3</v>
@@ -3765,13 +3765,13 @@
         <v>3.3</v>
       </c>
       <c r="S17" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="T17" t="n">
         <v>2.16</v>
       </c>
       <c r="U17" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="V17" t="n">
         <v>1.34</v>
@@ -3795,10 +3795,10 @@
         <v>1.05</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="AE17" t="n">
         <v>1.75</v>
@@ -3807,19 +3807,19 @@
         <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AI17" t="n">
         <v>4.65</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AL17" t="n">
         <v>2.19</v>
@@ -3828,43 +3828,43 @@
         <v>1.3</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.2</v>
+        <v>3.58</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.38</v>
+        <v>2.53</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="BA17" t="n">
         <v>3.2</v>
@@ -3873,13 +3873,13 @@
         <v>1.17</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="BD17" t="n">
         <v>4.25</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="BF17" t="n">
         <v>1.22</v>
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="S30" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U30" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="V30" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="W30" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="X30" t="n">
-        <v>2.8</v>
+        <v>3.28</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="Z30" t="n">
-        <v>6.75</v>
+        <v>8.5</v>
       </c>
       <c r="AA30" t="n">
         <v>1.04</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="AD30" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BD30" t="n">
         <v>3.45</v>
       </c>
-      <c r="AE30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY30" t="n">
+      <c r="BE30" t="n">
         <v>1.48</v>
       </c>
-      <c r="AZ30" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>1.62</v>
-      </c>
       <c r="BF30" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R32" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="S32" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="T32" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U32" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="V32" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="W32" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="X32" t="n">
-        <v>3.28</v>
+        <v>2.8</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>8.5</v>
+        <v>6.75</v>
       </c>
       <c r="AA32" t="n">
         <v>1.04</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.57</v>
+        <v>1.78</v>
       </c>
       <c r="AG32" t="n">
-        <v>4.55</v>
+        <v>3.35</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="AI32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.23</v>
+        <v>1.8</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AN32" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AR32" t="n">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.29</v>
+        <v>1.93</v>
       </c>
       <c r="AT32" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.42</v>
+        <v>3.9</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.46</v>
+        <v>2.85</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="BA32" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI32"/>
+  <dimension ref="A1:BI31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1195,34 +1195,34 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.62</v>
+        <v>3.73</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.37</v>
+        <v>3.26</v>
       </c>
       <c r="R4" t="n">
         <v>1.87</v>
       </c>
       <c r="S4" t="n">
-        <v>4.8</v>
+        <v>4.92</v>
       </c>
       <c r="T4" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U4" t="n">
-        <v>2.7</v>
+        <v>2.61</v>
       </c>
       <c r="V4" t="n">
         <v>1.53</v>
       </c>
       <c r="W4" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="X4" t="n">
         <v>3.82</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="Z4" t="n">
         <v>11</v>
@@ -1237,16 +1237,16 @@
         <v>1.51</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG4" t="n">
-        <v>5.65</v>
+        <v>5.7</v>
       </c>
       <c r="AH4" t="n">
         <v>1.08</v>
@@ -1261,13 +1261,13 @@
         <v>2.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AM4" t="n">
         <v>1.2</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1312,16 +1312,16 @@
         <v>1.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="BD4" t="n">
         <v>2.45</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2186,7 +2186,7 @@
         <v>3.4</v>
       </c>
       <c r="R9" t="n">
-        <v>6.25</v>
+        <v>6.44</v>
       </c>
       <c r="S9" t="n">
         <v>2.35</v>
@@ -2198,10 +2198,10 @@
         <v>6.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W9" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="X9" t="n">
         <v>3.3</v>
@@ -2213,7 +2213,7 @@
         <v>10</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB9" t="n">
         <v>1.06</v>
@@ -2222,7 +2222,7 @@
         <v>1.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AE9" t="n">
         <v>2.5</v>
@@ -2231,28 +2231,28 @@
         <v>1.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>4.5</v>
+        <v>5.25</v>
       </c>
       <c r="AH9" t="n">
         <v>1.1</v>
       </c>
       <c r="AI9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AK9" t="n">
         <v>2.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,13 +2294,13 @@
         <v>4.85</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BC9" t="n">
         <v>2.75</v>
       </c>
       <c r="BD9" t="n">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="BE9" t="n">
         <v>1.33</v>
@@ -2380,31 +2380,31 @@
         <v>1.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R10" t="n">
         <v>5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.79</v>
+        <v>2.67</v>
       </c>
       <c r="T10" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U10" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="V10" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="W10" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="X10" t="n">
         <v>4.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z10" t="n">
         <v>10</v>
@@ -2416,10 +2416,10 @@
         <v>1.12</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.48</v>
+        <v>1.69</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="AE10" t="n">
         <v>3.25</v>
@@ -2428,7 +2428,7 @@
         <v>1.29</v>
       </c>
       <c r="AG10" t="n">
-        <v>6.65</v>
+        <v>6.55</v>
       </c>
       <c r="AH10" t="n">
         <v>1.11</v>
@@ -2443,46 +2443,46 @@
         <v>2.3</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AM10" t="n">
         <v>1.09</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.94</v>
+        <v>5.22</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AZ10" t="n">
         <v>1.23</v>
@@ -2491,13 +2491,13 @@
         <v>6.38</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="BC10" t="n">
         <v>3.1</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BE10" t="n">
         <v>1.28</v>
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.63</v>
+        <v>3.25</v>
       </c>
       <c r="Q11" t="n">
         <v>2.8</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S11" t="n">
         <v>4.3</v>
@@ -2589,7 +2589,7 @@
         <v>1.87</v>
       </c>
       <c r="U11" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="V11" t="n">
         <v>1.53</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>1.86</v>
       </c>
       <c r="Q13" t="n">
         <v>3.3</v>
       </c>
       <c r="R13" t="n">
-        <v>2.37</v>
+        <v>5.15</v>
       </c>
       <c r="S13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AS13" t="n">
         <v>3.05</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U13" t="n">
+      <c r="AT13" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BD13" t="n">
         <v>2.9</v>
       </c>
-      <c r="V13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BE13" t="n">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,112 +3165,112 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>2.8</v>
+        <v>2.37</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AF14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW14" t="n">
         <v>2.2</v>
       </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,130 +3362,130 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>5.15</v>
+        <v>3.94</v>
       </c>
       <c r="S15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE15" t="n">
         <v>2.34</v>
       </c>
-      <c r="T15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U15" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.49</v>
-      </c>
       <c r="AF15" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AG15" t="n">
-        <v>4.75</v>
+        <v>3.76</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AI15" t="n">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
       <c r="AJ15" t="n">
         <v>1.03</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.75</v>
+        <v>1.84</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.05</v>
+        <v>2.36</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.06</v>
+        <v>3.14</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.5</v>
+        <v>3.34</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.93</v>
+        <v>2.39</v>
       </c>
       <c r="AW15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE15" t="n">
         <v>1.55</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.51</v>
       </c>
       <c r="BF15" t="n">
         <v>1.1</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>3.94</v>
+        <v>2.8</v>
       </c>
       <c r="S16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.34</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3703,12 +3703,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,134 +3756,134 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.91</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="R17" t="n">
-        <v>3.3</v>
+        <v>1.92</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4</v>
+        <v>5.95</v>
       </c>
       <c r="T17" t="n">
-        <v>2.16</v>
+        <v>1.84</v>
       </c>
       <c r="U17" t="n">
-        <v>3.85</v>
+        <v>2.54</v>
       </c>
       <c r="V17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
         <v>1.34</v>
       </c>
-      <c r="W17" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA17" t="n">
+      <c r="BC17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BF17" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.22</v>
-      </c>
       <c r="BG17" t="n">
         <v>0</v>
       </c>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>46113.6875</v>
+        <v>46113.66666666666</v>
       </c>
     </row>
     <row r="18">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46113.72916666666</v>
+        <v>46113.6875</v>
       </c>
     </row>
     <row r="19">
@@ -4097,27 +4097,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>6.5</v>
+        <v>1.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>4.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.07</v>
+        <v>1.66</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46113.72916666666</v>
+        <v>46113.75</v>
       </c>
     </row>
     <row r="20">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.98</v>
+        <v>2.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="R20" t="n">
-        <v>4.4</v>
+        <v>3.23</v>
       </c>
       <c r="S20" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="T20" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>4.56</v>
+        <v>3.7</v>
       </c>
       <c r="V20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC20" t="n">
         <v>1.4</v>
       </c>
-      <c r="W20" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AD20" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.58</v>
+        <v>4.14</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AI20" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AK20" t="n">
         <v>1.85</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AM20" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>1.31</v>
       </c>
-      <c r="AN20" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AR20" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.8</v>
+        <v>4.18</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.64</v>
+        <v>2.92</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="AX20" t="n">
         <v>1.71</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46113.75</v>
+        <v>46113.79166666666</v>
       </c>
     </row>
     <row r="21">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="R21" t="n">
-        <v>3.23</v>
+        <v>4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="U21" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W21" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="X21" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="Y21" t="n">
         <v>1.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AG21" t="n">
-        <v>4.14</v>
+        <v>4.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AI21" t="n">
         <v>9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AZ21" t="n">
         <v>1.14</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.71</v>
-      </c>
       <c r="BA21" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="BB21" t="n">
         <v>1.29</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
         <v>3.2</v>
       </c>
       <c r="R23" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="S23" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="T23" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="U23" t="n">
-        <v>5.2</v>
+        <v>3.66</v>
       </c>
       <c r="V23" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="W23" t="n">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="X23" t="n">
         <v>3.25</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="Z23" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.69</v>
+        <v>2.94</v>
       </c>
       <c r="AE23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC23" t="n">
         <v>2.3</v>
       </c>
-      <c r="AF23" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>2.44</v>
-      </c>
       <c r="BD23" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46113.79166666666</v>
+        <v>46113.8125</v>
       </c>
     </row>
     <row r="24">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>3.02</v>
       </c>
       <c r="R24" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="S24" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="U24" t="n">
-        <v>3.66</v>
+        <v>3.8</v>
       </c>
       <c r="V24" t="n">
         <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="X24" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AG24" t="n">
-        <v>4</v>
+        <v>3.54</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AI24" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="AJ24" t="n">
         <v>1.06</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.16</v>
+        <v>2.39</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.83</v>
+        <v>3.2</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.72</v>
+        <v>3.28</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.49</v>
+        <v>2.9</v>
       </c>
       <c r="BB24" t="n">
         <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="BD24" t="n">
         <v>3.42</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="Q25" t="n">
         <v>3.2</v>
       </c>
       <c r="R25" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="S25" t="n">
-        <v>2.91</v>
+        <v>2.38</v>
       </c>
       <c r="T25" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="U25" t="n">
-        <v>3.8</v>
+        <v>4.79</v>
       </c>
       <c r="V25" t="n">
         <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>2.47</v>
+        <v>2.77</v>
       </c>
       <c r="X25" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="Y25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AY25" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AZ25" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.42</v>
+        <v>3.66</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46113.8125</v>
+        <v>46113.83333333334</v>
       </c>
     </row>
     <row r="26">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,31 +5529,31 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="R26" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="S26" t="n">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="T26" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U26" t="n">
-        <v>4.15</v>
+        <v>5.8</v>
       </c>
       <c r="V26" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W26" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="X26" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Y26" t="n">
         <v>1.36</v>
@@ -5565,97 +5565,97 @@
         <v>1.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="AE26" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK26" t="n">
         <v>2</v>
       </c>
-      <c r="AF26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG26" t="n">
+      <c r="AL26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA26" t="n">
         <v>3.6</v>
       </c>
-      <c r="AH26" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AX26" t="n">
+      <c r="BB26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BE26" t="n">
         <v>1.59</v>
       </c>
-      <c r="AY26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>1.62</v>
-      </c>
       <c r="BF26" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.45</v>
+        <v>2.41</v>
       </c>
       <c r="Q27" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="R27" t="n">
-        <v>5.2</v>
+        <v>2.91</v>
       </c>
       <c r="S27" t="n">
-        <v>2.13</v>
+        <v>3.15</v>
       </c>
       <c r="T27" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="U27" t="n">
-        <v>5.6</v>
+        <v>3.58</v>
       </c>
       <c r="V27" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="W27" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="X27" t="n">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="Z27" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.14</v>
+        <v>2.8</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.07</v>
+        <v>2.26</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.75</v>
+        <v>4.14</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="AI27" t="n">
-        <v>6.95</v>
+        <v>8</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AK27" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.36</v>
+        <v>1.51</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5807,52 +5807,52 @@
         <v>1.22</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="AT27" t="n">
         <v>2.65</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AY27" t="n">
         <v>1.41</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="BA27" t="n">
-        <v>3.6</v>
+        <v>2.52</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46113.83333333334</v>
+        <v>46113.85416666666</v>
       </c>
     </row>
     <row r="28">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,134 +5923,134 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.38</v>
+        <v>3.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.15</v>
+        <v>3.06</v>
       </c>
       <c r="R28" t="n">
-        <v>2.91</v>
+        <v>1.96</v>
       </c>
       <c r="S28" t="n">
-        <v>3.15</v>
+        <v>4.84</v>
       </c>
       <c r="T28" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="U28" t="n">
-        <v>3.56</v>
+        <v>2.78</v>
       </c>
       <c r="V28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ28" t="n">
         <v>1.46</v>
       </c>
-      <c r="W28" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB28" t="n">
+      <c r="AR28" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BF28" t="n">
         <v>1.07</v>
       </c>
-      <c r="AC28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>1.09</v>
-      </c>
       <c r="BG28" t="n">
         <v>0</v>
       </c>
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46113.85416666666</v>
+        <v>46113.875</v>
       </c>
     </row>
     <row r="29">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>4</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U29" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA29" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q29" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="S29" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="X29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ29" t="n">
+      <c r="BB29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC29" t="n">
         <v>2.25</v>
       </c>
-      <c r="BA29" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>2.56</v>
-      </c>
       <c r="BD29" t="n">
-        <v>2.99</v>
+        <v>3.44</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>46113.875</v>
+        <v>46113.89583333334</v>
       </c>
     </row>
     <row r="30">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.91</v>
+        <v>1.67</v>
       </c>
       <c r="Q30" t="n">
         <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="S30" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="T30" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="V30" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W30" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="X30" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AB30" t="n">
         <v>1.05</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AG30" t="n">
-        <v>4.55</v>
+        <v>3.94</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AI30" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AM30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ30" t="n">
         <v>1.34</v>
       </c>
-      <c r="AN30" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AR30" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.29</v>
+        <v>1.98</v>
       </c>
       <c r="AT30" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BD30" t="n">
         <v>3</v>
       </c>
-      <c r="AU30" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>3.45</v>
-      </c>
       <c r="BE30" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="Q31" t="n">
         <v>3.4</v>
       </c>
       <c r="R31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U31" t="n">
         <v>5</v>
       </c>
-      <c r="S31" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2</v>
-      </c>
-      <c r="U31" t="n">
-        <v>5.2</v>
-      </c>
       <c r="V31" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W31" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="X31" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z31" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AB31" t="n">
         <v>1.05</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AD31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BA31" t="n">
         <v>2.8</v>
       </c>
-      <c r="AE31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>5.63</v>
-      </c>
       <c r="BB31" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.39</v>
+        <v>2.32</v>
       </c>
       <c r="BD31" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6649,203 +6649,6 @@
         <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
-        <v>46113.89583333334</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>CRB</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Avaí</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R32" t="n">
-        <v>4</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U32" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W32" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI32" s="3" t="n">
         <v>46113.89583333334</v>
       </c>
     </row>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R9" t="n">
-        <v>6.44</v>
+        <v>5</v>
       </c>
       <c r="S9" t="n">
-        <v>2.35</v>
+        <v>2.67</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="U9" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="V9" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="W9" t="n">
-        <v>2.41</v>
+        <v>2.08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z9" t="n">
         <v>10</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AK9" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AW9" t="n">
         <v>1.44</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AX9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BE9" t="n">
         <v>1.28</v>
       </c>
-      <c r="AY9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BF9" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>5</v>
+        <v>6.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.67</v>
+        <v>2.35</v>
       </c>
       <c r="T10" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="W10" t="n">
-        <v>2.08</v>
+        <v>2.41</v>
       </c>
       <c r="X10" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
         <v>10</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AK10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AY10" t="n">
         <v>1.12</v>
       </c>
-      <c r="AC10" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AY10" t="n">
+      <c r="AZ10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BF10" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.05</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AE20" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="Y20" t="n">
+      <c r="AF20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY20" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z20" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AZ20" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.6</v>
+        <v>3.08</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="R21" t="n">
-        <v>4</v>
+        <v>3.23</v>
       </c>
       <c r="S21" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="T21" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="V21" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W21" t="n">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="X21" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="Y21" t="n">
         <v>1.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="AG21" t="n">
-        <v>4.33</v>
+        <v>4.14</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AI21" t="n">
         <v>9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK21" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.92</v>
+        <v>1.52</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.94</v>
+        <v>2.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.47</v>
+        <v>2.58</v>
       </c>
       <c r="AU21" t="n">
-        <v>4.5</v>
+        <v>4.18</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.14</v>
+        <v>1.71</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="BB21" t="n">
         <v>1.29</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.44</v>
+        <v>2.34</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="Q22" t="n">
         <v>3.2</v>
@@ -4750,124 +4750,124 @@
         <v>4</v>
       </c>
       <c r="S22" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="T22" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U22" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="W22" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="X22" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z22" t="n">
         <v>9</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="AG22" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AI22" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AK22" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AM22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
         <v>1.15</v>
       </c>
-      <c r="AN22" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AQ22" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.04</v>
+        <v>1.48</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.27</v>
+        <v>1.94</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.15</v>
+        <v>2.47</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.46</v>
+        <v>4.5</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.45</v>
+        <v>2.97</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.66</v>
+        <v>1.14</v>
       </c>
       <c r="BA22" t="n">
-        <v>3.08</v>
+        <v>4.3</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="BE22" t="n">
         <v>1.48</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="R25" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="S25" t="n">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="T25" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="U25" t="n">
-        <v>4.79</v>
+        <v>5.8</v>
       </c>
       <c r="V25" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W25" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="X25" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="Z25" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="AA25" t="n">
         <v>1.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.24</v>
+        <v>3.14</v>
       </c>
       <c r="AE25" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK25" t="n">
         <v>2</v>
       </c>
-      <c r="AF25" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG25" t="n">
+      <c r="AL25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BA25" t="n">
         <v>3.6</v>
       </c>
-      <c r="AH25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>6.64</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AX25" t="n">
+      <c r="BB25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BE25" t="n">
         <v>1.59</v>
       </c>
-      <c r="AY25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.62</v>
-      </c>
       <c r="BF25" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
-        <v>5.2</v>
+        <v>3.85</v>
       </c>
       <c r="S26" t="n">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="T26" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="U26" t="n">
-        <v>5.8</v>
+        <v>4.79</v>
       </c>
       <c r="V26" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W26" t="n">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="X26" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z26" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="AA26" t="n">
         <v>1.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.14</v>
+        <v>3.24</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="AH26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BB26" t="n">
         <v>1.22</v>
       </c>
-      <c r="AI26" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BC26" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.42</v>
+        <v>3.66</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,79 +6120,79 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S29" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T29" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="V29" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W29" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="X29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD29" t="n">
         <v>2.8</v>
       </c>
-      <c r="Y29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC29" t="n">
+      <c r="AE29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM29" t="n">
         <v>1.27</v>
       </c>
-      <c r="AD29" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AN29" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6201,52 +6201,52 @@
         <v>1.14</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.9</v>
+        <v>4.22</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="AX29" t="n">
         <v>1.72</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="BA29" t="n">
-        <v>3.6</v>
+        <v>5.63</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S30" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AE30" t="n">
         <v>2</v>
       </c>
-      <c r="U30" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W30" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AF30" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.94</v>
+        <v>3.35</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AI30" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6398,52 +6398,52 @@
         <v>1.14</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="AU30" t="n">
-        <v>4.22</v>
+        <v>3.9</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="AW30" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AX30" t="n">
         <v>1.72</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="BA30" t="n">
-        <v>5.63</v>
+        <v>3.6</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="BD30" t="n">
-        <v>3</v>
+        <v>3.44</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R9" t="n">
-        <v>5</v>
+        <v>6.44</v>
       </c>
       <c r="S9" t="n">
-        <v>2.67</v>
+        <v>2.35</v>
       </c>
       <c r="T9" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="W9" t="n">
-        <v>2.08</v>
+        <v>2.41</v>
       </c>
       <c r="X9" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="Z9" t="n">
         <v>10</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AK9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AY9" t="n">
         <v>1.12</v>
       </c>
-      <c r="AC9" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AY9" t="n">
+      <c r="AZ9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BF9" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1.05</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="R10" t="n">
-        <v>6.44</v>
+        <v>5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.35</v>
+        <v>2.67</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="U10" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="V10" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="W10" t="n">
-        <v>2.41</v>
+        <v>2.08</v>
       </c>
       <c r="X10" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z10" t="n">
         <v>10</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AK10" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.08</v>
+        <v>1.75</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AW10" t="n">
         <v>1.44</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AX10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BE10" t="n">
         <v>1.28</v>
       </c>
-      <c r="AY10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BF10" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="Q11" t="n">
         <v>2.8</v>
@@ -2592,10 +2592,10 @@
         <v>2.91</v>
       </c>
       <c r="V11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W11" t="n">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="X11" t="n">
         <v>3.44</v>
@@ -2604,10 +2604,10 @@
         <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB11" t="n">
         <v>1.05</v>
@@ -2616,13 +2616,13 @@
         <v>1.48</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="AE11" t="n">
         <v>2.54</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="AG11" t="n">
         <v>4.65</v>
@@ -2646,7 +2646,7 @@
         <v>1.44</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>5.15</v>
+        <v>2.8</v>
       </c>
       <c r="S13" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>4.56</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.49</v>
+        <v>1.65</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>1.86</v>
       </c>
       <c r="Q14" t="n">
         <v>3.3</v>
       </c>
       <c r="R14" t="n">
-        <v>2.37</v>
+        <v>5.15</v>
       </c>
       <c r="S14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AS14" t="n">
         <v>3.05</v>
       </c>
-      <c r="T14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U14" t="n">
+      <c r="AT14" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BD14" t="n">
         <v>2.9</v>
       </c>
-      <c r="V14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BE14" t="n">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,112 +3559,112 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.8</v>
+        <v>2.37</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AF16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW16" t="n">
         <v>2.2</v>
       </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3756,31 +3756,31 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="R17" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="S17" t="n">
-        <v>5.95</v>
+        <v>4.92</v>
       </c>
       <c r="T17" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="U17" t="n">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="V17" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W17" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="X17" t="n">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="Y17" t="n">
         <v>1.19</v>
@@ -3792,43 +3792,43 @@
         <v>1.02</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AG17" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AI17" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ17" t="n">
         <v>1.02</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,16 +3870,16 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BF17" t="n">
         <v>1.08</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="R23" t="n">
         <v>3.3</v>
       </c>
       <c r="S23" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="U23" t="n">
-        <v>3.66</v>
+        <v>3.8</v>
       </c>
       <c r="V23" t="n">
         <v>1.4</v>
       </c>
       <c r="W23" t="n">
-        <v>2.65</v>
+        <v>2.47</v>
       </c>
       <c r="X23" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.85</v>
+        <v>3.54</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AI23" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="AJ23" t="n">
         <v>1.06</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.16</v>
+        <v>2.39</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.72</v>
+        <v>3.28</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.49</v>
+        <v>2.9</v>
       </c>
       <c r="BB23" t="n">
         <v>1.25</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="BD23" t="n">
         <v>3.42</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="R24" t="n">
         <v>3.3</v>
       </c>
       <c r="S24" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="T24" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="U24" t="n">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="V24" t="n">
         <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="X24" t="n">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="Z24" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AI24" t="n">
         <v>8</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>7.3</v>
       </c>
       <c r="AJ24" t="n">
         <v>1.06</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.39</v>
+        <v>2.16</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.28</v>
+        <v>3.72</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.9</v>
+        <v>2.49</v>
       </c>
       <c r="BB24" t="n">
         <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="BD24" t="n">
         <v>3.42</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.73</v>
+        <v>1.13</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.26</v>
+        <v>6.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.87</v>
+        <v>12.32</v>
       </c>
       <c r="S6" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.7</v>
+        <v>1.44</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.42</v>
+        <v>2.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.4</v>
+        <v>3.01</v>
       </c>
       <c r="R9" t="n">
-        <v>6.44</v>
+        <v>4.75</v>
       </c>
       <c r="S9" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="U9" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="V9" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="W9" t="n">
-        <v>2.41</v>
+        <v>2.1</v>
       </c>
       <c r="X9" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.28</v>
+        <v>1.15</v>
       </c>
       <c r="Z9" t="n">
         <v>10</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AK9" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.08</v>
+        <v>1.79</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AR9" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="AU9" t="n">
         <v>2.29</v>
       </c>
-      <c r="AS9" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.51</v>
-      </c>
       <c r="AV9" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.85</v>
+        <v>6.93</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.91</v>
+        <v>2.53</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>5</v>
+        <v>6.34</v>
       </c>
       <c r="S10" t="n">
-        <v>2.67</v>
+        <v>2.35</v>
       </c>
       <c r="T10" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="U10" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="W10" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="X10" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z10" t="n">
         <v>10</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AK10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AY10" t="n">
         <v>1.12</v>
       </c>
-      <c r="AC10" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AY10" t="n">
+      <c r="AZ10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BF10" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.05</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="Q11" t="n">
         <v>2.8</v>
@@ -2595,7 +2595,7 @@
         <v>1.55</v>
       </c>
       <c r="W11" t="n">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="X11" t="n">
         <v>3.44</v>
@@ -2604,10 +2604,10 @@
         <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AB11" t="n">
         <v>1.05</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R13" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BA13" t="n">
         <v>2.8</v>
       </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,130 +3165,130 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>5.15</v>
+        <v>3.94</v>
       </c>
       <c r="S14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE14" t="n">
         <v>2.34</v>
       </c>
-      <c r="T14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U14" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.49</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AG14" t="n">
-        <v>4.75</v>
+        <v>3.76</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AI14" t="n">
-        <v>9.5</v>
+        <v>6.5</v>
       </c>
       <c r="AJ14" t="n">
         <v>1.03</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.81</v>
+        <v>1.57</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.75</v>
+        <v>1.84</v>
       </c>
       <c r="AS14" t="n">
-        <v>3.05</v>
+        <v>2.36</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.06</v>
+        <v>3.14</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.5</v>
+        <v>3.34</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.93</v>
+        <v>2.39</v>
       </c>
       <c r="AW14" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BE14" t="n">
         <v>1.55</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.51</v>
       </c>
       <c r="BF14" t="n">
         <v>1.1</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>2.65</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="R15" t="n">
-        <v>3.94</v>
+        <v>2.35</v>
       </c>
       <c r="S15" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="T15" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="U15" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="V15" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="X15" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK15" t="n">
+      <c r="AR15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS15" t="n">
         <v>1.95</v>
       </c>
-      <c r="AL15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.36</v>
-      </c>
       <c r="AT15" t="n">
-        <v>3.14</v>
+        <v>2.48</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.34</v>
+        <v>4.39</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.39</v>
+        <v>2.95</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,112 +3559,112 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>2.37</v>
+        <v>2.8</v>
       </c>
       <c r="S16" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.74</v>
+        <v>2.2</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="Q17" t="n">
         <v>3.05</v>
       </c>
       <c r="R17" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="S17" t="n">
         <v>4.92</v>
@@ -3780,7 +3780,7 @@
         <v>2.3</v>
       </c>
       <c r="X17" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="Y17" t="n">
         <v>1.19</v>
@@ -3795,34 +3795,34 @@
         <v>1.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="AF17" t="n">
         <v>1.39</v>
       </c>
       <c r="AG17" t="n">
-        <v>5.5</v>
+        <v>5.45</v>
       </c>
       <c r="AH17" t="n">
         <v>1.08</v>
       </c>
       <c r="AI17" t="n">
-        <v>9.300000000000001</v>
+        <v>12</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AM17" t="n">
         <v>1.27</v>
@@ -3834,34 +3834,34 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>6.74</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
@@ -4150,16 +4150,16 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="R19" t="n">
         <v>4.4</v>
       </c>
       <c r="S19" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
         <v>2.05</v>
@@ -4180,7 +4180,7 @@
         <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>7.2</v>
+        <v>8.5</v>
       </c>
       <c r="AA19" t="n">
         <v>1.03</v>
@@ -4204,16 +4204,16 @@
         <v>3.58</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AI19" t="n">
-        <v>7.5</v>
+        <v>6.85</v>
       </c>
       <c r="AJ19" t="n">
         <v>1.05</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AL19" t="n">
         <v>1.83</v>
@@ -4228,34 +4228,34 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.98</v>
+        <v>2.11</v>
       </c>
       <c r="AT19" t="n">
         <v>2.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="AZ19" t="n">
         <v>1.6</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,34 +4347,34 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R20" t="n">
         <v>4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U20" t="n">
-        <v>5.1</v>
+        <v>5.15</v>
       </c>
       <c r="V20" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="W20" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="X20" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
         <v>9</v>
@@ -4383,97 +4383,97 @@
         <v>1.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AG20" t="n">
-        <v>4.75</v>
+        <v>4.15</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AI20" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AM20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
         <v>1.15</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AQ20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AX20" t="n">
         <v>1.76</v>
       </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AY20" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.66</v>
+        <v>1.12</v>
       </c>
       <c r="BA20" t="n">
-        <v>3.08</v>
+        <v>4.3</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="BE20" t="n">
         <v>1.48</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4544,25 +4544,25 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q21" t="n">
         <v>2.7</v>
       </c>
       <c r="R21" t="n">
-        <v>3.23</v>
+        <v>3.28</v>
       </c>
       <c r="S21" t="n">
-        <v>2.88</v>
+        <v>3.12</v>
       </c>
       <c r="T21" t="n">
         <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>3.7</v>
+        <v>4.08</v>
       </c>
       <c r="V21" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W21" t="n">
         <v>2.36</v>
@@ -4601,19 +4601,19 @@
         <v>1.18</v>
       </c>
       <c r="AI21" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK21" t="n">
         <v>1.85</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AN21" t="n">
         <v>1.52</v>
@@ -4622,37 +4622,37 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="AU21" t="n">
-        <v>4.18</v>
+        <v>4.34</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="BA21" t="n">
         <v>2.6</v>
@@ -4661,16 +4661,16 @@
         <v>1.29</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BD21" t="n">
         <v>3.1</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="S22" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="T22" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="U22" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="V22" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W22" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="X22" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z22" t="n">
         <v>9</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AC22" t="n">
         <v>1.43</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.69</v>
+        <v>2.46</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AF22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AX22" t="n">
         <v>1.59</v>
       </c>
-      <c r="AG22" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AY22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="BE22" t="n">
         <v>1.44</v>
       </c>
-      <c r="AZ22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.48</v>
-      </c>
       <c r="BF22" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="R23" t="n">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="S23" t="n">
-        <v>2.91</v>
+        <v>2.79</v>
       </c>
       <c r="T23" t="n">
-        <v>1.89</v>
+        <v>2.09</v>
       </c>
       <c r="U23" t="n">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="V23" t="n">
         <v>1.4</v>
       </c>
       <c r="W23" t="n">
-        <v>2.47</v>
+        <v>2.73</v>
       </c>
       <c r="X23" t="n">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z23" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.54</v>
+        <v>3.85</v>
       </c>
       <c r="AH23" t="n">
         <v>1.27</v>
       </c>
       <c r="AI23" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.39</v>
+        <v>2.15</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.2</v>
+        <v>2.78</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.28</v>
+        <v>3.52</v>
       </c>
       <c r="AV23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC23" t="n">
         <v>2.34</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>2.25</v>
       </c>
       <c r="BD23" t="n">
         <v>3.42</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R24" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="S24" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="U24" t="n">
-        <v>3.66</v>
+        <v>4.3</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W24" t="n">
-        <v>2.65</v>
+        <v>2.82</v>
       </c>
       <c r="X24" t="n">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z24" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC24" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AD24" t="n">
         <v>2.94</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.85</v>
+        <v>3.62</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.85</v>
+        <v>3.07</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.49</v>
+        <v>2.9</v>
       </c>
       <c r="BB24" t="n">
         <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,130 +5332,130 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="S25" t="n">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="T25" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="U25" t="n">
-        <v>5.8</v>
+        <v>4.15</v>
       </c>
       <c r="V25" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="X25" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z25" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AA25" t="n">
         <v>1.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AI25" t="n">
-        <v>6.95</v>
+        <v>7.11</v>
       </c>
       <c r="AJ25" t="n">
         <v>1.04</v>
       </c>
       <c r="AK25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN25" t="n">
         <v>2</v>
       </c>
-      <c r="AL25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>2.22</v>
-      </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="AV25" t="n">
         <v>2.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="AX25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AZ25" t="n">
         <v>1.57</v>
       </c>
-      <c r="AY25" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BA25" t="n">
-        <v>3.6</v>
+        <v>2.95</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BF25" t="n">
         <v>1.12</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.8</v>
+        <v>1.59</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>3.86</v>
       </c>
       <c r="R26" t="n">
-        <v>3.85</v>
+        <v>5.7</v>
       </c>
       <c r="S26" t="n">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="T26" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="U26" t="n">
-        <v>4.79</v>
+        <v>5.8</v>
       </c>
       <c r="V26" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W26" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="X26" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="AA26" t="n">
         <v>1.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="AE26" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK26" t="n">
         <v>2</v>
       </c>
-      <c r="AF26" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AH26" t="n">
+      <c r="AL26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AM26" t="n">
         <v>1.25</v>
       </c>
-      <c r="AI26" t="n">
-        <v>6.64</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AN26" t="n">
-        <v>2.01</v>
+        <v>2.36</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.78</v>
+        <v>3.52</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.66</v>
+        <v>3.8</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5726,22 +5726,22 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="R27" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="S27" t="n">
         <v>3.15</v>
       </c>
       <c r="T27" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U27" t="n">
-        <v>3.58</v>
+        <v>3.55</v>
       </c>
       <c r="V27" t="n">
         <v>1.46</v>
@@ -5771,22 +5771,22 @@
         <v>2.8</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG27" t="n">
-        <v>4.14</v>
+        <v>3.9</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AI27" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK27" t="n">
         <v>1.86</v>
@@ -5798,7 +5798,7 @@
         <v>1.3</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5810,28 +5810,28 @@
         <v>1.41</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.84</v>
+        <v>3.52</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="AW27" t="n">
         <v>2.02</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AZ27" t="n">
         <v>1.9</v>
@@ -5840,16 +5840,16 @@
         <v>2.52</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="BD27" t="n">
         <v>3.34</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="BF27" t="n">
         <v>1.08</v>
@@ -5923,31 +5923,31 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="R28" t="n">
-        <v>1.96</v>
+        <v>2.09</v>
       </c>
       <c r="S28" t="n">
         <v>4.84</v>
       </c>
       <c r="T28" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="U28" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="V28" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W28" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="X28" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="Y28" t="n">
         <v>1.3</v>
@@ -5956,25 +5956,25 @@
         <v>8.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.67</v>
+        <v>2.46</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="AF28" t="n">
         <v>1.58</v>
       </c>
       <c r="AG28" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="AH28" t="n">
         <v>1.14</v>
@@ -5986,13 +5986,13 @@
         <v>1.01</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="AN28" t="n">
         <v>1.23</v>
@@ -6001,46 +6001,46 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AR28" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="AT28" t="n">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AZ28" t="n">
         <v>2.25</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="BB28" t="n">
         <v>1.33</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BD28" t="n">
         <v>2.99</v>
@@ -6123,25 +6123,25 @@
         <v>1.67</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R29" t="n">
-        <v>5</v>
+        <v>5.45</v>
       </c>
       <c r="S29" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="T29" t="n">
         <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>5.2</v>
+        <v>4.94</v>
       </c>
       <c r="V29" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W29" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="X29" t="n">
         <v>3.2</v>
@@ -6153,7 +6153,7 @@
         <v>7.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AB29" t="n">
         <v>1.05</v>
@@ -6165,7 +6165,7 @@
         <v>2.8</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AF29" t="n">
         <v>1.61</v>
@@ -6183,7 +6183,7 @@
         <v>1.02</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AL29" t="n">
         <v>1.65</v>
@@ -6198,31 +6198,31 @@
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AS29" t="n">
         <v>1.98</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="AU29" t="n">
-        <v>4.22</v>
+        <v>3.55</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AY29" t="n">
         <v>1.41</v>
@@ -6231,10 +6231,10 @@
         <v>1.41</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.63</v>
+        <v>5.95</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="BC29" t="n">
         <v>2.39</v>
@@ -6243,10 +6243,10 @@
         <v>3</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="S30" t="n">
         <v>2.3</v>
@@ -6344,7 +6344,7 @@
         <v>2.8</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
         <v>6.75</v>
@@ -6353,19 +6353,19 @@
         <v>1.04</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AC30" t="n">
         <v>1.27</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.45</v>
+        <v>3.04</v>
       </c>
       <c r="AE30" t="n">
         <v>2</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG30" t="n">
         <v>3.35</v>
@@ -6374,22 +6374,22 @@
         <v>1.29</v>
       </c>
       <c r="AI30" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AK30" t="n">
         <v>1.8</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AN30" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6419,7 +6419,7 @@
         <v>2.18</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AY30" t="n">
         <v>1.48</v>
@@ -6431,10 +6431,10 @@
         <v>3.6</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BD30" t="n">
         <v>3.44</v>
@@ -6514,10 +6514,10 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R31" t="n">
         <v>4.2</v>
@@ -6526,28 +6526,28 @@
         <v>2.5</v>
       </c>
       <c r="T31" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U31" t="n">
         <v>5</v>
       </c>
       <c r="V31" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W31" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="X31" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="Y31" t="n">
         <v>1.29</v>
       </c>
       <c r="Z31" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AB31" t="n">
         <v>1.05</v>
@@ -6556,19 +6556,19 @@
         <v>1.38</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG31" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AI31" t="n">
         <v>9</v>
@@ -6577,7 +6577,7 @@
         <v>1.05</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="AL31" t="n">
         <v>1.71</v>
@@ -6592,34 +6592,34 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AT31" t="n">
         <v>3.05</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AZ31" t="n">
         <v>1.52</v>
@@ -6637,7 +6637,7 @@
         <v>3.15</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BF31" t="n">
         <v>1.08</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.11</v>
+        <v>4.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.2</v>
+        <v>3.07</v>
       </c>
       <c r="R3" t="n">
-        <v>12</v>
+        <v>1.92</v>
       </c>
       <c r="S3" t="n">
-        <v>1.64</v>
+        <v>5.14</v>
       </c>
       <c r="T3" t="n">
-        <v>2.64</v>
+        <v>1.85</v>
       </c>
       <c r="U3" t="n">
-        <v>7.2</v>
+        <v>2.7</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="W3" t="n">
-        <v>3.6</v>
+        <v>2.19</v>
       </c>
       <c r="X3" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.58</v>
+        <v>1.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.8</v>
+        <v>2.08</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.46</v>
+        <v>2.75</v>
       </c>
       <c r="AF3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AR3" t="n">
         <v>2.38</v>
       </c>
-      <c r="AG3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.71</v>
+        <v>2.28</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>1.13</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="R4" t="n">
-        <v>2.79</v>
+        <v>12.32</v>
       </c>
       <c r="S4" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AF4" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>4.1</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.07</v>
+        <v>8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.92</v>
+        <v>1.13</v>
       </c>
       <c r="S5" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.75</v>
+        <v>1.3</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.41</v>
+        <v>3.4</v>
       </c>
       <c r="AG5" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.13</v>
+        <v>3.46</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>12.32</v>
+        <v>1.72</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>14</v>
+        <v>1.11</v>
       </c>
       <c r="Q7" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.13</v>
+        <v>12</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AF7" t="n">
-        <v>3.4</v>
+        <v>2.38</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.46</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.72</v>
+        <v>2.79</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.01</v>
+        <v>3.4</v>
       </c>
       <c r="R9" t="n">
-        <v>4.75</v>
+        <v>6.34</v>
       </c>
       <c r="S9" t="n">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="T9" t="n">
-        <v>1.79</v>
+        <v>1.95</v>
       </c>
       <c r="U9" t="n">
-        <v>5.7</v>
+        <v>6.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
         <v>10</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AK9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AY9" t="n">
         <v>1.12</v>
       </c>
-      <c r="AC9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>5.43</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.93</v>
+        <v>4.85</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.53</v>
+        <v>2.91</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>3.01</v>
       </c>
       <c r="R10" t="n">
-        <v>6.34</v>
+        <v>4.75</v>
       </c>
       <c r="S10" t="n">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="T10" t="n">
-        <v>1.95</v>
+        <v>1.79</v>
       </c>
       <c r="U10" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="V10" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="W10" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="X10" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z10" t="n">
         <v>10</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AK10" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.06</v>
+        <v>1.31</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.21</v>
+        <v>3.23</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.11</v>
+        <v>3.58</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.54</v>
+        <v>5.43</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.51</v>
+        <v>2.29</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.85</v>
+        <v>6.93</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.91</v>
+        <v>2.53</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>3.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
         <v>2.13</v>
@@ -2595,7 +2595,7 @@
         <v>1.55</v>
       </c>
       <c r="W11" t="n">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="X11" t="n">
         <v>3.44</v>
@@ -2604,16 +2604,16 @@
         <v>1.24</v>
       </c>
       <c r="Z11" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AB11" t="n">
         <v>1.05</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AD11" t="n">
         <v>2.58</v>
@@ -2622,7 +2622,7 @@
         <v>2.54</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
         <v>4.65</v>
@@ -2643,7 +2643,7 @@
         <v>1.66</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AN11" t="n">
         <v>1.3</v>
@@ -2652,40 +2652,40 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.38</v>
+        <v>3.08</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.77</v>
+        <v>4.47</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.65</v>
+        <v>2.53</v>
       </c>
       <c r="AV11" t="n">
         <v>1.92</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AX11" t="n">
         <v>1.29</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3.06</v>
+        <v>2.88</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="BB11" t="n">
         <v>1.33</v>
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="R12" t="n">
-        <v>3.15</v>
+        <v>3.01</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2968,22 +2968,22 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>5.15</v>
+        <v>4.75</v>
       </c>
       <c r="S13" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="U13" t="n">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="V13" t="n">
         <v>1.44</v>
@@ -3004,34 +3004,34 @@
         <v>1.06</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG13" t="n">
-        <v>4.75</v>
+        <v>3.85</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AI13" t="n">
-        <v>9.5</v>
+        <v>7.7</v>
       </c>
       <c r="AJ13" t="n">
         <v>1.03</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AL13" t="n">
         <v>1.65</v>
@@ -3046,34 +3046,34 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.06</v>
+        <v>3.95</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AX13" t="n">
         <v>1.33</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AZ13" t="n">
         <v>1.57</v>
@@ -3082,13 +3082,13 @@
         <v>2.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="BC13" t="n">
         <v>2.39</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="BE13" t="n">
         <v>1.51</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>2.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="R14" t="n">
-        <v>3.94</v>
+        <v>2.35</v>
       </c>
       <c r="S14" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="T14" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="U14" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="V14" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="X14" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>1.31</v>
       </c>
-      <c r="Z14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK14" t="n">
+      <c r="AR14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS14" t="n">
         <v>1.95</v>
       </c>
-      <c r="AL14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.36</v>
-      </c>
       <c r="AT14" t="n">
-        <v>3.14</v>
+        <v>2.48</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.34</v>
+        <v>4.39</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.39</v>
+        <v>2.95</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.48</v>
+        <v>1.76</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,22 +3314,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.65</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE15" t="n">
         <v>2.35</v>
       </c>
-      <c r="S15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z15" t="n">
+      <c r="AF15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI15" t="n">
         <v>6.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>5.9</v>
       </c>
       <c r="AJ15" t="n">
         <v>1.07</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="AL15" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.37</v>
+        <v>1.77</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.74</v>
+        <v>2.08</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.48</v>
+        <v>3.05</v>
       </c>
       <c r="AU15" t="n">
-        <v>4.39</v>
+        <v>3.22</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
         <v>3.4</v>
       </c>
       <c r="R16" t="n">
-        <v>2.8</v>
+        <v>3.71</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3953,7 +3953,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q18" t="n">
         <v>3.3</v>
@@ -3968,7 +3968,7 @@
         <v>2.16</v>
       </c>
       <c r="U18" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="V18" t="n">
         <v>1.34</v>
@@ -3995,7 +3995,7 @@
         <v>1.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="AE18" t="n">
         <v>1.75</v>
@@ -4031,40 +4031,40 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AT18" t="n">
         <v>2.92</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.58</v>
+        <v>3.36</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="BB18" t="n">
         <v>1.17</v>
@@ -4076,7 +4076,7 @@
         <v>4.25</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="BF18" t="n">
         <v>1.22</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,34 +4347,34 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="S20" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="T20" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="U20" t="n">
-        <v>5.15</v>
+        <v>5.1</v>
       </c>
       <c r="V20" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W20" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="X20" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z20" t="n">
         <v>9</v>
@@ -4383,97 +4383,97 @@
         <v>1.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AC20" t="n">
         <v>1.43</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.7</v>
+        <v>2.46</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AG20" t="n">
-        <v>4.15</v>
+        <v>4.75</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AI20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AK20" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.47</v>
+        <v>2.88</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.97</v>
+        <v>2.55</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.76</v>
+        <v>1.59</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.12</v>
+        <v>1.66</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>4</v>
+      </c>
+      <c r="S21" t="n">
         <v>2.4</v>
       </c>
-      <c r="Q21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="R21" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.12</v>
-      </c>
       <c r="T21" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="U21" t="n">
-        <v>4.08</v>
+        <v>5.15</v>
       </c>
       <c r="V21" t="n">
         <v>1.47</v>
       </c>
       <c r="W21" t="n">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="X21" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="Y21" t="n">
         <v>1.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG21" t="n">
-        <v>4.14</v>
+        <v>4.15</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AI21" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.52</v>
+        <v>1.91</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.55</v>
+        <v>1.74</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="AU21" t="n">
-        <v>4.34</v>
+        <v>4.5</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.58</v>
+        <v>1.12</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R22" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T22" t="n">
         <v>2</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="U22" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BD22" t="n">
         <v>3.1</v>
       </c>
-      <c r="R22" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U22" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>10</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>2.99</v>
-      </c>
       <c r="BE22" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R30" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="S30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U30" t="n">
+        <v>5</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AE30" t="n">
         <v>2.3</v>
       </c>
-      <c r="T30" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U30" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W30" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X30" t="n">
+      <c r="AF30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BA30" t="n">
         <v>2.8</v>
       </c>
-      <c r="Y30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BB30" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.44</v>
+        <v>3.15</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AS31" t="n">
         <v>1.93</v>
       </c>
-      <c r="Q31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U31" t="n">
-        <v>5</v>
-      </c>
-      <c r="V31" t="n">
+      <c r="AT31" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AY31" t="n">
         <v>1.48</v>
       </c>
-      <c r="W31" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="X31" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AZ31" t="n">
-        <v>1.52</v>
+        <v>1.35</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.15</v>
+        <v>3.44</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>4.1</v>
+        <v>3.46</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.07</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="S3" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1.5</v>
       </c>
-      <c r="AD3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AF3" t="n">
-        <v>1.41</v>
+        <v>2.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.96</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="R4" t="n">
-        <v>12.32</v>
+        <v>12</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>3.46</v>
+        <v>1.13</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.72</v>
+        <v>12.32</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.11</v>
+        <v>4.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.2</v>
+        <v>3.07</v>
       </c>
       <c r="R7" t="n">
-        <v>12</v>
+        <v>1.92</v>
       </c>
       <c r="S7" t="n">
-        <v>1.64</v>
+        <v>5.14</v>
       </c>
       <c r="T7" t="n">
-        <v>2.64</v>
+        <v>1.85</v>
       </c>
       <c r="U7" t="n">
-        <v>7.2</v>
+        <v>2.7</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="W7" t="n">
-        <v>3.6</v>
+        <v>2.19</v>
       </c>
       <c r="X7" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.58</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.8</v>
+        <v>2.08</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.46</v>
+        <v>2.75</v>
       </c>
       <c r="AF7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AR7" t="n">
         <v>2.38</v>
       </c>
-      <c r="AG7" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.71</v>
+        <v>2.28</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,130 +2968,130 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.66</v>
+        <v>2.02</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="S13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC13" t="n">
         <v>2.3</v>
       </c>
-      <c r="T13" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="U13" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.39</v>
-      </c>
       <c r="BD13" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="BF13" t="n">
         <v>1.1</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,112 +3165,112 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.65</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R14" t="n">
-        <v>2.35</v>
+        <v>3.71</v>
       </c>
       <c r="S14" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,130 +3362,130 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="S15" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="T15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AV15" t="n">
         <v>1.94</v>
       </c>
-      <c r="U15" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="X15" t="n">
+      <c r="AW15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BD15" t="n">
         <v>3.15</v>
       </c>
-      <c r="Y15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ15" t="n">
+      <c r="BE15" t="n">
         <v>1.51</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.55</v>
       </c>
       <c r="BF15" t="n">
         <v>1.1</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,112 +3559,112 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R16" t="n">
-        <v>3.71</v>
+        <v>2.35</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW16" t="n">
         <v>2.2</v>
       </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -4153,25 +4153,25 @@
         <v>1.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.26</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="S19" t="n">
         <v>2.65</v>
       </c>
       <c r="T19" t="n">
-        <v>2.05</v>
+        <v>1.99</v>
       </c>
       <c r="U19" t="n">
-        <v>4.56</v>
+        <v>3.89</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W19" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="X19" t="n">
         <v>2.99</v>
@@ -4180,10 +4180,10 @@
         <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AB19" t="n">
         <v>1.03</v>
@@ -4201,19 +4201,19 @@
         <v>1.66</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.58</v>
+        <v>3.85</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AI19" t="n">
-        <v>6.85</v>
+        <v>8</v>
       </c>
       <c r="AJ19" t="n">
         <v>1.05</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AL19" t="n">
         <v>1.83</v>
@@ -4222,7 +4222,7 @@
         <v>1.31</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4231,37 +4231,37 @@
         <v>1.19</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.87</v>
+        <v>3.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="AX19" t="n">
         <v>1.64</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AZ19" t="n">
         <v>1.6</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="BB19" t="n">
         <v>1.26</v>
@@ -4276,7 +4276,7 @@
         <v>1.56</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4347,28 +4347,28 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R20" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="S20" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="T20" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="U20" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="V20" t="n">
         <v>1.49</v>
       </c>
       <c r="W20" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="X20" t="n">
         <v>3.35</v>
@@ -4383,7 +4383,7 @@
         <v>1.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AC20" t="n">
         <v>1.43</v>
@@ -4392,7 +4392,7 @@
         <v>2.46</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="AF20" t="n">
         <v>1.52</v>
@@ -4404,10 +4404,10 @@
         <v>1.13</v>
       </c>
       <c r="AI20" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AK20" t="n">
         <v>2.05</v>
@@ -4425,43 +4425,43 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AR20" t="n">
         <v>1.89</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.65</v>
+        <v>3.78</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AZ20" t="n">
         <v>1.66</v>
       </c>
       <c r="BA20" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BC20" t="n">
         <v>2.56</v>
@@ -4544,40 +4544,40 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>4</v>
+        <v>4.43</v>
       </c>
       <c r="S21" t="n">
         <v>2.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U21" t="n">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="V21" t="n">
         <v>1.47</v>
       </c>
       <c r="W21" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="X21" t="n">
         <v>3.25</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z21" t="n">
         <v>9</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AB21" t="n">
         <v>1.08</v>
@@ -4595,13 +4595,13 @@
         <v>1.62</v>
       </c>
       <c r="AG21" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AH21" t="n">
         <v>1.2</v>
       </c>
       <c r="AI21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ21" t="n">
         <v>1.01</v>
@@ -4610,61 +4610,61 @@
         <v>2</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AM21" t="n">
         <v>1.29</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="AU21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BA21" t="n">
         <v>4.5</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>4.3</v>
       </c>
       <c r="BB21" t="n">
         <v>1.28</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="BE21" t="n">
         <v>1.48</v>
@@ -4744,22 +4744,22 @@
         <v>2.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="R22" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="S22" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="U22" t="n">
-        <v>4.08</v>
+        <v>3.34</v>
       </c>
       <c r="V22" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W22" t="n">
         <v>2.36</v>
@@ -4777,7 +4777,7 @@
         <v>1.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AC22" t="n">
         <v>1.4</v>
@@ -4792,13 +4792,13 @@
         <v>1.61</v>
       </c>
       <c r="AG22" t="n">
-        <v>4.14</v>
+        <v>4.22</v>
       </c>
       <c r="AH22" t="n">
         <v>1.18</v>
       </c>
       <c r="AI22" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="AJ22" t="n">
         <v>1.06</v>
@@ -4807,7 +4807,7 @@
         <v>1.85</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AM22" t="n">
         <v>1.36</v>
@@ -4822,10 +4822,10 @@
         <v>1.13</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AS22" t="n">
         <v>1.96</v>
@@ -4837,7 +4837,7 @@
         <v>4.34</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="AW22" t="n">
         <v>2.18</v>
@@ -4855,19 +4855,19 @@
         <v>2.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="BD22" t="n">
         <v>3.1</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R23" t="n">
-        <v>3.13</v>
+        <v>2.99</v>
       </c>
       <c r="S23" t="n">
-        <v>2.79</v>
+        <v>2.89</v>
       </c>
       <c r="T23" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="U23" t="n">
-        <v>3.66</v>
+        <v>4.3</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W23" t="n">
-        <v>2.73</v>
+        <v>2.82</v>
       </c>
       <c r="X23" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="Y23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC23" t="n">
         <v>1.34</v>
       </c>
-      <c r="Z23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AD23" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AE23" t="n">
         <v>2.15</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.85</v>
+        <v>3.62</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AI23" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="AJ23" t="n">
         <v>1.03</v>
       </c>
       <c r="AK23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL23" t="n">
         <v>1.83</v>
       </c>
-      <c r="AL23" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AM23" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.78</v>
+        <v>3.07</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R24" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X24" t="n">
         <v>2.99</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="X24" t="n">
-        <v>3.04</v>
-      </c>
       <c r="Y24" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AE24" t="n">
         <v>2.15</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.62</v>
+        <v>3.85</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AI24" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="AJ24" t="n">
         <v>1.03</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AM24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY24" t="n">
         <v>1.38</v>
       </c>
-      <c r="AN24" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AZ24" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.83</v>
+        <v>1.59</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>3.86</v>
       </c>
       <c r="R25" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="S25" t="n">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="T25" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="U25" t="n">
-        <v>4.15</v>
+        <v>5.8</v>
       </c>
       <c r="V25" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W25" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="X25" t="n">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="Y25" t="n">
         <v>1.35</v>
       </c>
       <c r="Z25" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AA25" t="n">
         <v>1.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.12</v>
+        <v>2.99</v>
       </c>
       <c r="AE25" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.6</v>
+        <v>3.83</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AI25" t="n">
-        <v>7.11</v>
+        <v>7</v>
       </c>
       <c r="AJ25" t="n">
         <v>1.04</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN25" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5413,13 +5413,13 @@
         <v>1.24</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AT25" t="n">
         <v>2.78</v>
@@ -5431,7 +5431,7 @@
         <v>2.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="AX25" t="n">
         <v>1.62</v>
@@ -5440,25 +5440,25 @@
         <v>1.38</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.59</v>
+        <v>1.83</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.86</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="S26" t="n">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="T26" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="U26" t="n">
-        <v>5.8</v>
+        <v>4.15</v>
       </c>
       <c r="V26" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W26" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="X26" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="Y26" t="n">
         <v>1.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AA26" t="n">
         <v>1.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.99</v>
+        <v>3.12</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.83</v>
+        <v>3.6</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AI26" t="n">
-        <v>7</v>
+        <v>7.11</v>
       </c>
       <c r="AJ26" t="n">
         <v>1.04</v>
       </c>
       <c r="AK26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN26" t="n">
         <v>2</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2.36</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5610,13 +5610,13 @@
         <v>1.24</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AT26" t="n">
         <v>2.78</v>
@@ -5628,7 +5628,7 @@
         <v>2.6</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="AX26" t="n">
         <v>1.62</v>
@@ -5637,25 +5637,25 @@
         <v>1.38</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="BA26" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5923,22 +5923,22 @@
         </is>
       </c>
       <c r="P28" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="Q28" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q28" t="n">
-        <v>3.04</v>
-      </c>
       <c r="R28" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="S28" t="n">
-        <v>4.84</v>
+        <v>4.65</v>
       </c>
       <c r="T28" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="U28" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="V28" t="n">
         <v>1.52</v>
@@ -5947,7 +5947,7 @@
         <v>2.48</v>
       </c>
       <c r="X28" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="Y28" t="n">
         <v>1.3</v>
@@ -5986,28 +5986,28 @@
         <v>1.01</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AL28" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM28" t="n">
         <v>1.68</v>
       </c>
-      <c r="AM28" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AN28" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AR28" t="n">
-        <v>2.07</v>
+        <v>1.71</v>
       </c>
       <c r="AS28" t="n">
         <v>2.31</v>
@@ -6025,31 +6025,31 @@
         <v>1.88</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AY28" t="n">
         <v>1.38</v>
       </c>
       <c r="AZ28" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="BA28" t="n">
         <v>2.17</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BC28" t="n">
         <v>2.54</v>
       </c>
       <c r="BD28" t="n">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,103 +6120,103 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>5.45</v>
+        <v>4</v>
       </c>
       <c r="S29" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="T29" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U29" t="n">
-        <v>4.94</v>
+        <v>4.75</v>
       </c>
       <c r="V29" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="W29" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="X29" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z29" t="n">
         <v>7.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AC29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ29" t="n">
         <v>1.36</v>
       </c>
-      <c r="AD29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AR29" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.55</v>
+        <v>4.24</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="AW29" t="n">
         <v>2.15</v>
@@ -6225,28 +6225,28 @@
         <v>1.73</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.95</v>
+        <v>3.6</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="BD29" t="n">
-        <v>3</v>
+        <v>3.44</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="R30" t="n">
-        <v>4.2</v>
+        <v>5.45</v>
       </c>
       <c r="S30" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="T30" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>5</v>
+        <v>5.95</v>
       </c>
       <c r="V30" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W30" t="n">
         <v>2.47</v>
       </c>
       <c r="X30" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG30" t="n">
-        <v>4.6</v>
+        <v>3.92</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AI30" t="n">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS30" t="n">
         <v>2.08</v>
       </c>
-      <c r="AS30" t="n">
-        <v>2.32</v>
-      </c>
       <c r="AT30" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.4</v>
+        <v>2.87</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.8</v>
+        <v>3.96</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="BE30" t="n">
         <v>1.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="R31" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="S31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U31" t="n">
+        <v>5</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AE31" t="n">
         <v>2.3</v>
       </c>
-      <c r="T31" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U31" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W31" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X31" t="n">
+      <c r="AF31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BA31" t="n">
         <v>2.8</v>
       </c>
-      <c r="Y31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BB31" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.44</v>
+        <v>3.15</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.46</v>
+        <v>1.13</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.72</v>
+        <v>12.32</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.11</v>
+        <v>4.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.2</v>
+        <v>3.07</v>
       </c>
       <c r="R4" t="n">
-        <v>12</v>
+        <v>1.92</v>
       </c>
       <c r="S4" t="n">
-        <v>1.64</v>
+        <v>5.14</v>
       </c>
       <c r="T4" t="n">
-        <v>2.64</v>
+        <v>1.85</v>
       </c>
       <c r="U4" t="n">
-        <v>7.2</v>
+        <v>2.7</v>
       </c>
       <c r="V4" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="W4" t="n">
-        <v>3.6</v>
+        <v>2.19</v>
       </c>
       <c r="X4" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.58</v>
+        <v>1.19</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.8</v>
+        <v>11</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.8</v>
+        <v>2.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.46</v>
+        <v>2.75</v>
       </c>
       <c r="AF4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AR4" t="n">
         <v>2.38</v>
       </c>
-      <c r="AG4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.71</v>
+        <v>2.28</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.85</v>
+        <v>1.49</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>14</v>
+        <v>3.46</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.13</v>
+        <v>1.72</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AF5" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,14 +1589,14 @@
         </is>
       </c>
       <c r="P6" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>8</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.13</v>
       </c>
-      <c r="Q6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R6" t="n">
-        <v>12.32</v>
-      </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
@@ -1634,10 +1634,10 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>4.1</v>
+        <v>1.11</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.07</v>
+        <v>6.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.92</v>
+        <v>12</v>
       </c>
       <c r="S7" t="n">
-        <v>5.14</v>
+        <v>1.64</v>
       </c>
       <c r="T7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="U7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE7" t="n">
         <v>1.85</v>
       </c>
-      <c r="U7" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W7" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.49</v>
-      </c>
       <c r="BF7" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>3.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
         <v>2.13</v>
@@ -2586,10 +2586,10 @@
         <v>4.3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U11" t="n">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="V11" t="n">
         <v>1.55</v>
@@ -2610,25 +2610,25 @@
         <v>1.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AC11" t="n">
         <v>1.49</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AG11" t="n">
         <v>4.65</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AI11" t="n">
         <v>9</v>
@@ -2643,22 +2643,22 @@
         <v>1.66</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="AS11" t="n">
         <v>3.08</v>
@@ -2667,13 +2667,13 @@
         <v>4.47</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="AX11" t="n">
         <v>1.29</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="S13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.58</v>
+        <v>2.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,112 +3165,112 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R14" t="n">
-        <v>3.71</v>
+        <v>2.35</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AF14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW14" t="n">
         <v>2.2</v>
       </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.65</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE16" t="n">
         <v>2.35</v>
       </c>
-      <c r="S16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z16" t="n">
+      <c r="AF16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI16" t="n">
         <v>6.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>5.9</v>
       </c>
       <c r="AJ16" t="n">
         <v>1.07</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.37</v>
+        <v>1.77</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.74</v>
+        <v>2.08</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.95</v>
+        <v>2.32</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.48</v>
+        <v>3.05</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.39</v>
+        <v>3.22</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R23" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="X23" t="n">
         <v>2.99</v>
       </c>
-      <c r="S23" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.04</v>
-      </c>
       <c r="Y23" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z23" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AE23" t="n">
         <v>2.15</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.62</v>
+        <v>3.85</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AI23" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="AJ23" t="n">
         <v>1.03</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AM23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY23" t="n">
         <v>1.38</v>
       </c>
-      <c r="AN23" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AZ23" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.25</v>
+        <v>3.42</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R24" t="n">
-        <v>3.13</v>
+        <v>2.99</v>
       </c>
       <c r="S24" t="n">
-        <v>2.79</v>
+        <v>2.89</v>
       </c>
       <c r="T24" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="U24" t="n">
-        <v>3.66</v>
+        <v>4.3</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W24" t="n">
-        <v>2.73</v>
+        <v>2.82</v>
       </c>
       <c r="X24" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="Y24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC24" t="n">
         <v>1.34</v>
       </c>
-      <c r="Z24" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AD24" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AE24" t="n">
         <v>2.15</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.85</v>
+        <v>3.62</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="AJ24" t="n">
         <v>1.03</v>
       </c>
       <c r="AK24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL24" t="n">
         <v>1.83</v>
       </c>
-      <c r="AL24" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AM24" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.78</v>
+        <v>3.07</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitória</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.59</v>
+        <v>1.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.86</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>5.7</v>
+        <v>4.2</v>
       </c>
       <c r="S25" t="n">
-        <v>2.13</v>
+        <v>2.38</v>
       </c>
       <c r="T25" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="U25" t="n">
-        <v>5.8</v>
+        <v>4.15</v>
       </c>
       <c r="V25" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W25" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="X25" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="Y25" t="n">
         <v>1.35</v>
       </c>
       <c r="Z25" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AA25" t="n">
         <v>1.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.99</v>
+        <v>3.12</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.83</v>
+        <v>3.6</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AI25" t="n">
-        <v>7</v>
+        <v>7.11</v>
       </c>
       <c r="AJ25" t="n">
         <v>1.04</v>
       </c>
       <c r="AK25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN25" t="n">
         <v>2</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>2.36</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5413,13 +5413,13 @@
         <v>1.24</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AT25" t="n">
         <v>2.78</v>
@@ -5431,7 +5431,7 @@
         <v>2.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="AX25" t="n">
         <v>1.62</v>
@@ -5440,25 +5440,25 @@
         <v>1.38</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="BA25" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Vitória</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.83</v>
+        <v>1.59</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>3.86</v>
       </c>
       <c r="R26" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="S26" t="n">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="T26" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="U26" t="n">
-        <v>4.15</v>
+        <v>5.8</v>
       </c>
       <c r="V26" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W26" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="X26" t="n">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="Y26" t="n">
         <v>1.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AA26" t="n">
         <v>1.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.12</v>
+        <v>2.99</v>
       </c>
       <c r="AE26" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.6</v>
+        <v>3.83</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AI26" t="n">
-        <v>7.11</v>
+        <v>7</v>
       </c>
       <c r="AJ26" t="n">
         <v>1.04</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AN26" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5610,13 +5610,13 @@
         <v>1.24</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AT26" t="n">
         <v>2.78</v>
@@ -5628,7 +5628,7 @@
         <v>2.6</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="AX26" t="n">
         <v>1.62</v>
@@ -5637,25 +5637,25 @@
         <v>1.38</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.58</v>
+        <v>3.8</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R29" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="S29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U29" t="n">
+        <v>5</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AE29" t="n">
         <v>2.3</v>
       </c>
-      <c r="T29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U29" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W29" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X29" t="n">
+      <c r="AF29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BA29" t="n">
         <v>2.8</v>
       </c>
-      <c r="Y29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA29" t="n">
+      <c r="BB29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF29" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>1.15</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>5.45</v>
+        <v>4</v>
       </c>
       <c r="S30" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U30" t="n">
-        <v>5.95</v>
+        <v>4.75</v>
       </c>
       <c r="V30" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W30" t="n">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="X30" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z30" t="n">
         <v>7.5</v>
       </c>
       <c r="AA30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB30" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AC30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ30" t="n">
         <v>1.36</v>
       </c>
-      <c r="AD30" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AR30" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.65</v>
+        <v>2.43</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.55</v>
+        <v>4.24</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="AW30" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="BA30" t="n">
-        <v>3.96</v>
+        <v>3.6</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="R31" t="n">
-        <v>4.2</v>
+        <v>5.45</v>
       </c>
       <c r="S31" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="T31" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="U31" t="n">
-        <v>5</v>
+        <v>5.95</v>
       </c>
       <c r="V31" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W31" t="n">
         <v>2.47</v>
       </c>
       <c r="X31" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG31" t="n">
-        <v>4.6</v>
+        <v>3.92</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AI31" t="n">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.02</v>
+        <v>2.11</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS31" t="n">
         <v>2.08</v>
       </c>
-      <c r="AS31" t="n">
-        <v>2.32</v>
-      </c>
       <c r="AT31" t="n">
-        <v>3.05</v>
+        <v>2.65</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.22</v>
+        <v>3.55</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.4</v>
+        <v>2.87</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="BA31" t="n">
-        <v>2.8</v>
+        <v>3.96</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="BE31" t="n">
         <v>1.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q2" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q2" t="n">
-        <v>3.4</v>
-      </c>
       <c r="R2" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -846,10 +846,10 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -950,22 +950,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.13</v>
+        <v>4.14</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.5</v>
+        <v>3.13</v>
       </c>
       <c r="R3" t="n">
-        <v>12.32</v>
+        <v>1.87</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.44</v>
+        <v>2.63</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.62</v>
+        <v>1.43</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.07</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.92</v>
+        <v>2.79</v>
       </c>
       <c r="S4" t="n">
-        <v>5.14</v>
+        <v>2.64</v>
       </c>
       <c r="T4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC4" t="n">
         <v>1.85</v>
       </c>
-      <c r="U4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W4" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AM4" t="n">
+      <c r="BD4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BF4" t="n">
         <v>1.2</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.07</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.46</v>
+        <v>12.32</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R5" t="n">
-        <v>1.72</v>
+        <v>1.13</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1437,10 +1437,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.5</v>
+        <v>3.75</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,112 +1589,112 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>14</v>
+        <v>1.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.13</v>
+        <v>10</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AF6" t="n">
-        <v>3.4</v>
+        <v>2.49</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="R7" t="n">
         <v>12</v>
       </c>
       <c r="S7" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>3.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.5</v>
+        <v>3.96</v>
       </c>
       <c r="R8" t="n">
-        <v>2.79</v>
+        <v>1.97</v>
       </c>
       <c r="S8" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2186,19 +2186,19 @@
         <v>3.4</v>
       </c>
       <c r="R9" t="n">
-        <v>6.34</v>
+        <v>6.25</v>
       </c>
       <c r="S9" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="T9" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="U9" t="n">
         <v>6.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W9" t="n">
         <v>2.24</v>
@@ -2210,7 +2210,7 @@
         <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA9" t="n">
         <v>1.02</v>
@@ -2228,13 +2228,13 @@
         <v>2.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AG9" t="n">
         <v>4.75</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AI9" t="n">
         <v>9.6</v>
@@ -2246,22 +2246,22 @@
         <v>2.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.06</v>
+        <v>1.26</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AR9" t="n">
         <v>2.21</v>
@@ -2276,7 +2276,7 @@
         <v>2.51</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AW9" t="n">
         <v>1.54</v>
@@ -2297,7 +2297,7 @@
         <v>1.33</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="BD9" t="n">
         <v>2.91</v>
@@ -2377,34 +2377,34 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.01</v>
+        <v>3.06</v>
       </c>
       <c r="R10" t="n">
-        <v>4.75</v>
+        <v>4.7</v>
       </c>
       <c r="S10" t="n">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="T10" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="V10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="W10" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
         <v>10</v>
@@ -2413,25 +2413,25 @@
         <v>1.01</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AE10" t="n">
         <v>3</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AG10" t="n">
-        <v>6.45</v>
+        <v>6.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AI10" t="n">
         <v>12</v>
@@ -2443,25 +2443,25 @@
         <v>2.3</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.31</v>
+        <v>1.11</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.23</v>
+        <v>2.49</v>
       </c>
       <c r="AS10" t="n">
         <v>3.58</v>
@@ -2470,13 +2470,13 @@
         <v>5.43</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="AV10" t="n">
         <v>1.76</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AX10" t="n">
         <v>1.21</v>
@@ -2494,16 +2494,16 @@
         <v>1.43</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,112 +2968,112 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>2.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R13" t="n">
-        <v>3.71</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AF13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW13" t="n">
         <v>2.2</v>
       </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>2.35</v>
+        <v>4.75</v>
       </c>
       <c r="S14" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="U14" t="n">
-        <v>2.9</v>
+        <v>4.63</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W14" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="X14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AD14" t="n">
         <v>2.62</v>
       </c>
-      <c r="Y14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AE14" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AQ14" t="n">
+      <c r="AR14" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BB14" t="n">
         <v>1.31</v>
       </c>
-      <c r="AR14" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.17</v>
-      </c>
       <c r="BC14" t="n">
-        <v>2.18</v>
+        <v>2.39</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
-        <v>4.75</v>
+        <v>3.71</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.51</v>
+        <v>1.65</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.61</v>
+        <v>2.2</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -4153,43 +4153,43 @@
         <v>1.95</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R19" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="S19" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W19" t="n">
         <v>2.65</v>
       </c>
-      <c r="T19" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U19" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.7</v>
-      </c>
       <c r="X19" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z19" t="n">
         <v>7.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AB19" t="n">
         <v>1.03</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AD19" t="n">
         <v>2.83</v>
@@ -4201,16 +4201,16 @@
         <v>1.66</v>
       </c>
       <c r="AG19" t="n">
-        <v>3.85</v>
+        <v>3.98</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AI19" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK19" t="n">
         <v>1.85</v>
@@ -4222,40 +4222,40 @@
         <v>1.31</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.78</v>
+        <v>2.35</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AX19" t="n">
         <v>1.64</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AZ19" t="n">
         <v>1.6</v>
@@ -4276,7 +4276,7 @@
         <v>1.56</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.99</v>
+        <v>2.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="R20" t="n">
-        <v>3.9</v>
+        <v>3.26</v>
       </c>
       <c r="S20" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="U20" t="n">
-        <v>4.6</v>
+        <v>3.34</v>
       </c>
       <c r="V20" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="W20" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="X20" t="n">
-        <v>3.35</v>
+        <v>3.16</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AB20" t="n">
         <v>1.05</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AG20" t="n">
-        <v>4.75</v>
+        <v>4.22</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AI20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.14</v>
+        <v>1.85</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.78</v>
+        <v>4.34</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.62</v>
+        <v>2.93</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.35</v>
+        <v>1.54</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
         <v>3.25</v>
       </c>
       <c r="R21" t="n">
-        <v>4.43</v>
+        <v>4</v>
       </c>
       <c r="S21" t="n">
         <v>2.4</v>
@@ -4565,13 +4565,13 @@
         <v>1.47</v>
       </c>
       <c r="W21" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="X21" t="n">
         <v>3.25</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z21" t="n">
         <v>9</v>
@@ -4583,7 +4583,7 @@
         <v>1.08</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AD21" t="n">
         <v>2.7</v>
@@ -4595,7 +4595,7 @@
         <v>1.62</v>
       </c>
       <c r="AG21" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="AH21" t="n">
         <v>1.2</v>
@@ -4613,10 +4613,10 @@
         <v>1.7</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4631,25 +4631,25 @@
         <v>1.87</v>
       </c>
       <c r="AS21" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AU21" t="n">
         <v>3.9</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="AX21" t="n">
         <v>1.65</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AZ21" t="n">
         <v>1.24</v>
@@ -4661,10 +4661,10 @@
         <v>1.28</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="BD21" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BE21" t="n">
         <v>1.48</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="R22" t="n">
-        <v>3.26</v>
+        <v>3.9</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="T22" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="U22" t="n">
-        <v>3.34</v>
+        <v>5.05</v>
       </c>
       <c r="V22" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W22" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="X22" t="n">
-        <v>3.16</v>
+        <v>3.35</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AC22" t="n">
         <v>1.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.85</v>
+        <v>2.56</v>
       </c>
       <c r="AE22" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BA22" t="n">
         <v>2.25</v>
       </c>
-      <c r="AF22" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AT22" t="n">
+      <c r="BB22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BC22" t="n">
         <v>2.5</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.45</v>
       </c>
       <c r="BD22" t="n">
         <v>3.1</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="R23" t="n">
-        <v>3.13</v>
+        <v>3.68</v>
       </c>
       <c r="S23" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="T23" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="U23" t="n">
-        <v>3.66</v>
+        <v>3.9</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W23" t="n">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="X23" t="n">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB23" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AC23" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.85</v>
+        <v>3.87</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AI23" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AJ23" t="n">
         <v>1.03</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AL23" t="n">
         <v>1.85</v>
       </c>
       <c r="AM23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY23" t="n">
         <v>1.36</v>
       </c>
-      <c r="AN23" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AZ23" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,55 +5135,55 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="R24" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="S24" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="T24" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="U24" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="V24" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W24" t="n">
-        <v>2.82</v>
+        <v>2.69</v>
       </c>
       <c r="X24" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.94</v>
+        <v>3.23</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG24" t="n">
         <v>3.62</v>
@@ -5192,61 +5192,61 @@
         <v>1.21</v>
       </c>
       <c r="AI24" t="n">
-        <v>7.3</v>
+        <v>9.5</v>
       </c>
       <c r="AJ24" t="n">
         <v>1.03</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.07</v>
+        <v>2.63</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.37</v>
+        <v>2.65</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="BB24" t="n">
         <v>1.25</v>
@@ -5255,13 +5255,13 @@
         <v>2.25</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5332,22 +5332,22 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>3.56</v>
       </c>
       <c r="R25" t="n">
-        <v>4.2</v>
+        <v>4.35</v>
       </c>
       <c r="S25" t="n">
         <v>2.38</v>
       </c>
       <c r="T25" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="U25" t="n">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="V25" t="n">
         <v>1.4</v>
@@ -5356,7 +5356,7 @@
         <v>2.73</v>
       </c>
       <c r="X25" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="Y25" t="n">
         <v>1.35</v>
@@ -5371,34 +5371,34 @@
         <v>1</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="AE25" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG25" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AI25" t="n">
-        <v>7.11</v>
+        <v>7.34</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AK25" t="n">
         <v>1.87</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AM25" t="n">
         <v>1.3</v>
@@ -5410,37 +5410,37 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.52</v>
+        <v>3.7</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="BA25" t="n">
         <v>2.95</v>
@@ -5449,13 +5449,13 @@
         <v>1.23</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="BD25" t="n">
         <v>3.58</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="BF25" t="n">
         <v>1.12</v>
@@ -5532,19 +5532,19 @@
         <v>1.59</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.86</v>
+        <v>3.7</v>
       </c>
       <c r="R26" t="n">
-        <v>5.7</v>
+        <v>5.89</v>
       </c>
       <c r="S26" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="T26" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="U26" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="V26" t="n">
         <v>1.41</v>
@@ -5553,40 +5553,40 @@
         <v>2.69</v>
       </c>
       <c r="X26" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Y26" t="n">
         <v>1.35</v>
       </c>
       <c r="Z26" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="AA26" t="n">
         <v>1.03</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AD26" t="n">
         <v>2.99</v>
       </c>
       <c r="AE26" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AG26" t="n">
-        <v>3.83</v>
+        <v>3.52</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AI26" t="n">
-        <v>7</v>
+        <v>6.85</v>
       </c>
       <c r="AJ26" t="n">
         <v>1.04</v>
@@ -5595,10 +5595,10 @@
         <v>2</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AN26" t="n">
         <v>2.36</v>
@@ -5610,52 +5610,52 @@
         <v>1.24</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AY26" t="n">
         <v>1.38</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="BA26" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5726,19 +5726,19 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="R27" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="S27" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="T27" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U27" t="n">
         <v>3.55</v>
@@ -5750,52 +5750,52 @@
         <v>2.53</v>
       </c>
       <c r="X27" t="n">
-        <v>3.15</v>
+        <v>3.36</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z27" t="n">
-        <v>7.5</v>
+        <v>8.6</v>
       </c>
       <c r="AA27" t="n">
         <v>1.01</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AD27" t="n">
         <v>2.8</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AG27" t="n">
         <v>3.9</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AI27" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AL27" t="n">
         <v>1.84</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AN27" t="n">
         <v>1.5</v>
@@ -5804,55 +5804,55 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.41</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="AU27" t="n">
-        <v>3.52</v>
+        <v>3.74</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AW27" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.52</v>
+        <v>2.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5923,37 +5923,37 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.81</v>
+        <v>3.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S28" t="n">
         <v>4.65</v>
       </c>
       <c r="T28" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U28" t="n">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="V28" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W28" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="X28" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="Y28" t="n">
         <v>1.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AA28" t="n">
         <v>1.01</v>
@@ -5962,28 +5962,28 @@
         <v>1.06</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AD28" t="n">
         <v>2.46</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AF28" t="n">
         <v>1.58</v>
       </c>
       <c r="AG28" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AH28" t="n">
         <v>1.14</v>
       </c>
       <c r="AI28" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AK28" t="n">
         <v>2.05</v>
@@ -5992,64 +5992,64 @@
         <v>1.67</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.68</v>
+        <v>1.32</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.71</v>
+        <v>1.97</v>
       </c>
       <c r="AS28" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AU28" t="n">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="AV28" t="n">
-        <v>2.41</v>
+        <v>2.54</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AZ28" t="n">
-        <v>2.08</v>
+        <v>2.53</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.17</v>
+        <v>1.84</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.93</v>
+        <v>1.65</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="S29" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="T29" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>5</v>
+        <v>5.95</v>
       </c>
       <c r="V29" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W29" t="n">
         <v>2.47</v>
       </c>
       <c r="X29" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB29" t="n">
         <v>1.05</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.64</v>
+        <v>2.89</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG29" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AI29" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.86</v>
+        <v>2.11</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="BB29" t="n">
         <v>1.28</v>
       </c>
-      <c r="AQ29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AX29" t="n">
+      <c r="BC29" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BE29" t="n">
         <v>1.54</v>
       </c>
-      <c r="AY29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>1.5</v>
-      </c>
       <c r="BF29" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R30" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="S30" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U30" t="n">
+        <v>5</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AE30" t="n">
         <v>2.3</v>
       </c>
-      <c r="T30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U30" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X30" t="n">
+      <c r="AF30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA30" t="n">
         <v>2.8</v>
       </c>
-      <c r="Y30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>3.6</v>
-      </c>
       <c r="BB30" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="R31" t="n">
-        <v>5.45</v>
+        <v>3.9</v>
       </c>
       <c r="S31" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="T31" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="U31" t="n">
-        <v>5.95</v>
+        <v>4.5</v>
       </c>
       <c r="V31" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W31" t="n">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="X31" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z31" t="n">
         <v>7.5</v>
       </c>
       <c r="AA31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>1.06</v>
       </c>
-      <c r="AB31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AK31" t="n">
-        <v>2.11</v>
+        <v>1.8</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AN31" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.33</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.55</v>
+        <v>4.24</v>
       </c>
       <c r="AV31" t="n">
         <v>2.87</v>
       </c>
       <c r="AW31" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="BA31" t="n">
-        <v>3.96</v>
+        <v>3.6</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.39</v>
+        <v>2.2</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>

--- a/jogos_2026-04-01.xlsx
+++ b/jogos_2026-04-01.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,112 +1195,112 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>3.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>3.96</v>
       </c>
       <c r="R4" t="n">
-        <v>2.79</v>
+        <v>1.97</v>
       </c>
       <c r="S4" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.07</v>
+        <v>2.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>12.32</v>
+        <v>1.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.13</v>
+        <v>10</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BF5" t="n">
         <v>1.25</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v